--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59DA2F1-8B95-9841-90DE-45C55A08D4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7353C5E3-6E60-E24A-8F15-C80C197CC5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="9" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2182,6 +2182,21 @@
     <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2191,25 +2206,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2317,7 +2317,6 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
-      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2328,14 +2327,13 @@
         </row>
         <row r="18">
           <cell r="C18">
-            <v>249.7</v>
+            <v>250.71</v>
           </cell>
           <cell r="F18">
             <v>1.4171</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2883,8 +2881,8 @@
         <v>73</v>
       </c>
       <c r="C3" s="34">
-        <f>[1]Sheet1!$C$18</f>
-        <v>249.7</v>
+        <f ca="1">[1]Sheet1!$C$18</f>
+        <v>250.71</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2917,8 +2915,8 @@
         <v>107</v>
       </c>
       <c r="C11" s="92">
-        <f>$C$3/'Statement Q'!$N$24</f>
-        <v>14.5583275527192</v>
+        <f ca="1">$C$3/'Statement Q'!$N$24</f>
+        <v>14.617213859600446</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2926,8 +2924,8 @@
         <v>181</v>
       </c>
       <c r="C12" s="92">
-        <f>$C$3/Statements!W24</f>
-        <v>14.5583275527192</v>
+        <f ca="1">$C$3/Statements!W24</f>
+        <v>14.617213859600446</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2935,8 +2933,8 @@
         <v>108</v>
       </c>
       <c r="C13" s="97">
-        <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
-        <v>4.2913517768780922</v>
+        <f ca="1">$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
+        <v>4.3087096675254566</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2944,8 +2942,8 @@
         <v>140</v>
       </c>
       <c r="C15" s="20">
-        <f>C3*'Statement Q'!N116</f>
-        <v>100878.79999999999</v>
+        <f ca="1">C3*'Statement Q'!N116</f>
+        <v>101286.84</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2971,8 +2969,8 @@
         <v>142</v>
       </c>
       <c r="C18" s="20">
-        <f>C15+C17-C16</f>
-        <v>100216.79999999999</v>
+        <f ca="1">C15+C17-C16</f>
+        <v>100624.84</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3055,15 +3053,17 @@
       <c r="B33" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="20"/>
+      <c r="C33" s="20">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C34" s="20">
-        <f>'Statement Y'!L122</f>
-        <v>411</v>
+        <f>'Statement Q'!N116</f>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C35" s="158">
         <f>C33/C34</f>
-        <v>0</v>
+        <v>2.4752475247524753E-3</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
@@ -3192,60 +3192,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="219" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="213"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
-      <c r="S2" s="221"/>
-      <c r="T2" s="221"/>
-      <c r="U2" s="221"/>
-      <c r="V2" s="221"/>
-      <c r="W2" s="221"/>
-      <c r="X2" s="221"/>
-      <c r="Y2" s="221"/>
-      <c r="Z2" s="221"/>
-      <c r="AA2" s="221"/>
-      <c r="AB2" s="221"/>
-      <c r="AC2" s="221"/>
+      <c r="I2" s="213"/>
+      <c r="J2" s="213"/>
+      <c r="K2" s="213"/>
+      <c r="L2" s="213"/>
+      <c r="S2" s="216"/>
+      <c r="T2" s="216"/>
+      <c r="U2" s="216"/>
+      <c r="V2" s="216"/>
+      <c r="W2" s="216"/>
+      <c r="X2" s="216"/>
+      <c r="Y2" s="216"/>
+      <c r="Z2" s="216"/>
+      <c r="AA2" s="216"/>
+      <c r="AB2" s="216"/>
+      <c r="AC2" s="216"/>
       <c r="AE2" s="121"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="91"/>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="221"/>
-      <c r="Y4" s="221"/>
-      <c r="Z4" s="221"/>
-      <c r="AA4" s="221"/>
-      <c r="AB4" s="221"/>
-      <c r="AC4" s="221"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="S4" s="216"/>
+      <c r="T4" s="216"/>
+      <c r="U4" s="216"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="216"/>
+      <c r="X4" s="216"/>
+      <c r="Y4" s="216"/>
+      <c r="Z4" s="216"/>
+      <c r="AA4" s="216"/>
+      <c r="AB4" s="216"/>
+      <c r="AC4" s="216"/>
       <c r="AE4" s="122"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3332,23 +3332,23 @@
       </c>
       <c r="H6" s="106">
         <f>Revenue!H9</f>
-        <v>26414.730000000003</v>
+        <v>26013.462</v>
       </c>
       <c r="I6" s="106">
         <f>Revenue!I9</f>
-        <v>29402.990100000006</v>
+        <v>28696.378320000003</v>
       </c>
       <c r="J6" s="106">
         <f>Revenue!J9</f>
-        <v>32484.413761000007</v>
+        <v>31704.242395200006</v>
       </c>
       <c r="K6" s="106">
         <f>Revenue!K9</f>
-        <v>35923.13711221001</v>
+        <v>34874.030860900813</v>
       </c>
       <c r="L6" s="106">
         <f>Revenue!L9</f>
-        <v>39402.179015618509</v>
+        <v>38252.850332990893</v>
       </c>
       <c r="N6" s="114" t="s">
         <v>145</v>
@@ -3393,23 +3393,23 @@
       </c>
       <c r="H7" s="131">
         <f>'COGS &amp; OpEx'!H11</f>
-        <v>2773.5466500000002</v>
+        <v>2731.4135099999999</v>
       </c>
       <c r="I7" s="131">
         <f>'COGS &amp; OpEx'!I11</f>
-        <v>3028.5079803000003</v>
+        <v>2955.72696696</v>
       </c>
       <c r="J7" s="131">
         <f>'COGS &amp; OpEx'!J11</f>
-        <v>3280.9257898610008</v>
+        <v>3202.1284819152011</v>
       </c>
       <c r="K7" s="131">
         <f>'COGS &amp; OpEx'!K11</f>
-        <v>3592.3137112210011</v>
+        <v>3487.4030860900816</v>
       </c>
       <c r="L7" s="131">
         <f>'COGS &amp; OpEx'!L11</f>
-        <v>3940.2179015618512</v>
+        <v>3825.2850332990893</v>
       </c>
       <c r="N7" s="114" t="s">
         <v>139</v>
@@ -3454,23 +3454,23 @@
       </c>
       <c r="H8" s="108">
         <f t="shared" si="0"/>
-        <v>23641.183350000003</v>
+        <v>23282.048490000001</v>
       </c>
       <c r="I8" s="108">
         <f t="shared" si="0"/>
-        <v>26374.482119700006</v>
+        <v>25740.651353040004</v>
       </c>
       <c r="J8" s="108">
         <f t="shared" si="0"/>
-        <v>29203.487971139006</v>
+        <v>28502.113913284804</v>
       </c>
       <c r="K8" s="108">
         <f t="shared" si="0"/>
-        <v>32330.823400989007</v>
+        <v>31386.627774810731</v>
       </c>
       <c r="L8" s="108">
         <f t="shared" si="0"/>
-        <v>35461.961114056656</v>
+        <v>34427.565299691807</v>
       </c>
       <c r="N8" s="114"/>
       <c r="Q8" s="114"/>
@@ -3514,23 +3514,23 @@
       </c>
       <c r="H9" s="131">
         <f>'COGS &amp; OpEx'!H12</f>
-        <v>5018.7987000000003</v>
+        <v>4942.5577800000001</v>
       </c>
       <c r="I9" s="131">
         <f>'COGS &amp; OpEx'!I12</f>
-        <v>5615.9711091000017</v>
+        <v>5481.0082591200007</v>
       </c>
       <c r="J9" s="131">
         <f>'COGS &amp; OpEx'!J12</f>
-        <v>6269.4918558730014</v>
+        <v>6118.9187822736012</v>
       </c>
       <c r="K9" s="131">
         <f>'COGS &amp; OpEx'!K12</f>
-        <v>7005.0117368809524</v>
+        <v>6800.4360178756588</v>
       </c>
       <c r="L9" s="131">
         <f>'COGS &amp; OpEx'!L12</f>
-        <v>7683.4249080456093</v>
+        <v>7459.3058149332246</v>
       </c>
       <c r="N9" s="114" t="s">
         <v>139</v>
@@ -3576,23 +3576,23 @@
       </c>
       <c r="H10" s="131">
         <f>'COGS &amp; OpEx'!H13</f>
-        <v>7131.977100000001</v>
+        <v>7023.6347400000004</v>
       </c>
       <c r="I10" s="131">
         <f>'COGS &amp; OpEx'!I13</f>
-        <v>7938.8073270000023</v>
+        <v>7748.0221464000015</v>
       </c>
       <c r="J10" s="131">
         <f>'COGS &amp; OpEx'!J13</f>
-        <v>8770.7917154700026</v>
+        <v>8560.1454467040021</v>
       </c>
       <c r="K10" s="131">
         <f>'COGS &amp; OpEx'!K13</f>
-        <v>9699.2470202967033</v>
+        <v>9415.9883324432194</v>
       </c>
       <c r="L10" s="131">
         <f>'COGS &amp; OpEx'!L13</f>
-        <v>10638.588334216998</v>
+        <v>10328.269589907542</v>
       </c>
       <c r="N10" s="114" t="s">
         <v>139</v>
@@ -3638,23 +3638,23 @@
       </c>
       <c r="H11" s="131">
         <f>'COGS &amp; OpEx'!H14</f>
-        <v>1849.0311000000004</v>
+        <v>1820.9423400000001</v>
       </c>
       <c r="I11" s="131">
         <f>'COGS &amp; OpEx'!I14</f>
-        <v>2058.2093070000005</v>
+        <v>2008.7464824000003</v>
       </c>
       <c r="J11" s="131">
         <f>'COGS &amp; OpEx'!J14</f>
-        <v>2273.9089632700006</v>
+        <v>2219.2969676640005</v>
       </c>
       <c r="K11" s="131">
         <f>'COGS &amp; OpEx'!K14</f>
-        <v>2514.6195978547007</v>
+        <v>2441.1821602630571</v>
       </c>
       <c r="L11" s="131">
         <f>'COGS &amp; OpEx'!L14</f>
-        <v>2758.1525310932957</v>
+        <v>2677.6995233093626</v>
       </c>
       <c r="N11" s="114" t="s">
         <v>139</v>
@@ -3761,23 +3761,23 @@
       </c>
       <c r="H13" s="131">
         <f>'COGS &amp; OpEx'!H16</f>
-        <v>14160.806900000001</v>
+        <v>13948.13486</v>
       </c>
       <c r="I13" s="131">
         <f>'COGS &amp; OpEx'!I16</f>
-        <v>15731.987743100006</v>
+        <v>15356.776887920003</v>
       </c>
       <c r="J13" s="131">
         <f>'COGS &amp; OpEx'!J16</f>
-        <v>17387.192534613005</v>
+        <v>16971.361196641607</v>
       </c>
       <c r="K13" s="131">
         <f>'COGS &amp; OpEx'!K16</f>
-        <v>19287.878355032357</v>
+        <v>18726.606510581936</v>
       </c>
       <c r="L13" s="131">
         <f>'COGS &amp; OpEx'!L16</f>
-        <v>21145.165773355904</v>
+        <v>20530.274928150131</v>
       </c>
       <c r="N13" s="142" t="s">
         <v>139</v>
@@ -3822,23 +3822,23 @@
       </c>
       <c r="H14" s="108">
         <f t="shared" si="1"/>
-        <v>9480.3764500000016</v>
+        <v>9333.9136300000009</v>
       </c>
       <c r="I14" s="108">
         <f t="shared" si="1"/>
-        <v>10642.4943766</v>
+        <v>10383.874465120001</v>
       </c>
       <c r="J14" s="108">
         <f t="shared" si="1"/>
-        <v>11816.295436526001</v>
+        <v>11530.752716643197</v>
       </c>
       <c r="K14" s="108">
         <f t="shared" si="1"/>
-        <v>13042.945045956651</v>
+        <v>12660.021264228795</v>
       </c>
       <c r="L14" s="108">
         <f t="shared" si="1"/>
-        <v>14316.795340700752</v>
+        <v>13897.290371541676</v>
       </c>
       <c r="N14" s="114"/>
       <c r="Q14" s="114"/>
@@ -3856,18 +3856,18 @@
       <c r="AE14" s="103"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="220" t="s">
+      <c r="C17" s="212" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="220"/>
-      <c r="E17" s="220"/>
-      <c r="F17" s="220"/>
-      <c r="G17" s="220"/>
-      <c r="H17" s="220"/>
-      <c r="I17" s="220"/>
-      <c r="J17" s="220"/>
-      <c r="K17" s="220"/>
-      <c r="L17" s="220"/>
+      <c r="D17" s="212"/>
+      <c r="E17" s="212"/>
+      <c r="F17" s="212"/>
+      <c r="G17" s="212"/>
+      <c r="H17" s="212"/>
+      <c r="I17" s="212"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="212"/>
+      <c r="L17" s="212"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C18" s="61">
@@ -3952,18 +3952,18 @@
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="220" t="s">
+      <c r="C22" s="212" t="s">
         <v>249</v>
       </c>
-      <c r="D22" s="220"/>
-      <c r="E22" s="220"/>
-      <c r="F22" s="220"/>
-      <c r="G22" s="220"/>
-      <c r="H22" s="220"/>
-      <c r="I22" s="220"/>
-      <c r="J22" s="220"/>
-      <c r="K22" s="220"/>
-      <c r="L22" s="220"/>
+      <c r="D22" s="212"/>
+      <c r="E22" s="212"/>
+      <c r="F22" s="212"/>
+      <c r="G22" s="212"/>
+      <c r="H22" s="212"/>
+      <c r="I22" s="212"/>
+      <c r="J22" s="212"/>
+      <c r="K22" s="212"/>
+      <c r="L22" s="212"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
@@ -4036,23 +4036,23 @@
       </c>
       <c r="H24" s="102">
         <f>'WC &amp; Investments'!H42</f>
-        <v>792.44190000000003</v>
+        <v>780.40386000000001</v>
       </c>
       <c r="I24" s="102">
         <f>'WC &amp; Investments'!I42</f>
-        <v>882.08970300000021</v>
+        <v>860.89134960000013</v>
       </c>
       <c r="J24" s="102">
         <f>'WC &amp; Investments'!J42</f>
-        <v>974.53241283000023</v>
+        <v>951.12727185600011</v>
       </c>
       <c r="K24" s="102">
         <f>'WC &amp; Investments'!K42</f>
-        <v>1077.6941133663004</v>
+        <v>1046.2209258270243</v>
       </c>
       <c r="L24" s="102">
         <f>'WC &amp; Investments'!L42</f>
-        <v>1182.0653704685553</v>
+        <v>1147.5855099897267</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>250</v>
@@ -4084,23 +4084,23 @@
       </c>
       <c r="H25" s="102">
         <f>'WC &amp; Investments'!H45</f>
-        <v>396.22095000000002</v>
+        <v>390.20193</v>
       </c>
       <c r="I25" s="102">
         <f>'WC &amp; Investments'!I45</f>
-        <v>441.04485150000011</v>
+        <v>430.44567480000006</v>
       </c>
       <c r="J25" s="102">
         <f>'WC &amp; Investments'!J45</f>
-        <v>487.26620641500011</v>
+        <v>475.56363592800005</v>
       </c>
       <c r="K25" s="102">
         <f>'WC &amp; Investments'!K45</f>
-        <v>538.84705668315019</v>
+        <v>523.11046291351215</v>
       </c>
       <c r="L25" s="102">
         <f>'WC &amp; Investments'!L45</f>
-        <v>591.03268523427766</v>
+        <v>573.79275499486334</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>250</v>
@@ -4132,41 +4132,41 @@
       </c>
       <c r="H26" s="102">
         <f>'WC &amp; Investments'!H35</f>
-        <v>138.39711794520531</v>
+        <v>165.56790868493141</v>
       </c>
       <c r="I26" s="102">
         <f>'WC &amp; Investments'!I35</f>
-        <v>316.76915001945184</v>
+        <v>329.64002362389004</v>
       </c>
       <c r="J26" s="102">
         <f>'WC &amp; Investments'!J35</f>
-        <v>368.30119584185485</v>
+        <v>359.4164958350861</v>
       </c>
       <c r="K26" s="102">
         <f>'WC &amp; Investments'!K35</f>
-        <v>409.08637011143298</v>
+        <v>412.02497541346207</v>
       </c>
       <c r="L26" s="102">
         <f>'WC &amp; Investments'!L35</f>
-        <v>480.17220091485069</v>
+        <v>466.05462597896906</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C29" s="220" t="s">
+      <c r="C29" s="212" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="220"/>
-      <c r="E29" s="220"/>
-      <c r="F29" s="220"/>
-      <c r="G29" s="220"/>
-      <c r="H29" s="220"/>
-      <c r="I29" s="220"/>
-      <c r="J29" s="220"/>
-      <c r="K29" s="220"/>
-      <c r="L29" s="220"/>
+      <c r="D29" s="212"/>
+      <c r="E29" s="212"/>
+      <c r="F29" s="212"/>
+      <c r="G29" s="212"/>
+      <c r="H29" s="212"/>
+      <c r="I29" s="212"/>
+      <c r="J29" s="212"/>
+      <c r="K29" s="212"/>
+      <c r="L29" s="212"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
@@ -4239,23 +4239,23 @@
       </c>
       <c r="H31" s="132">
         <f t="shared" si="5"/>
-        <v>7489.4973955000014</v>
+        <v>7373.7917677000014</v>
       </c>
       <c r="I31" s="132">
         <f t="shared" si="5"/>
-        <v>8407.570557514</v>
+        <v>8203.2608274448012</v>
       </c>
       <c r="J31" s="132">
         <f t="shared" si="5"/>
-        <v>9334.8733948555418</v>
+        <v>9109.294646148126</v>
       </c>
       <c r="K31" s="132">
         <f t="shared" si="5"/>
-        <v>10303.926586305754</v>
+        <v>10001.416798740749</v>
       </c>
       <c r="L31" s="132">
         <f t="shared" si="5"/>
-        <v>11310.268319153594</v>
+        <v>10978.859393517925</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
@@ -4284,23 +4284,23 @@
       </c>
       <c r="H32" s="108">
         <f t="shared" si="6"/>
-        <v>8024.1154634452078</v>
+        <v>7929.5616063849329</v>
       </c>
       <c r="I32" s="108">
         <f t="shared" si="6"/>
-        <v>9165.3845590334513</v>
+        <v>8963.346525868692</v>
       </c>
       <c r="J32" s="108">
         <f t="shared" si="6"/>
-        <v>10190.440797112396</v>
+        <v>9944.2747779112124</v>
       </c>
       <c r="K32" s="108">
         <f t="shared" si="6"/>
-        <v>11251.860013100337</v>
+        <v>10936.552237067724</v>
       </c>
       <c r="L32" s="108">
         <f t="shared" si="6"/>
-        <v>12381.473205302724</v>
+        <v>12018.706774491759</v>
       </c>
     </row>
   </sheetData>
@@ -4373,10 +4373,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="213" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="215"/>
+      <c r="C4" s="213"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4392,8 +4392,8 @@
         <v>73</v>
       </c>
       <c r="C6" s="144">
-        <f>Overview!C3</f>
-        <v>249.7</v>
+        <f ca="1">Overview!C3</f>
+        <v>250.71</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4401,8 +4401,8 @@
         <v>138</v>
       </c>
       <c r="C7" s="146">
-        <f>C5*C6</f>
-        <v>100878.79999999999</v>
+        <f ca="1">C5*C6</f>
+        <v>101286.84</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4419,7 +4419,7 @@
         <v>153</v>
       </c>
       <c r="C9" s="169">
-        <f>[1]Sheet1!$C$10/1000</f>
+        <f ca="1">[1]Sheet1!$C$10/1000</f>
         <v>4.3900000000000002E-2</v>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
         <v>154</v>
       </c>
       <c r="C10" s="144">
-        <f>[1]Sheet1!$F$18</f>
+        <f ca="1">[1]Sheet1!$F$18</f>
         <v>1.4171</v>
       </c>
     </row>
@@ -4458,18 +4458,18 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="215" t="s">
+      <c r="B15" s="213" t="s">
         <v>157</v>
       </c>
-      <c r="C15" s="215"/>
+      <c r="C15" s="213"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C16" s="147">
-        <f>C8/(C8+C7)</f>
-        <v>5.8147568595084541E-2</v>
+        <f ca="1">C8/(C8+C7)</f>
+        <v>5.7926887116234373E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4477,8 +4477,8 @@
         <v>149</v>
       </c>
       <c r="C17" s="147">
-        <f>C7/(C8+C7)</f>
-        <v>0.94185243140491548</v>
+        <f ca="1">C7/(C8+C7)</f>
+        <v>0.94207311288376561</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4495,7 +4495,7 @@
         <v>150</v>
       </c>
       <c r="C19" s="147">
-        <f>C9+C10*C11</f>
+        <f ca="1">C9+C10*C11</f>
         <v>0.114755</v>
       </c>
     </row>
@@ -4504,8 +4504,8 @@
         <v>147</v>
       </c>
       <c r="C20" s="147">
-        <f>(C17*C19)+(C16*C18)</f>
-        <v>0.11056285104213737</v>
+        <f ca="1">(C17*C19)+(C16*C18)</f>
+        <v>0.11057876107335507</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4552,60 +4552,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="215" t="s">
+      <c r="C3" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="215"/>
-      <c r="E3" s="215"/>
-      <c r="F3" s="215"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="219" t="s">
+      <c r="D3" s="213"/>
+      <c r="E3" s="213"/>
+      <c r="F3" s="213"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="215"/>
-      <c r="K3" s="215"/>
-      <c r="L3" s="215"/>
-      <c r="P3" s="221"/>
-      <c r="Q3" s="221"/>
-      <c r="R3" s="221"/>
-      <c r="S3" s="221"/>
-      <c r="T3" s="221"/>
-      <c r="U3" s="221"/>
-      <c r="V3" s="221"/>
-      <c r="W3" s="221"/>
-      <c r="X3" s="221"/>
-      <c r="Y3" s="221"/>
-      <c r="Z3" s="221"/>
+      <c r="I3" s="213"/>
+      <c r="J3" s="213"/>
+      <c r="K3" s="213"/>
+      <c r="L3" s="213"/>
+      <c r="P3" s="216"/>
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="216"/>
+      <c r="T3" s="216"/>
+      <c r="U3" s="216"/>
+      <c r="V3" s="216"/>
+      <c r="W3" s="216"/>
+      <c r="X3" s="216"/>
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
       <c r="AB3" s="121"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="104"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="220" t="s">
+      <c r="C5" s="212" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="220"/>
-      <c r="E5" s="220"/>
-      <c r="F5" s="220"/>
-      <c r="G5" s="220"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="220"/>
-      <c r="J5" s="220"/>
-      <c r="K5" s="220"/>
-      <c r="L5" s="220"/>
-      <c r="P5" s="221"/>
-      <c r="Q5" s="221"/>
-      <c r="R5" s="221"/>
-      <c r="S5" s="221"/>
-      <c r="T5" s="221"/>
-      <c r="U5" s="221"/>
-      <c r="V5" s="221"/>
-      <c r="W5" s="221"/>
-      <c r="X5" s="221"/>
-      <c r="Y5" s="221"/>
-      <c r="Z5" s="221"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="216"/>
+      <c r="R5" s="216"/>
+      <c r="S5" s="216"/>
+      <c r="T5" s="216"/>
+      <c r="U5" s="216"/>
+      <c r="V5" s="216"/>
+      <c r="W5" s="216"/>
+      <c r="X5" s="216"/>
+      <c r="Y5" s="216"/>
+      <c r="Z5" s="216"/>
       <c r="AB5" s="122"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4692,23 +4692,23 @@
       </c>
       <c r="H7" s="131">
         <f>'FCF &amp; Other'!H32</f>
-        <v>8024.1154634452078</v>
+        <v>7929.5616063849329</v>
       </c>
       <c r="I7" s="131">
         <f>'FCF &amp; Other'!I32</f>
-        <v>9165.3845590334513</v>
+        <v>8963.346525868692</v>
       </c>
       <c r="J7" s="131">
         <f>'FCF &amp; Other'!J32</f>
-        <v>10190.440797112396</v>
+        <v>9944.2747779112124</v>
       </c>
       <c r="K7" s="131">
         <f>'FCF &amp; Other'!K32</f>
-        <v>11251.860013100337</v>
+        <v>10936.552237067724</v>
       </c>
       <c r="L7" s="131">
         <f>'FCF &amp; Other'!L32</f>
-        <v>12381.473205302724</v>
+        <v>12018.706774491759</v>
       </c>
       <c r="N7" s="90"/>
       <c r="O7" s="7"/>
@@ -4757,8 +4757,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="132">
-        <f>L7*(1+C14)/(C15-C14)</f>
-        <v>148323.83307547003</v>
+        <f ca="1">L7*(1+C14)/(C15-C14)</f>
+        <v>143951.30625102756</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -4811,24 +4811,24 @@
       <c r="F10" s="129"/>
       <c r="G10" s="149"/>
       <c r="H10" s="132">
-        <f>H7/(1+$C$15)^H9</f>
-        <v>7225.269110987716</v>
+        <f ca="1">H7/(1+$C$15)^H9</f>
+        <v>7140.0263397088102</v>
       </c>
       <c r="I10" s="132">
-        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>7431.2933900346352</v>
+        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
+        <v>7267.2727369910053</v>
       </c>
       <c r="J10" s="132">
-        <f t="shared" si="0"/>
-        <v>7439.8391178070378</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7259.8061612306137</v>
       </c>
       <c r="K10" s="132">
-        <f t="shared" si="0"/>
-        <v>7396.9341492984358</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7189.2399158161461</v>
       </c>
       <c r="L10" s="132">
-        <f t="shared" si="0"/>
-        <v>7329.2006631466484</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7113.9518473341886</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -4846,15 +4846,15 @@
       <c r="J11" s="129"/>
       <c r="K11" s="129"/>
       <c r="L11" s="132">
-        <f>L8/(1+C15)^L9</f>
-        <v>87800.144434477144</v>
+        <f ca="1">L8/(1+C15)^L9</f>
+        <v>85205.728057540706</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="215" t="s">
+      <c r="B13" s="213" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="215"/>
+      <c r="C13" s="213"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4869,23 +4869,23 @@
         <v>147</v>
       </c>
       <c r="C15" s="148">
-        <f>WACC!C20</f>
-        <v>0.11056285104213737</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11057876107335507</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="215" t="s">
+      <c r="B18" s="213" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="215"/>
+      <c r="C18" s="213"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C19" s="103">
-        <f>SUM(H10:L10)</f>
-        <v>36822.536431274471</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>35970.297001080762</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4893,8 +4893,8 @@
         <v>164</v>
       </c>
       <c r="C20" s="103">
-        <f>L11</f>
-        <v>87800.144434477144</v>
+        <f ca="1">L11</f>
+        <v>85205.728057540706</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4902,8 +4902,8 @@
         <v>167</v>
       </c>
       <c r="C21" s="108">
-        <f>C19+C20</f>
-        <v>124622.68086575161</v>
+        <f ca="1">C19+C20</f>
+        <v>121176.02505862147</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4929,8 +4929,8 @@
         <v>168</v>
       </c>
       <c r="C24" s="108">
-        <f>C21+C22-C23</f>
-        <v>125284.68086575161</v>
+        <f ca="1">C21+C22-C23</f>
+        <v>121838.02505862147</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4947,8 +4947,8 @@
         <v>169</v>
       </c>
       <c r="C26" s="151">
-        <f>C24/C25</f>
-        <v>310.11059620235545</v>
+        <f ca="1">C24/C25</f>
+        <v>301.57926994708282</v>
       </c>
     </row>
   </sheetData>
@@ -4991,37 +4991,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="219" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="213"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
+      <c r="I2" s="213"/>
+      <c r="J2" s="213"/>
+      <c r="K2" s="213"/>
+      <c r="L2" s="213"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="91"/>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="212" t="s">
         <v>253</v>
       </c>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5094,23 +5094,23 @@
       </c>
       <c r="H6" s="106">
         <f>Revenue!H9</f>
-        <v>26414.730000000003</v>
+        <v>26013.462</v>
       </c>
       <c r="I6" s="106">
         <f>Revenue!I9</f>
-        <v>29402.990100000006</v>
+        <v>28696.378320000003</v>
       </c>
       <c r="J6" s="106">
         <f>Revenue!J9</f>
-        <v>32484.413761000007</v>
+        <v>31704.242395200006</v>
       </c>
       <c r="K6" s="106">
         <f>Revenue!K9</f>
-        <v>35923.13711221001</v>
+        <v>34874.030860900813</v>
       </c>
       <c r="L6" s="106">
         <f>Revenue!L9</f>
-        <v>39402.179015618509</v>
+        <v>38252.850332990893</v>
       </c>
       <c r="N6" s="90"/>
     </row>
@@ -5140,23 +5140,23 @@
       </c>
       <c r="H7" s="106">
         <f>'FCF &amp; Other'!H14</f>
-        <v>9480.3764500000016</v>
+        <v>9333.9136300000009</v>
       </c>
       <c r="I7" s="106">
         <f>'FCF &amp; Other'!I14</f>
-        <v>10642.4943766</v>
+        <v>10383.874465120001</v>
       </c>
       <c r="J7" s="106">
         <f>'FCF &amp; Other'!J14</f>
-        <v>11816.295436526001</v>
+        <v>11530.752716643197</v>
       </c>
       <c r="K7" s="106">
         <f>'FCF &amp; Other'!K14</f>
-        <v>13042.945045956651</v>
+        <v>12660.021264228795</v>
       </c>
       <c r="L7" s="106">
         <f>'FCF &amp; Other'!L14</f>
-        <v>14316.795340700752</v>
+        <v>13897.290371541676</v>
       </c>
       <c r="N7" s="90"/>
     </row>
@@ -5186,23 +5186,23 @@
       </c>
       <c r="H8" s="106">
         <f>'FCF &amp; Other'!H32</f>
-        <v>8024.1154634452078</v>
+        <v>7929.5616063849329</v>
       </c>
       <c r="I8" s="106">
         <f>'FCF &amp; Other'!I32</f>
-        <v>9165.3845590334513</v>
+        <v>8963.346525868692</v>
       </c>
       <c r="J8" s="106">
         <f>'FCF &amp; Other'!J32</f>
-        <v>10190.440797112396</v>
+        <v>9944.2747779112124</v>
       </c>
       <c r="K8" s="106">
         <f>'FCF &amp; Other'!K32</f>
-        <v>11251.860013100337</v>
+        <v>10936.552237067724</v>
       </c>
       <c r="L8" s="106">
         <f>'FCF &amp; Other'!L32</f>
-        <v>12381.473205302724</v>
+        <v>12018.706774491759</v>
       </c>
       <c r="N8" s="90"/>
     </row>
@@ -5210,18 +5210,18 @@
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="220" t="s">
+      <c r="C10" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="220"/>
-      <c r="E10" s="220"/>
-      <c r="F10" s="220"/>
-      <c r="G10" s="220"/>
-      <c r="H10" s="220"/>
-      <c r="I10" s="220"/>
-      <c r="J10" s="220"/>
-      <c r="K10" s="220"/>
-      <c r="L10" s="220"/>
+      <c r="D10" s="212"/>
+      <c r="E10" s="212"/>
+      <c r="F10" s="212"/>
+      <c r="G10" s="212"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
+      <c r="L10" s="212"/>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5293,23 +5293,23 @@
       </c>
       <c r="H12" s="110">
         <f t="shared" si="1"/>
-        <v>0.11131010980689146</v>
+        <v>9.4428120661365619E-2</v>
       </c>
       <c r="I12" s="110">
         <f t="shared" si="1"/>
-        <v>0.11312854986592719</v>
+        <v>0.10313568874454326</v>
       </c>
       <c r="J12" s="110">
         <f t="shared" si="1"/>
-        <v>0.10479967005124421</v>
+        <v>0.10481685325090886</v>
       </c>
       <c r="K12" s="110">
         <f t="shared" si="1"/>
-        <v>0.10585763918998133</v>
+        <v>9.9979946727278057E-2</v>
       </c>
       <c r="L12" s="110">
         <f t="shared" si="1"/>
-        <v>9.6846828620265404E-2</v>
+        <v>9.6886404831345682E-2</v>
       </c>
       <c r="N12" s="90"/>
     </row>
@@ -5336,23 +5336,23 @@
       </c>
       <c r="H13" s="110">
         <f t="shared" si="1"/>
-        <v>8.8947444291293545E-2</v>
+        <v>7.2124239604870313E-2</v>
       </c>
       <c r="I13" s="110">
         <f t="shared" si="1"/>
-        <v>0.12258141147970954</v>
+        <v>0.11248880981128173</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" si="1"/>
-        <v>0.11029379188650325</v>
+        <v>0.11044800814721156</v>
       </c>
       <c r="K13" s="110">
         <f t="shared" si="1"/>
-        <v>0.1038099983213762</v>
+        <v>9.7935371205701088E-2</v>
       </c>
       <c r="L13" s="110">
         <f t="shared" si="1"/>
-        <v>9.766584849170995E-2</v>
+        <v>9.7730413045104075E-2</v>
       </c>
       <c r="N13" s="90"/>
     </row>
@@ -5379,23 +5379,23 @@
       </c>
       <c r="H14" s="110">
         <f t="shared" si="1"/>
-        <v>-3.9159522313855701E-2</v>
+        <v>-5.0481788749171218E-2</v>
       </c>
       <c r="I14" s="110">
         <f t="shared" si="1"/>
-        <v>0.1422298944709143</v>
+        <v>0.13037100546029542</v>
       </c>
       <c r="J14" s="110">
         <f t="shared" si="1"/>
-        <v>0.11183995952124501</v>
+        <v>0.10943772498491602</v>
       </c>
       <c r="K14" s="110">
         <f t="shared" si="1"/>
-        <v>0.10415832220807449</v>
+        <v>9.978379332001315E-2</v>
       </c>
       <c r="L14" s="110">
         <f t="shared" si="1"/>
-        <v>0.10039346302630843</v>
+        <v>9.8948417560357035E-2</v>
       </c>
       <c r="N14" s="90"/>
     </row>
@@ -5403,18 +5403,18 @@
       <c r="N15" s="90"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="220" t="s">
+      <c r="C16" s="212" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="220"/>
-      <c r="E16" s="220"/>
-      <c r="F16" s="220"/>
-      <c r="G16" s="220"/>
-      <c r="H16" s="220"/>
-      <c r="I16" s="220"/>
-      <c r="J16" s="220"/>
-      <c r="K16" s="220"/>
-      <c r="L16" s="220"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="212"/>
+      <c r="K16" s="212"/>
+      <c r="L16" s="212"/>
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5486,23 +5486,23 @@
       </c>
       <c r="H18" s="172">
         <f>G18*(1+H19)</f>
-        <v>416.32499999999999</v>
+        <v>407.78499999999997</v>
       </c>
       <c r="I18" s="172">
         <f t="shared" ref="I18:L18" si="4">H18*(1+I19)</f>
-        <v>405.916875</v>
+        <v>395.55144999999993</v>
       </c>
       <c r="J18" s="172">
         <f t="shared" si="4"/>
-        <v>396.17487</v>
+        <v>385.66266374999992</v>
       </c>
       <c r="K18" s="172">
         <f t="shared" si="4"/>
-        <v>387.06284798999997</v>
+        <v>376.79242248374993</v>
       </c>
       <c r="L18" s="172">
         <f t="shared" si="4"/>
-        <v>378.54746533421996</v>
+        <v>368.50298918910744</v>
       </c>
       <c r="N18" s="90"/>
     </row>
@@ -5528,13 +5528,13 @@
         <v>-5.1111111111111107E-2</v>
       </c>
       <c r="H19" s="171">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="I19" s="112">
+        <v>-0.03</v>
+      </c>
+      <c r="J19" s="112">
         <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="I19" s="112">
-        <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="J19" s="112">
-        <v>-2.4E-2</v>
       </c>
       <c r="K19" s="112">
         <v>-2.3E-2</v>
@@ -5548,18 +5548,18 @@
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="220" t="s">
+      <c r="C21" s="212" t="s">
         <v>254</v>
       </c>
-      <c r="D21" s="220"/>
-      <c r="E21" s="220"/>
-      <c r="F21" s="220"/>
-      <c r="G21" s="220"/>
-      <c r="H21" s="220"/>
-      <c r="I21" s="220"/>
-      <c r="J21" s="220"/>
-      <c r="K21" s="220"/>
-      <c r="L21" s="220"/>
+      <c r="D21" s="212"/>
+      <c r="E21" s="212"/>
+      <c r="F21" s="212"/>
+      <c r="G21" s="212"/>
+      <c r="H21" s="212"/>
+      <c r="I21" s="212"/>
+      <c r="J21" s="212"/>
+      <c r="K21" s="212"/>
+      <c r="L21" s="212"/>
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5643,18 +5643,18 @@
       <c r="N25" s="90"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="220" t="s">
+      <c r="C26" s="212" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="220"/>
-      <c r="E26" s="220"/>
-      <c r="F26" s="220"/>
-      <c r="G26" s="220"/>
-      <c r="H26" s="220"/>
-      <c r="I26" s="220"/>
-      <c r="J26" s="220"/>
-      <c r="K26" s="220"/>
-      <c r="L26" s="220"/>
+      <c r="D26" s="212"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="212"/>
+      <c r="G26" s="212"/>
+      <c r="H26" s="212"/>
+      <c r="I26" s="212"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="212"/>
+      <c r="L26" s="212"/>
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5924,10 +5924,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="215" t="s">
+      <c r="B37" s="213" t="s">
         <v>259</v>
       </c>
-      <c r="C37" s="215"/>
+      <c r="C37" s="213"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C38" s="103">
         <f>L7</f>
-        <v>14316.795340700752</v>
+        <v>13897.290371541676</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -5944,8 +5944,8 @@
         <v>147</v>
       </c>
       <c r="C39" s="137">
-        <f>WACC!C20</f>
-        <v>0.11056285104213737</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11057876107335507</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C41" s="20">
         <f>L18</f>
-        <v>378.54746533421996</v>
+        <v>368.50298918910744</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="C42" s="20">
         <f>(C38*C40)-G30+G31</f>
-        <v>358304.88351751881</v>
+        <v>347817.25928854191</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="C43" s="20">
         <f>C42/C41</f>
-        <v>946.52564428392373</v>
+        <v>943.8655031100709</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -5988,15 +5988,15 @@
         <v>262</v>
       </c>
       <c r="C44" s="151">
-        <f>C43/(1+C48)^5</f>
-        <v>560.29490713592577</v>
+        <f ca="1">C43/(1+C48)^5</f>
+        <v>558.68021955039728</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="215" t="s">
+      <c r="B46" s="213" t="s">
         <v>184</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="213"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="C47" s="103">
         <f>L6</f>
-        <v>39402.179015618509</v>
+        <v>38252.850332990893</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -6012,8 +6012,8 @@
         <v>147</v>
       </c>
       <c r="C48" s="137">
-        <f>WACC!C20</f>
-        <v>0.11056285104213737</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11057876107335507</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="C50" s="20">
         <f>L18</f>
-        <v>378.54746533421996</v>
+        <v>368.50298918910744</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C51" s="20">
         <f>(C47*C49)/C50</f>
-        <v>936.79034629771604</v>
+        <v>934.25470918023814</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -6047,15 +6047,15 @@
         <v>262</v>
       </c>
       <c r="C52" s="151">
-        <f>C51/(1+C48)^5</f>
-        <v>554.53210724343114</v>
+        <f ca="1">C51/(1+C48)^5</f>
+        <v>552.99152720484551</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="215" t="s">
+      <c r="B54" s="213" t="s">
         <v>263</v>
       </c>
-      <c r="C54" s="215"/>
+      <c r="C54" s="213"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C55" s="103">
         <f>L8</f>
-        <v>12381.473205302724</v>
+        <v>12018.706774491759</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
@@ -6071,8 +6071,8 @@
         <v>147</v>
       </c>
       <c r="C56" s="137">
-        <f>WACC!C20</f>
-        <v>0.11056285104213737</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11057876107335507</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C58" s="20">
         <f>L18</f>
-        <v>378.54746533421996</v>
+        <v>368.50298918910744</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="C59" s="20">
         <f>(C55*C57)-G30+G31</f>
-        <v>334684.77654317353</v>
+        <v>324890.08291127748</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C60" s="20">
         <f>C59/C58</f>
-        <v>884.12895922491509</v>
+        <v>881.64843282872584</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -6115,8 +6115,8 @@
         <v>262</v>
       </c>
       <c r="C61" s="151">
-        <f>C60/(1+C56)^5</f>
-        <v>523.35925190898729</v>
+        <f ca="1">C60/(1+C56)^5</f>
+        <v>521.85352510078474</v>
       </c>
     </row>
   </sheetData>
@@ -6165,10 +6165,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="213" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="215"/>
+      <c r="C4" s="213"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6176,8 +6176,8 @@
         <v>189</v>
       </c>
       <c r="C5" s="166">
-        <f>DCF!C26</f>
-        <v>310.11059620235545</v>
+        <f ca="1">DCF!C26</f>
+        <v>301.57926994708282</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6185,8 +6185,8 @@
         <v>266</v>
       </c>
       <c r="C6" s="166">
-        <f>Multiples!C44</f>
-        <v>560.29490713592577</v>
+        <f ca="1">Multiples!C44</f>
+        <v>558.68021955039728</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6194,8 +6194,8 @@
         <v>190</v>
       </c>
       <c r="C7" s="166">
-        <f>Multiples!C52</f>
-        <v>554.53210724343114</v>
+        <f ca="1">Multiples!C52</f>
+        <v>552.99152720484551</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6203,8 +6203,8 @@
         <v>267</v>
       </c>
       <c r="C8" s="166">
-        <f>Multiples!C61</f>
-        <v>523.35925190898729</v>
+        <f ca="1">Multiples!C61</f>
+        <v>521.85352510078474</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6212,8 +6212,8 @@
         <v>188</v>
       </c>
       <c r="C9" s="151">
-        <f>AVERAGE(C5:C8)</f>
-        <v>487.0742156226749</v>
+        <f ca="1">AVERAGE(C5:C8)</f>
+        <v>483.77613545077759</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6221,8 +6221,8 @@
         <v>335</v>
       </c>
       <c r="C10" s="34">
-        <f>Overview!C3</f>
-        <v>249.7</v>
+        <f ca="1">Overview!C3</f>
+        <v>250.71</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6230,8 +6230,8 @@
         <v>336</v>
       </c>
       <c r="C11" s="88">
-        <f>(C9-C10)/C10</f>
-        <v>0.95063762764387238</v>
+        <f ca="1">(C9-C10)/C10</f>
+        <v>0.92962440848301853</v>
       </c>
     </row>
   </sheetData>
@@ -6275,60 +6275,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="215" t="s">
+      <c r="C3" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="215"/>
-      <c r="E3" s="215"/>
-      <c r="F3" s="215"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="219" t="s">
+      <c r="D3" s="213"/>
+      <c r="E3" s="213"/>
+      <c r="F3" s="213"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="215"/>
-      <c r="K3" s="215"/>
-      <c r="L3" s="215"/>
-      <c r="P3" s="221"/>
-      <c r="Q3" s="221"/>
-      <c r="R3" s="221"/>
-      <c r="S3" s="221"/>
-      <c r="T3" s="221"/>
-      <c r="U3" s="221"/>
-      <c r="V3" s="221"/>
-      <c r="W3" s="221"/>
-      <c r="X3" s="221"/>
-      <c r="Y3" s="221"/>
-      <c r="Z3" s="221"/>
+      <c r="I3" s="213"/>
+      <c r="J3" s="213"/>
+      <c r="K3" s="213"/>
+      <c r="L3" s="213"/>
+      <c r="P3" s="216"/>
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="216"/>
+      <c r="T3" s="216"/>
+      <c r="U3" s="216"/>
+      <c r="V3" s="216"/>
+      <c r="W3" s="216"/>
+      <c r="X3" s="216"/>
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
       <c r="AB3" s="121"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="104"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="220" t="s">
+      <c r="C5" s="212" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="220"/>
-      <c r="E5" s="220"/>
-      <c r="F5" s="220"/>
-      <c r="G5" s="220"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="220"/>
-      <c r="J5" s="220"/>
-      <c r="K5" s="220"/>
-      <c r="L5" s="220"/>
-      <c r="P5" s="221"/>
-      <c r="Q5" s="221"/>
-      <c r="R5" s="221"/>
-      <c r="S5" s="221"/>
-      <c r="T5" s="221"/>
-      <c r="U5" s="221"/>
-      <c r="V5" s="221"/>
-      <c r="W5" s="221"/>
-      <c r="X5" s="221"/>
-      <c r="Y5" s="221"/>
-      <c r="Z5" s="221"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="216"/>
+      <c r="R5" s="216"/>
+      <c r="S5" s="216"/>
+      <c r="T5" s="216"/>
+      <c r="U5" s="216"/>
+      <c r="V5" s="216"/>
+      <c r="W5" s="216"/>
+      <c r="X5" s="216"/>
+      <c r="Y5" s="216"/>
+      <c r="Z5" s="216"/>
       <c r="AB5" s="122"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6462,8 +6462,8 @@
       <c r="J8" s="129"/>
       <c r="K8" s="129"/>
       <c r="L8" s="132">
-        <f>L7*(1+C20)/(C21-C20)</f>
-        <v>115976.66618046047</v>
+        <f ca="1">L7*(1+C20)/(C21-C20)</f>
+        <v>115955.10484495721</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -6516,24 +6516,24 @@
       <c r="F10" s="129"/>
       <c r="G10" s="149"/>
       <c r="H10" s="132">
-        <f>H7/(1+$C$21)^H9</f>
-        <v>7745.3306320305383</v>
+        <f ca="1">H7/(1+$C$21)^H9</f>
+        <v>7745.2196732615921</v>
       </c>
       <c r="I10" s="132">
-        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>7183.4660627314288</v>
+        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
+        <v>7183.2602450899121</v>
       </c>
       <c r="J10" s="132">
-        <f t="shared" si="1"/>
-        <v>6662.3604757445983</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>6662.0741470797066</v>
       </c>
       <c r="K10" s="132">
-        <f t="shared" si="1"/>
-        <v>6179.0571182689109</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>6178.7030438617039</v>
       </c>
       <c r="L10" s="132">
-        <f t="shared" si="1"/>
-        <v>5730.8137273317607</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>5730.4032440047731</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -6551,8 +6551,8 @@
       <c r="J11" s="129"/>
       <c r="K11" s="129"/>
       <c r="L11" s="132">
-        <f>L8/(1+C21)^L9</f>
-        <v>68652.271388458394</v>
+        <f ca="1">L8/(1+C21)^L9</f>
+        <v>68634.591707517204</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6567,8 +6567,8 @@
         <v>339</v>
       </c>
       <c r="C15" s="197">
-        <f>Overview!C3</f>
-        <v>249.7</v>
+        <f ca="1">Overview!C3</f>
+        <v>250.71</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6576,8 +6576,8 @@
         <v>340</v>
       </c>
       <c r="C16" s="197">
-        <f>C36</f>
-        <v>254.49331535783571</v>
+        <f ca="1">C36</f>
+        <v>254.44616846736361</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6615,8 +6615,8 @@
         <v>147</v>
       </c>
       <c r="C21" s="202">
-        <f>WACC!C20</f>
-        <v>0.11056285104213737</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11057876107335507</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6633,8 +6633,8 @@
         <v>140</v>
       </c>
       <c r="C23" s="203">
-        <f>C15*C22</f>
-        <v>100878.79999999999</v>
+        <f ca="1">C15*C22</f>
+        <v>101286.84</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6660,8 +6660,8 @@
         <v>343</v>
       </c>
       <c r="C26" s="204">
-        <f>C23+C25-C24</f>
-        <v>100216.79999999999</v>
+        <f ca="1">C23+C25-C24</f>
+        <v>100624.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6676,8 +6676,8 @@
         <v>170</v>
       </c>
       <c r="C29" s="203">
-        <f>SUM(H10:L10)</f>
-        <v>33501.028016107237</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>33499.660353297688</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6685,8 +6685,8 @@
         <v>164</v>
       </c>
       <c r="C30" s="203">
-        <f>L11</f>
-        <v>68652.271388458394</v>
+        <f ca="1">L11</f>
+        <v>68634.591707517204</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6694,8 +6694,8 @@
         <v>167</v>
       </c>
       <c r="C31" s="206">
-        <f>C29+C30</f>
-        <v>102153.29940456562</v>
+        <f ca="1">C29+C30</f>
+        <v>102134.25206081489</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6721,8 +6721,8 @@
         <v>168</v>
       </c>
       <c r="C34" s="206">
-        <f>C31+C32-C33</f>
-        <v>102815.29940456562</v>
+        <f ca="1">C31+C32-C33</f>
+        <v>102796.25206081489</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6739,23 +6739,23 @@
         <v>169</v>
       </c>
       <c r="C36" s="209">
-        <f>C34/C35</f>
-        <v>254.49331535783571</v>
+        <f ca="1">C34/C35</f>
+        <v>254.44616846736361</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="220" t="s">
+      <c r="C39" s="212" t="s">
         <v>344</v>
       </c>
-      <c r="D39" s="220"/>
-      <c r="E39" s="220"/>
-      <c r="F39" s="220"/>
-      <c r="G39" s="220"/>
-      <c r="H39" s="220"/>
-      <c r="I39" s="220"/>
-      <c r="J39" s="220"/>
-      <c r="K39" s="220"/>
-      <c r="L39" s="220"/>
+      <c r="D39" s="212"/>
+      <c r="E39" s="212"/>
+      <c r="F39" s="212"/>
+      <c r="G39" s="212"/>
+      <c r="H39" s="212"/>
+      <c r="I39" s="212"/>
+      <c r="J39" s="212"/>
+      <c r="K39" s="212"/>
+      <c r="L39" s="212"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="61">
@@ -7187,17 +7187,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13874,11 +13874,11 @@
         <v>74</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="212" t="s">
+      <c r="P4" s="217" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="213"/>
-      <c r="R4" s="214"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="219"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -25290,36 +25290,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="219" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="213"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
+      <c r="I2" s="213"/>
+      <c r="J2" s="213"/>
+      <c r="K2" s="213"/>
+      <c r="L2" s="213"/>
       <c r="O2" s="89"/>
-      <c r="S2" s="215" t="s">
+      <c r="S2" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="T2" s="215"/>
-      <c r="U2" s="215"/>
-      <c r="V2" s="215"/>
-      <c r="W2" s="215"/>
-      <c r="X2" s="215"/>
-      <c r="Y2" s="215"/>
-      <c r="Z2" s="215"/>
-      <c r="AA2" s="215" t="s">
+      <c r="T2" s="213"/>
+      <c r="U2" s="213"/>
+      <c r="V2" s="213"/>
+      <c r="W2" s="213"/>
+      <c r="X2" s="213"/>
+      <c r="Y2" s="213"/>
+      <c r="Z2" s="213"/>
+      <c r="AA2" s="213" t="s">
         <v>103</v>
       </c>
-      <c r="AB2" s="215"/>
-      <c r="AC2" s="215"/>
+      <c r="AB2" s="213"/>
+      <c r="AC2" s="213"/>
       <c r="AE2" s="116" t="s">
         <v>74</v>
       </c>
@@ -25330,32 +25330,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="91"/>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="212" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
       <c r="O4" s="89"/>
-      <c r="S4" s="216" t="s">
+      <c r="S4" s="220" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="217"/>
-      <c r="Y4" s="217"/>
-      <c r="Z4" s="217"/>
-      <c r="AA4" s="217"/>
-      <c r="AB4" s="217"/>
-      <c r="AC4" s="217"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="221"/>
+      <c r="Y4" s="221"/>
+      <c r="Z4" s="221"/>
+      <c r="AA4" s="221"/>
+      <c r="AB4" s="221"/>
+      <c r="AC4" s="221"/>
       <c r="AE4" s="118" t="s">
         <v>334</v>
       </c>
@@ -25480,23 +25480,23 @@
       </c>
       <c r="H6" s="103">
         <f t="shared" ref="H6:L8" si="1">G6*(1+H13)</f>
-        <v>25652.480000000003</v>
+        <v>25263.112000000001</v>
       </c>
       <c r="I6" s="103">
         <f t="shared" si="1"/>
-        <v>28730.777600000005</v>
+        <v>28042.054320000003</v>
       </c>
       <c r="J6" s="103">
         <f t="shared" si="1"/>
-        <v>31891.163136000006</v>
+        <v>31126.680295200007</v>
       </c>
       <c r="K6" s="103">
         <f t="shared" si="1"/>
-        <v>35399.191080960009</v>
+        <v>34363.855045900811</v>
       </c>
       <c r="L6" s="103">
         <f t="shared" si="1"/>
-        <v>38939.110189056009</v>
+        <v>37800.240550490897</v>
       </c>
       <c r="N6" s="114"/>
       <c r="O6" s="89"/>
@@ -25575,23 +25575,23 @@
       </c>
       <c r="H7" s="103">
         <f t="shared" si="1"/>
-        <v>276.25</v>
+        <v>269.75</v>
       </c>
       <c r="I7" s="103">
         <f t="shared" si="1"/>
-        <v>234.8125</v>
+        <v>226.59</v>
       </c>
       <c r="J7" s="103">
         <f t="shared" si="1"/>
-        <v>199.59062499999999</v>
+        <v>192.60149999999999</v>
       </c>
       <c r="K7" s="103">
         <f t="shared" si="1"/>
-        <v>169.65203124999999</v>
+        <v>163.71127499999997</v>
       </c>
       <c r="L7" s="103">
         <f t="shared" si="1"/>
-        <v>144.2042265625</v>
+        <v>140.79169649999997</v>
       </c>
       <c r="N7" s="114"/>
       <c r="O7" s="89"/>
@@ -25670,23 +25670,23 @@
       </c>
       <c r="H8" s="103">
         <f t="shared" si="1"/>
-        <v>486</v>
+        <v>480.6</v>
       </c>
       <c r="I8" s="103">
         <f t="shared" si="1"/>
-        <v>437.40000000000003</v>
+        <v>427.73400000000004</v>
       </c>
       <c r="J8" s="103">
         <f t="shared" si="1"/>
-        <v>393.66</v>
+        <v>384.96060000000006</v>
       </c>
       <c r="K8" s="103">
         <f t="shared" si="1"/>
-        <v>354.29400000000004</v>
+        <v>346.46454000000006</v>
       </c>
       <c r="L8" s="103">
         <f t="shared" si="1"/>
-        <v>318.86460000000005</v>
+        <v>311.81808600000005</v>
       </c>
       <c r="N8" s="114"/>
       <c r="O8" s="89"/>
@@ -25764,23 +25764,23 @@
       </c>
       <c r="H9" s="108">
         <f>SUM(H6:H8)</f>
-        <v>26414.730000000003</v>
+        <v>26013.462</v>
       </c>
       <c r="I9" s="108">
         <f>SUM(I6:I8)</f>
-        <v>29402.990100000006</v>
+        <v>28696.378320000003</v>
       </c>
       <c r="J9" s="108">
         <f>SUM(J6:J8)</f>
-        <v>32484.413761000007</v>
+        <v>31704.242395200006</v>
       </c>
       <c r="K9" s="108">
         <f>SUM(K6:K8)</f>
-        <v>35923.13711221001</v>
+        <v>34874.030860900813</v>
       </c>
       <c r="L9" s="108">
         <f>SUM(L6:L8)</f>
-        <v>39402.179015618509</v>
+        <v>38252.850332990893</v>
       </c>
       <c r="O9" s="89"/>
       <c r="Q9" s="90"/>
@@ -25835,33 +25835,33 @@
       <c r="Q10" s="90"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="220" t="s">
+      <c r="C11" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="220"/>
-      <c r="E11" s="220"/>
-      <c r="F11" s="220"/>
-      <c r="G11" s="220"/>
-      <c r="H11" s="220"/>
-      <c r="I11" s="220"/>
-      <c r="J11" s="220"/>
-      <c r="K11" s="220"/>
-      <c r="L11" s="220"/>
+      <c r="D11" s="212"/>
+      <c r="E11" s="212"/>
+      <c r="F11" s="212"/>
+      <c r="G11" s="212"/>
+      <c r="H11" s="212"/>
+      <c r="I11" s="212"/>
+      <c r="J11" s="212"/>
+      <c r="K11" s="212"/>
+      <c r="L11" s="212"/>
       <c r="O11" s="89"/>
       <c r="Q11" s="90"/>
-      <c r="S11" s="216" t="s">
+      <c r="S11" s="220" t="s">
         <v>113</v>
       </c>
-      <c r="T11" s="217"/>
-      <c r="U11" s="217"/>
-      <c r="V11" s="217"/>
-      <c r="W11" s="217"/>
-      <c r="X11" s="217"/>
-      <c r="Y11" s="217"/>
-      <c r="Z11" s="217"/>
-      <c r="AA11" s="217"/>
-      <c r="AB11" s="217"/>
-      <c r="AC11" s="217"/>
+      <c r="T11" s="221"/>
+      <c r="U11" s="221"/>
+      <c r="V11" s="221"/>
+      <c r="W11" s="221"/>
+      <c r="X11" s="221"/>
+      <c r="Y11" s="221"/>
+      <c r="Z11" s="221"/>
+      <c r="AA11" s="221"/>
+      <c r="AB11" s="221"/>
+      <c r="AC11" s="221"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
@@ -25980,16 +25980,16 @@
         <v>0.11612494517811034</v>
       </c>
       <c r="H13" s="112">
-        <v>0.12</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="I13" s="112">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" s="112">
         <v>0.11</v>
       </c>
       <c r="K13" s="112">
-        <v>0.11</v>
+        <v>0.104</v>
       </c>
       <c r="L13" s="112">
         <v>0.1</v>
@@ -26058,10 +26058,10 @@
         <v>-0.15803108808290156</v>
       </c>
       <c r="H14" s="112">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="I14" s="112">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="J14" s="112">
         <v>-0.15</v>
@@ -26070,7 +26070,7 @@
         <v>-0.15</v>
       </c>
       <c r="L14" s="112">
-        <v>-0.15</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="O14" s="89"/>
       <c r="Q14" s="90"/>
@@ -26136,10 +26136,10 @@
         <v>-9.6989966555183993E-2</v>
       </c>
       <c r="H15" s="112">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="I15" s="112">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="J15" s="112">
         <v>-0.1</v>
@@ -26214,23 +26214,23 @@
       </c>
       <c r="H16" s="177">
         <f t="shared" ref="H16:L16" si="9">H9/G9-1</f>
-        <v>0.11131010980689138</v>
+        <v>9.4428120661365522E-2</v>
       </c>
       <c r="I16" s="177">
         <f t="shared" si="9"/>
-        <v>0.11312854986592713</v>
+        <v>0.10313568874454337</v>
       </c>
       <c r="J16" s="177">
         <f t="shared" si="9"/>
-        <v>0.10479967005124413</v>
+        <v>0.10481685325090884</v>
       </c>
       <c r="K16" s="177">
         <f t="shared" si="9"/>
-        <v>0.10585763918998126</v>
+        <v>9.9979946727278168E-2</v>
       </c>
       <c r="L16" s="177">
         <f t="shared" si="9"/>
-        <v>9.6846828620265502E-2</v>
+        <v>9.6886404831345585E-2</v>
       </c>
       <c r="O16" s="89"/>
       <c r="Q16" s="90"/>
@@ -26318,35 +26318,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="219" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="213"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
-      <c r="P2" s="215" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="213"/>
+      <c r="K2" s="213"/>
+      <c r="L2" s="213"/>
+      <c r="P2" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="Q2" s="215"/>
-      <c r="R2" s="215"/>
-      <c r="S2" s="215"/>
-      <c r="T2" s="215"/>
-      <c r="U2" s="215"/>
-      <c r="V2" s="215"/>
-      <c r="W2" s="215"/>
-      <c r="X2" s="215" t="s">
+      <c r="Q2" s="213"/>
+      <c r="R2" s="213"/>
+      <c r="S2" s="213"/>
+      <c r="T2" s="213"/>
+      <c r="U2" s="213"/>
+      <c r="V2" s="213"/>
+      <c r="W2" s="213"/>
+      <c r="X2" s="213" t="s">
         <v>103</v>
       </c>
-      <c r="Y2" s="215"/>
-      <c r="Z2" s="215"/>
+      <c r="Y2" s="213"/>
+      <c r="Z2" s="213"/>
       <c r="AB2" s="116" t="s">
         <v>74</v>
       </c>
@@ -26355,31 +26355,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="91"/>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="212" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="P4" s="217" t="s">
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="P4" s="221" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="217"/>
-      <c r="Y4" s="217"/>
-      <c r="Z4" s="217"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="221"/>
+      <c r="Y4" s="221"/>
+      <c r="Z4" s="221"/>
       <c r="AB4" s="118" t="str">
         <f>Revenue!AE4</f>
         <v>Q3-Q4-Q1</v>
@@ -26504,23 +26504,23 @@
       </c>
       <c r="H6" s="106">
         <f>Revenue!H9</f>
-        <v>26414.730000000003</v>
+        <v>26013.462</v>
       </c>
       <c r="I6" s="106">
         <f>Revenue!I9</f>
-        <v>29402.990100000006</v>
+        <v>28696.378320000003</v>
       </c>
       <c r="J6" s="106">
         <f>Revenue!J9</f>
-        <v>32484.413761000007</v>
+        <v>31704.242395200006</v>
       </c>
       <c r="K6" s="106">
         <f>Revenue!K9</f>
-        <v>35923.13711221001</v>
+        <v>34874.030860900813</v>
       </c>
       <c r="L6" s="106">
         <f>Revenue!L9</f>
-        <v>39402.179015618509</v>
+        <v>38252.850332990893</v>
       </c>
       <c r="N6" s="90"/>
       <c r="O6" s="7" t="s">
@@ -26582,32 +26582,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="220" t="s">
+      <c r="C9" s="212" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="220"/>
-      <c r="E9" s="220"/>
-      <c r="F9" s="220"/>
-      <c r="G9" s="220"/>
-      <c r="H9" s="220"/>
-      <c r="I9" s="220"/>
-      <c r="J9" s="220"/>
-      <c r="K9" s="220"/>
-      <c r="L9" s="220"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="212"/>
+      <c r="F9" s="212"/>
+      <c r="G9" s="212"/>
+      <c r="H9" s="212"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="212"/>
+      <c r="K9" s="212"/>
+      <c r="L9" s="212"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="217" t="s">
+      <c r="P9" s="221" t="s">
         <v>124</v>
       </c>
-      <c r="Q9" s="217"/>
-      <c r="R9" s="217"/>
-      <c r="S9" s="217"/>
-      <c r="T9" s="217"/>
-      <c r="U9" s="217"/>
-      <c r="V9" s="217"/>
-      <c r="W9" s="217"/>
-      <c r="X9" s="217"/>
-      <c r="Y9" s="217"/>
-      <c r="Z9" s="217"/>
+      <c r="Q9" s="221"/>
+      <c r="R9" s="221"/>
+      <c r="S9" s="221"/>
+      <c r="T9" s="221"/>
+      <c r="U9" s="221"/>
+      <c r="V9" s="221"/>
+      <c r="W9" s="221"/>
+      <c r="X9" s="221"/>
+      <c r="Y9" s="221"/>
+      <c r="Z9" s="221"/>
       <c r="AB9" s="118" t="str">
         <f>AB4</f>
         <v>Q3-Q4-Q1</v>
@@ -26736,23 +26736,23 @@
       </c>
       <c r="H11" s="21">
         <f t="shared" ref="H11:L13" si="3">H21*H$6</f>
-        <v>2773.5466500000002</v>
+        <v>2731.4135099999999</v>
       </c>
       <c r="I11" s="21">
         <f t="shared" si="3"/>
-        <v>3028.5079803000003</v>
+        <v>2955.72696696</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="3"/>
-        <v>3280.9257898610008</v>
+        <v>3202.1284819152011</v>
       </c>
       <c r="K11" s="21">
         <f t="shared" si="3"/>
-        <v>3592.3137112210011</v>
+        <v>3487.4030860900816</v>
       </c>
       <c r="L11" s="21">
         <f t="shared" si="3"/>
-        <v>3940.2179015618512</v>
+        <v>3825.2850332990893</v>
       </c>
       <c r="N11" s="90"/>
       <c r="O11" s="7" t="s">
@@ -26828,23 +26828,23 @@
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
-        <v>5018.7987000000003</v>
+        <v>4942.5577800000001</v>
       </c>
       <c r="I12" s="20">
         <f t="shared" si="3"/>
-        <v>5615.9711091000017</v>
+        <v>5481.0082591200007</v>
       </c>
       <c r="J12" s="20">
         <f t="shared" si="3"/>
-        <v>6269.4918558730014</v>
+        <v>6118.9187822736012</v>
       </c>
       <c r="K12" s="20">
         <f t="shared" si="3"/>
-        <v>7005.0117368809524</v>
+        <v>6800.4360178756588</v>
       </c>
       <c r="L12" s="20">
         <f t="shared" si="3"/>
-        <v>7683.4249080456093</v>
+        <v>7459.3058149332246</v>
       </c>
       <c r="N12" s="90"/>
       <c r="O12" s="1" t="s">
@@ -26920,23 +26920,23 @@
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
-        <v>7131.977100000001</v>
+        <v>7023.6347400000004</v>
       </c>
       <c r="I13" s="20">
         <f t="shared" si="3"/>
-        <v>7938.8073270000023</v>
+        <v>7748.0221464000015</v>
       </c>
       <c r="J13" s="20">
         <f t="shared" si="3"/>
-        <v>8770.7917154700026</v>
+        <v>8560.1454467040021</v>
       </c>
       <c r="K13" s="20">
         <f t="shared" si="3"/>
-        <v>9699.2470202967033</v>
+        <v>9415.9883324432194</v>
       </c>
       <c r="L13" s="20">
         <f t="shared" si="3"/>
-        <v>10638.588334216998</v>
+        <v>10328.269589907542</v>
       </c>
       <c r="M13" s="114"/>
       <c r="N13" s="114"/>
@@ -27013,23 +27013,23 @@
       </c>
       <c r="H14" s="20">
         <f>H24*H$6</f>
-        <v>1849.0311000000004</v>
+        <v>1820.9423400000001</v>
       </c>
       <c r="I14" s="20">
         <f t="shared" ref="I14:L14" si="5">I24*I$6</f>
-        <v>2058.2093070000005</v>
+        <v>2008.7464824000003</v>
       </c>
       <c r="J14" s="20">
         <f t="shared" si="5"/>
-        <v>2273.9089632700006</v>
+        <v>2219.2969676640005</v>
       </c>
       <c r="K14" s="20">
         <f t="shared" si="5"/>
-        <v>2514.6195978547007</v>
+        <v>2441.1821602630571</v>
       </c>
       <c r="L14" s="20">
         <f t="shared" si="5"/>
-        <v>2758.1525310932957</v>
+        <v>2677.6995233093626</v>
       </c>
       <c r="M14" s="114"/>
       <c r="N14" s="114"/>
@@ -27127,23 +27127,23 @@
       </c>
       <c r="H16" s="21">
         <f>SUM(H12:H15)</f>
-        <v>14160.806900000001</v>
+        <v>13948.13486</v>
       </c>
       <c r="I16" s="21">
         <f t="shared" ref="I16:L16" si="6">SUM(I12:I15)</f>
-        <v>15731.987743100006</v>
+        <v>15356.776887920003</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="6"/>
-        <v>17387.192534613005</v>
+        <v>16971.361196641607</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="6"/>
-        <v>19287.878355032357</v>
+        <v>18726.606510581936</v>
       </c>
       <c r="L16" s="21">
         <f t="shared" si="6"/>
-        <v>21145.165773355904</v>
+        <v>20530.274928150131</v>
       </c>
       <c r="M16" s="114"/>
       <c r="N16" s="114"/>
@@ -27194,31 +27194,31 @@
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C19" s="220" t="s">
+      <c r="C19" s="212" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="220"/>
-      <c r="E19" s="220"/>
-      <c r="F19" s="220"/>
-      <c r="G19" s="220"/>
-      <c r="H19" s="220"/>
-      <c r="I19" s="220"/>
-      <c r="J19" s="220"/>
-      <c r="K19" s="220"/>
-      <c r="L19" s="220"/>
-      <c r="P19" s="217" t="s">
+      <c r="D19" s="212"/>
+      <c r="E19" s="212"/>
+      <c r="F19" s="212"/>
+      <c r="G19" s="212"/>
+      <c r="H19" s="212"/>
+      <c r="I19" s="212"/>
+      <c r="J19" s="212"/>
+      <c r="K19" s="212"/>
+      <c r="L19" s="212"/>
+      <c r="P19" s="221" t="s">
         <v>122</v>
       </c>
-      <c r="Q19" s="217"/>
-      <c r="R19" s="217"/>
-      <c r="S19" s="217"/>
-      <c r="T19" s="217"/>
-      <c r="U19" s="217"/>
-      <c r="V19" s="217"/>
-      <c r="W19" s="217"/>
-      <c r="X19" s="217"/>
-      <c r="Y19" s="217"/>
-      <c r="Z19" s="217"/>
+      <c r="Q19" s="221"/>
+      <c r="R19" s="221"/>
+      <c r="S19" s="221"/>
+      <c r="T19" s="221"/>
+      <c r="U19" s="221"/>
+      <c r="V19" s="221"/>
+      <c r="W19" s="221"/>
+      <c r="X19" s="221"/>
+      <c r="Y19" s="221"/>
+      <c r="Z19" s="221"/>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
@@ -27630,19 +27630,19 @@
       </c>
       <c r="I25" s="110">
         <f t="shared" ref="I25:L25" si="17">I15/H$6</f>
-        <v>4.5050621376784838E-3</v>
+        <v>4.5745545133515867E-3</v>
       </c>
       <c r="J25" s="110">
         <f t="shared" si="17"/>
-        <v>2.4827406924168567E-3</v>
+        <v>2.543875020950727E-3</v>
       </c>
       <c r="K25" s="110">
         <f t="shared" si="17"/>
-        <v>2.1240955895851727E-3</v>
+        <v>2.1763648895911335E-3</v>
       </c>
       <c r="L25" s="110">
         <f t="shared" si="17"/>
-        <v>1.8094188098596482E-3</v>
+        <v>1.863851077590089E-3</v>
       </c>
     </row>
   </sheetData>
@@ -27696,60 +27696,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="215" t="s">
+      <c r="C3" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="215"/>
-      <c r="E3" s="215"/>
-      <c r="F3" s="215"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="219" t="s">
+      <c r="D3" s="213"/>
+      <c r="E3" s="213"/>
+      <c r="F3" s="213"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="215"/>
-      <c r="K3" s="215"/>
-      <c r="L3" s="215"/>
-      <c r="P3" s="221"/>
-      <c r="Q3" s="221"/>
-      <c r="R3" s="221"/>
-      <c r="S3" s="221"/>
-      <c r="T3" s="221"/>
-      <c r="U3" s="221"/>
-      <c r="V3" s="221"/>
-      <c r="W3" s="221"/>
-      <c r="X3" s="221"/>
-      <c r="Y3" s="221"/>
-      <c r="Z3" s="221"/>
+      <c r="I3" s="213"/>
+      <c r="J3" s="213"/>
+      <c r="K3" s="213"/>
+      <c r="L3" s="213"/>
+      <c r="P3" s="216"/>
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="216"/>
+      <c r="T3" s="216"/>
+      <c r="U3" s="216"/>
+      <c r="V3" s="216"/>
+      <c r="W3" s="216"/>
+      <c r="X3" s="216"/>
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
       <c r="AB3" s="121"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="104"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="220" t="s">
+      <c r="C5" s="212" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="220"/>
-      <c r="E5" s="220"/>
-      <c r="F5" s="220"/>
-      <c r="G5" s="220"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="220"/>
-      <c r="J5" s="220"/>
-      <c r="K5" s="220"/>
-      <c r="L5" s="220"/>
-      <c r="P5" s="221"/>
-      <c r="Q5" s="221"/>
-      <c r="R5" s="221"/>
-      <c r="S5" s="221"/>
-      <c r="T5" s="221"/>
-      <c r="U5" s="221"/>
-      <c r="V5" s="221"/>
-      <c r="W5" s="221"/>
-      <c r="X5" s="221"/>
-      <c r="Y5" s="221"/>
-      <c r="Z5" s="221"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="216"/>
+      <c r="R5" s="216"/>
+      <c r="S5" s="216"/>
+      <c r="T5" s="216"/>
+      <c r="U5" s="216"/>
+      <c r="V5" s="216"/>
+      <c r="W5" s="216"/>
+      <c r="X5" s="216"/>
+      <c r="Y5" s="216"/>
+      <c r="Z5" s="216"/>
       <c r="AB5" s="122"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -27836,23 +27836,23 @@
       </c>
       <c r="H7" s="106">
         <f>Revenue!H9</f>
-        <v>26414.730000000003</v>
+        <v>26013.462</v>
       </c>
       <c r="I7" s="106">
         <f>Revenue!I9</f>
-        <v>29402.990100000006</v>
+        <v>28696.378320000003</v>
       </c>
       <c r="J7" s="106">
         <f>Revenue!J9</f>
-        <v>32484.413761000007</v>
+        <v>31704.242395200006</v>
       </c>
       <c r="K7" s="106">
         <f>Revenue!K9</f>
-        <v>35923.13711221001</v>
+        <v>34874.030860900813</v>
       </c>
       <c r="L7" s="106">
         <f>Revenue!L9</f>
-        <v>39402.179015618509</v>
+        <v>38252.850332990893</v>
       </c>
       <c r="N7" s="90"/>
       <c r="O7" s="7"/>
@@ -27895,23 +27895,23 @@
       </c>
       <c r="H8" s="131">
         <f>'COGS &amp; OpEx'!H11</f>
-        <v>2773.5466500000002</v>
+        <v>2731.4135099999999</v>
       </c>
       <c r="I8" s="131">
         <f>'COGS &amp; OpEx'!I11</f>
-        <v>3028.5079803000003</v>
+        <v>2955.72696696</v>
       </c>
       <c r="J8" s="131">
         <f>'COGS &amp; OpEx'!J11</f>
-        <v>3280.9257898610008</v>
+        <v>3202.1284819152011</v>
       </c>
       <c r="K8" s="131">
         <f>'COGS &amp; OpEx'!K11</f>
-        <v>3592.3137112210011</v>
+        <v>3487.4030860900816</v>
       </c>
       <c r="L8" s="131">
         <f>'COGS &amp; OpEx'!L11</f>
-        <v>3940.2179015618512</v>
+        <v>3825.2850332990893</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -27935,30 +27935,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="220" t="s">
+      <c r="C11" s="212" t="s">
         <v>126</v>
       </c>
-      <c r="D11" s="220"/>
-      <c r="E11" s="220"/>
-      <c r="F11" s="220"/>
-      <c r="G11" s="220"/>
-      <c r="H11" s="220"/>
-      <c r="I11" s="220"/>
-      <c r="J11" s="220"/>
-      <c r="K11" s="220"/>
-      <c r="L11" s="220"/>
+      <c r="D11" s="212"/>
+      <c r="E11" s="212"/>
+      <c r="F11" s="212"/>
+      <c r="G11" s="212"/>
+      <c r="H11" s="212"/>
+      <c r="I11" s="212"/>
+      <c r="J11" s="212"/>
+      <c r="K11" s="212"/>
+      <c r="L11" s="212"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="221"/>
-      <c r="Q11" s="221"/>
-      <c r="R11" s="221"/>
-      <c r="S11" s="221"/>
-      <c r="T11" s="221"/>
-      <c r="U11" s="221"/>
-      <c r="V11" s="221"/>
-      <c r="W11" s="221"/>
-      <c r="X11" s="221"/>
-      <c r="Y11" s="221"/>
-      <c r="Z11" s="221"/>
+      <c r="P11" s="216"/>
+      <c r="Q11" s="216"/>
+      <c r="R11" s="216"/>
+      <c r="S11" s="216"/>
+      <c r="T11" s="216"/>
+      <c r="U11" s="216"/>
+      <c r="V11" s="216"/>
+      <c r="W11" s="216"/>
+      <c r="X11" s="216"/>
+      <c r="Y11" s="216"/>
+      <c r="Z11" s="216"/>
       <c r="AB11" s="122"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -28046,23 +28046,23 @@
       </c>
       <c r="H13" s="33">
         <f>H20*H7/365</f>
-        <v>2750.0266849315071</v>
+        <v>2708.2508383561644</v>
       </c>
       <c r="I13" s="33">
         <f>I20*I7/365</f>
-        <v>3061.1332158904115</v>
+        <v>2987.5681538630142</v>
       </c>
       <c r="J13" s="33">
         <f>J20*J7/365</f>
-        <v>3381.938966898631</v>
+        <v>3300.7156466235624</v>
       </c>
       <c r="K13" s="33">
         <f>K20*K7/365</f>
-        <v>3739.9430418191241</v>
+        <v>3630.7210211348788</v>
       </c>
       <c r="L13" s="33">
         <f>L20*L7/365</f>
-        <v>4102.1446646397353</v>
+        <v>3982.4885278182301</v>
       </c>
       <c r="N13" s="90"/>
       <c r="O13" s="7"/>
@@ -28154,23 +28154,23 @@
       </c>
       <c r="H15" s="20">
         <f>H22*H8/365</f>
-        <v>433.12920287671238</v>
+        <v>426.54950704109586</v>
       </c>
       <c r="I15" s="20">
         <f>I22*I8/365</f>
-        <v>472.94508185506851</v>
+        <v>461.57927977183567</v>
       </c>
       <c r="J15" s="20">
         <f>J22*J8/365</f>
-        <v>512.36375348514264</v>
+        <v>500.05842046346976</v>
       </c>
       <c r="K15" s="20">
         <f>K22*K8/365</f>
-        <v>560.99145627286862</v>
+        <v>544.60815317023196</v>
       </c>
       <c r="L15" s="20">
         <f>L22*L8/365</f>
-        <v>615.32169969596032</v>
+        <v>597.37327917273444</v>
       </c>
       <c r="N15" s="90"/>
       <c r="P15" s="125"/>
@@ -28190,18 +28190,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="220" t="s">
+      <c r="C18" s="212" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="220"/>
-      <c r="E18" s="220"/>
-      <c r="F18" s="220"/>
-      <c r="G18" s="220"/>
-      <c r="H18" s="220"/>
-      <c r="I18" s="220"/>
-      <c r="J18" s="220"/>
-      <c r="K18" s="220"/>
-      <c r="L18" s="220"/>
+      <c r="D18" s="212"/>
+      <c r="E18" s="212"/>
+      <c r="F18" s="212"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="212"/>
+      <c r="I18" s="212"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="212"/>
+      <c r="L18" s="212"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -28414,23 +28414,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="221"/>
-      <c r="C25" s="221"/>
+      <c r="B25" s="216"/>
+      <c r="C25" s="216"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="121"/>
-      <c r="C26" s="220" t="s">
+      <c r="C26" s="212" t="s">
         <v>237</v>
       </c>
-      <c r="D26" s="220"/>
-      <c r="E26" s="220"/>
-      <c r="F26" s="220"/>
-      <c r="G26" s="220"/>
-      <c r="H26" s="220"/>
-      <c r="I26" s="220"/>
-      <c r="J26" s="220"/>
-      <c r="K26" s="220"/>
-      <c r="L26" s="220"/>
+      <c r="D26" s="212"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="212"/>
+      <c r="G26" s="212"/>
+      <c r="H26" s="212"/>
+      <c r="I26" s="212"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="212"/>
+      <c r="L26" s="212"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -28503,23 +28503,23 @@
       </c>
       <c r="H28" s="33">
         <f>-(H13-G13)</f>
-        <v>-406.02668493150713</v>
+        <v>-364.25083835616442</v>
       </c>
       <c r="I28" s="33">
         <f t="shared" ref="I28:L28" si="5">-(I13-H13)</f>
-        <v>-311.10653095890439</v>
+        <v>-279.31731550684981</v>
       </c>
       <c r="J28" s="33">
         <f t="shared" si="5"/>
-        <v>-320.80575100821943</v>
+        <v>-313.14749276054818</v>
       </c>
       <c r="K28" s="33">
         <f t="shared" si="5"/>
-        <v>-358.00407492049317</v>
+        <v>-330.0053745113164</v>
       </c>
       <c r="L28" s="33">
         <f t="shared" si="5"/>
-        <v>-362.20162282061119</v>
+        <v>-351.76750668335126</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
@@ -28588,23 +28588,23 @@
       </c>
       <c r="H30" s="20">
         <f>H15-G15</f>
-        <v>16.129202876712384</v>
+        <v>9.5495070410958647</v>
       </c>
       <c r="I30" s="20">
         <f t="shared" ref="I30:L30" si="7">I15-H15</f>
-        <v>39.815878978356125</v>
+        <v>35.029772730739808</v>
       </c>
       <c r="J30" s="20">
         <f t="shared" si="7"/>
-        <v>39.41867163007413</v>
+        <v>38.479140691634086</v>
       </c>
       <c r="K30" s="20">
         <f t="shared" si="7"/>
-        <v>48.62770278772598</v>
+        <v>44.5497327067622</v>
       </c>
       <c r="L30" s="20">
         <f t="shared" si="7"/>
-        <v>54.330243423091702</v>
+        <v>52.765126002502484</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
@@ -28617,18 +28617,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="121"/>
-      <c r="C33" s="220" t="s">
+      <c r="C33" s="212" t="s">
         <v>240</v>
       </c>
-      <c r="D33" s="220"/>
-      <c r="E33" s="220"/>
-      <c r="F33" s="220"/>
-      <c r="G33" s="220"/>
-      <c r="H33" s="220"/>
-      <c r="I33" s="220"/>
-      <c r="J33" s="220"/>
-      <c r="K33" s="220"/>
-      <c r="L33" s="220"/>
+      <c r="D33" s="212"/>
+      <c r="E33" s="212"/>
+      <c r="F33" s="212"/>
+      <c r="G33" s="212"/>
+      <c r="H33" s="212"/>
+      <c r="I33" s="212"/>
+      <c r="J33" s="212"/>
+      <c r="K33" s="212"/>
+      <c r="L33" s="212"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -28701,23 +28701,23 @@
       </c>
       <c r="H35" s="33">
         <f>H36+H28+H29+H30</f>
-        <v>138.39711794520531</v>
+        <v>165.56790868493141</v>
       </c>
       <c r="I35" s="33">
         <f t="shared" ref="I35:L35" si="9">I36+I28+I29+I30</f>
-        <v>316.76915001945184</v>
+        <v>329.64002362389004</v>
       </c>
       <c r="J35" s="33">
         <f t="shared" si="9"/>
-        <v>368.30119584185485</v>
+        <v>359.4164958350861</v>
       </c>
       <c r="K35" s="33">
         <f t="shared" si="9"/>
-        <v>409.08637011143298</v>
+        <v>412.02497541346207</v>
       </c>
       <c r="L35" s="33">
         <f t="shared" si="9"/>
-        <v>480.17220091485069</v>
+        <v>466.05462597896906</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
@@ -28746,23 +28746,23 @@
       </c>
       <c r="H36" s="20">
         <f>H7*H37</f>
-        <v>528.29460000000006</v>
+        <v>520.26923999999997</v>
       </c>
       <c r="I36" s="20">
         <f>I7*I37</f>
-        <v>588.0598020000001</v>
+        <v>573.92756640000005</v>
       </c>
       <c r="J36" s="20">
         <f>J7*J37</f>
-        <v>649.68827522000015</v>
+        <v>634.08484790400018</v>
       </c>
       <c r="K36" s="20">
         <f>K7*K37</f>
-        <v>718.46274224420017</v>
+        <v>697.48061721801628</v>
       </c>
       <c r="L36" s="20">
         <f>L7*L37</f>
-        <v>788.04358031237018</v>
+        <v>765.05700665981783</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
@@ -28812,18 +28812,18 @@
       <c r="C39" s="130"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="220" t="s">
+      <c r="C40" s="212" t="s">
         <v>243</v>
       </c>
-      <c r="D40" s="220"/>
-      <c r="E40" s="220"/>
-      <c r="F40" s="220"/>
-      <c r="G40" s="220"/>
-      <c r="H40" s="220"/>
-      <c r="I40" s="220"/>
-      <c r="J40" s="220"/>
-      <c r="K40" s="220"/>
-      <c r="L40" s="220"/>
+      <c r="D40" s="212"/>
+      <c r="E40" s="212"/>
+      <c r="F40" s="212"/>
+      <c r="G40" s="212"/>
+      <c r="H40" s="212"/>
+      <c r="I40" s="212"/>
+      <c r="J40" s="212"/>
+      <c r="K40" s="212"/>
+      <c r="L40" s="212"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -28896,23 +28896,23 @@
       </c>
       <c r="H42" s="33">
         <f>H7*H43</f>
-        <v>792.44190000000003</v>
+        <v>780.40386000000001</v>
       </c>
       <c r="I42" s="33">
         <f>I7*I43</f>
-        <v>882.08970300000021</v>
+        <v>860.89134960000013</v>
       </c>
       <c r="J42" s="33">
         <f>J7*J43</f>
-        <v>974.53241283000023</v>
+        <v>951.12727185600011</v>
       </c>
       <c r="K42" s="33">
         <f>K7*K43</f>
-        <v>1077.6941133663004</v>
+        <v>1046.2209258270243</v>
       </c>
       <c r="L42" s="33">
         <f>L7*L43</f>
-        <v>1182.0653704685553</v>
+        <v>1147.5855099897267</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -29026,23 +29026,23 @@
       </c>
       <c r="H45" s="33">
         <f>H7*H46</f>
-        <v>396.22095000000002</v>
+        <v>390.20193</v>
       </c>
       <c r="I45" s="33">
         <f>I7*I46</f>
-        <v>441.04485150000011</v>
+        <v>430.44567480000006</v>
       </c>
       <c r="J45" s="33">
         <f>J7*J46</f>
-        <v>487.26620641500011</v>
+        <v>475.56363592800005</v>
       </c>
       <c r="K45" s="33">
         <f>K7*K46</f>
-        <v>538.84705668315019</v>
+        <v>523.11046291351215</v>
       </c>
       <c r="L45" s="33">
         <f>L7*L46</f>
-        <v>591.03268523427766</v>
+        <v>573.79275499486334</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
@@ -29087,6 +29087,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -29094,12 +29100,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7353C5E3-6E60-E24A-8F15-C80C197CC5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED36E65-99B9-CA43-97BF-0427E7EC6B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2182,21 +2182,6 @@
     <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2206,10 +2191,25 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2322,15 +2322,15 @@
       <sheetData sheetId="0">
         <row r="10">
           <cell r="C10">
-            <v>43.9</v>
+            <v>44.16</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>250.71</v>
+            <v>250.17</v>
           </cell>
           <cell r="F18">
-            <v>1.4171</v>
+            <v>1.4159999999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -2881,8 +2881,8 @@
         <v>73</v>
       </c>
       <c r="C3" s="34">
-        <f ca="1">[1]Sheet1!$C$18</f>
-        <v>250.71</v>
+        <f>[1]Sheet1!$C$18</f>
+        <v>250.17</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2915,8 +2915,8 @@
         <v>107</v>
       </c>
       <c r="C11" s="92">
-        <f ca="1">$C$3/'Statement Q'!$N$24</f>
-        <v>14.617213859600446</v>
+        <f>$C$3/'Statement Q'!$N$24</f>
+        <v>14.585730091564928</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2924,8 +2924,8 @@
         <v>181</v>
       </c>
       <c r="C12" s="92">
-        <f ca="1">$C$3/Statements!W24</f>
-        <v>14.617213859600446</v>
+        <f>$C$3/Statements!W24</f>
+        <v>14.585730091564928</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2933,8 +2933,8 @@
         <v>108</v>
       </c>
       <c r="C13" s="97">
-        <f ca="1">$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
-        <v>4.3087096675254566</v>
+        <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
+        <v>4.2994292111397368</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2942,8 +2942,8 @@
         <v>140</v>
       </c>
       <c r="C15" s="20">
-        <f ca="1">C3*'Statement Q'!N116</f>
-        <v>101286.84</v>
+        <f>C3*'Statement Q'!N116</f>
+        <v>101068.68</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2969,8 +2969,8 @@
         <v>142</v>
       </c>
       <c r="C18" s="20">
-        <f ca="1">C15+C17-C16</f>
-        <v>100624.84</v>
+        <f>C15+C17-C16</f>
+        <v>100406.68</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3192,60 +3192,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215" t="s">
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="216"/>
-      <c r="U2" s="216"/>
-      <c r="V2" s="216"/>
-      <c r="W2" s="216"/>
-      <c r="X2" s="216"/>
-      <c r="Y2" s="216"/>
-      <c r="Z2" s="216"/>
-      <c r="AA2" s="216"/>
-      <c r="AB2" s="216"/>
-      <c r="AC2" s="216"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
+      <c r="S2" s="221"/>
+      <c r="T2" s="221"/>
+      <c r="U2" s="221"/>
+      <c r="V2" s="221"/>
+      <c r="W2" s="221"/>
+      <c r="X2" s="221"/>
+      <c r="Y2" s="221"/>
+      <c r="Z2" s="221"/>
+      <c r="AA2" s="221"/>
+      <c r="AB2" s="221"/>
+      <c r="AC2" s="221"/>
       <c r="AE2" s="121"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="91"/>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="220" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="216"/>
-      <c r="Y4" s="216"/>
-      <c r="Z4" s="216"/>
-      <c r="AA4" s="216"/>
-      <c r="AB4" s="216"/>
-      <c r="AC4" s="216"/>
+      <c r="D4" s="220"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="220"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="221"/>
+      <c r="Y4" s="221"/>
+      <c r="Z4" s="221"/>
+      <c r="AA4" s="221"/>
+      <c r="AB4" s="221"/>
+      <c r="AC4" s="221"/>
       <c r="AE4" s="122"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3856,18 +3856,18 @@
       <c r="AE14" s="103"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="212" t="s">
+      <c r="C17" s="220" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="212"/>
-      <c r="E17" s="212"/>
-      <c r="F17" s="212"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="212"/>
-      <c r="I17" s="212"/>
-      <c r="J17" s="212"/>
-      <c r="K17" s="212"/>
-      <c r="L17" s="212"/>
+      <c r="D17" s="220"/>
+      <c r="E17" s="220"/>
+      <c r="F17" s="220"/>
+      <c r="G17" s="220"/>
+      <c r="H17" s="220"/>
+      <c r="I17" s="220"/>
+      <c r="J17" s="220"/>
+      <c r="K17" s="220"/>
+      <c r="L17" s="220"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C18" s="61">
@@ -3952,18 +3952,18 @@
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="212" t="s">
+      <c r="C22" s="220" t="s">
         <v>249</v>
       </c>
-      <c r="D22" s="212"/>
-      <c r="E22" s="212"/>
-      <c r="F22" s="212"/>
-      <c r="G22" s="212"/>
-      <c r="H22" s="212"/>
-      <c r="I22" s="212"/>
-      <c r="J22" s="212"/>
-      <c r="K22" s="212"/>
-      <c r="L22" s="212"/>
+      <c r="D22" s="220"/>
+      <c r="E22" s="220"/>
+      <c r="F22" s="220"/>
+      <c r="G22" s="220"/>
+      <c r="H22" s="220"/>
+      <c r="I22" s="220"/>
+      <c r="J22" s="220"/>
+      <c r="K22" s="220"/>
+      <c r="L22" s="220"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
@@ -4155,18 +4155,18 @@
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C29" s="212" t="s">
+      <c r="C29" s="220" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="212"/>
-      <c r="E29" s="212"/>
-      <c r="F29" s="212"/>
-      <c r="G29" s="212"/>
-      <c r="H29" s="212"/>
-      <c r="I29" s="212"/>
-      <c r="J29" s="212"/>
-      <c r="K29" s="212"/>
-      <c r="L29" s="212"/>
+      <c r="D29" s="220"/>
+      <c r="E29" s="220"/>
+      <c r="F29" s="220"/>
+      <c r="G29" s="220"/>
+      <c r="H29" s="220"/>
+      <c r="I29" s="220"/>
+      <c r="J29" s="220"/>
+      <c r="K29" s="220"/>
+      <c r="L29" s="220"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
@@ -4373,10 +4373,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="215" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="213"/>
+      <c r="C4" s="215"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4392,8 +4392,8 @@
         <v>73</v>
       </c>
       <c r="C6" s="144">
-        <f ca="1">Overview!C3</f>
-        <v>250.71</v>
+        <f>Overview!C3</f>
+        <v>250.17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4401,8 +4401,8 @@
         <v>138</v>
       </c>
       <c r="C7" s="146">
-        <f ca="1">C5*C6</f>
-        <v>101286.84</v>
+        <f>C5*C6</f>
+        <v>101068.68</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4419,8 +4419,8 @@
         <v>153</v>
       </c>
       <c r="C9" s="169">
-        <f ca="1">[1]Sheet1!$C$10/1000</f>
-        <v>4.3900000000000002E-2</v>
+        <f>[1]Sheet1!$C$10/1000</f>
+        <v>4.4159999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4428,8 +4428,8 @@
         <v>154</v>
       </c>
       <c r="C10" s="144">
-        <f ca="1">[1]Sheet1!$F$18</f>
-        <v>1.4171</v>
+        <f>[1]Sheet1!$F$18</f>
+        <v>1.4159999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4458,18 +4458,18 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="213" t="s">
+      <c r="B15" s="215" t="s">
         <v>157</v>
       </c>
-      <c r="C15" s="213"/>
+      <c r="C15" s="215"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C16" s="147">
-        <f ca="1">C8/(C8+C7)</f>
-        <v>5.7926887116234373E-2</v>
+        <f>C8/(C8+C7)</f>
+        <v>5.8044666433295047E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4477,8 +4477,8 @@
         <v>149</v>
       </c>
       <c r="C17" s="147">
-        <f ca="1">C7/(C8+C7)</f>
-        <v>0.94207311288376561</v>
+        <f>C7/(C8+C7)</f>
+        <v>0.94195533356670491</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4495,8 +4495,8 @@
         <v>150</v>
       </c>
       <c r="C19" s="147">
-        <f ca="1">C9+C10*C11</f>
-        <v>0.114755</v>
+        <f>C9+C10*C11</f>
+        <v>0.11496000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4504,8 +4504,8 @@
         <v>147</v>
       </c>
       <c r="C20" s="147">
-        <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11057876107335507</v>
+        <f>(C17*C19)+(C16*C18)</f>
+        <v>0.11076337061687277</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4552,60 +4552,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="213" t="s">
+      <c r="C3" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="213"/>
-      <c r="E3" s="213"/>
-      <c r="F3" s="213"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="215" t="s">
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="218"/>
+      <c r="H3" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="213"/>
-      <c r="J3" s="213"/>
-      <c r="K3" s="213"/>
-      <c r="L3" s="213"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="215"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="215"/>
+      <c r="P3" s="221"/>
+      <c r="Q3" s="221"/>
+      <c r="R3" s="221"/>
+      <c r="S3" s="221"/>
+      <c r="T3" s="221"/>
+      <c r="U3" s="221"/>
+      <c r="V3" s="221"/>
+      <c r="W3" s="221"/>
+      <c r="X3" s="221"/>
+      <c r="Y3" s="221"/>
+      <c r="Z3" s="221"/>
       <c r="AB3" s="121"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="104"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="212" t="s">
+      <c r="C5" s="220" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="216"/>
-      <c r="R5" s="216"/>
-      <c r="S5" s="216"/>
-      <c r="T5" s="216"/>
-      <c r="U5" s="216"/>
-      <c r="V5" s="216"/>
-      <c r="W5" s="216"/>
-      <c r="X5" s="216"/>
-      <c r="Y5" s="216"/>
-      <c r="Z5" s="216"/>
+      <c r="D5" s="220"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="220"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="220"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
+      <c r="L5" s="220"/>
+      <c r="P5" s="221"/>
+      <c r="Q5" s="221"/>
+      <c r="R5" s="221"/>
+      <c r="S5" s="221"/>
+      <c r="T5" s="221"/>
+      <c r="U5" s="221"/>
+      <c r="V5" s="221"/>
+      <c r="W5" s="221"/>
+      <c r="X5" s="221"/>
+      <c r="Y5" s="221"/>
+      <c r="Z5" s="221"/>
       <c r="AB5" s="122"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4757,8 +4757,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="132">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>143951.30625102756</v>
+        <f>L7*(1+C14)/(C15-C14)</f>
+        <v>143641.44453798345</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -4811,24 +4811,24 @@
       <c r="F10" s="129"/>
       <c r="G10" s="149"/>
       <c r="H10" s="132">
-        <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7140.0263397088102</v>
+        <f>H7/(1+$C$15)^H9</f>
+        <v>7138.839663015875</v>
       </c>
       <c r="I10" s="132">
-        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7267.2727369910053</v>
+        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
+        <v>7264.8572874901329</v>
       </c>
       <c r="J10" s="132">
-        <f t="shared" ca="1" si="0"/>
-        <v>7259.8061612306137</v>
+        <f t="shared" si="0"/>
+        <v>7256.1870102873463</v>
       </c>
       <c r="K10" s="132">
-        <f t="shared" ca="1" si="0"/>
-        <v>7189.2399158161461</v>
+        <f t="shared" si="0"/>
+        <v>7184.4616831227731</v>
       </c>
       <c r="L10" s="132">
-        <f t="shared" ca="1" si="0"/>
-        <v>7113.9518473341886</v>
+        <f t="shared" si="0"/>
+        <v>7108.0420965862731</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -4846,15 +4846,15 @@
       <c r="J11" s="129"/>
       <c r="K11" s="129"/>
       <c r="L11" s="132">
-        <f ca="1">L8/(1+C15)^L9</f>
-        <v>85205.728057540706</v>
+        <f>L8/(1+C15)^L9</f>
+        <v>84951.688542515811</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="213" t="s">
+      <c r="B13" s="215" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="213"/>
+      <c r="C13" s="215"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4869,23 +4869,23 @@
         <v>147</v>
       </c>
       <c r="C15" s="148">
-        <f ca="1">WACC!C20</f>
-        <v>0.11057876107335507</v>
+        <f>WACC!C20</f>
+        <v>0.11076337061687277</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="213" t="s">
+      <c r="B18" s="215" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="213"/>
+      <c r="C18" s="215"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C19" s="103">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>35970.297001080762</v>
+        <f>SUM(H10:L10)</f>
+        <v>35952.387740502403</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4893,8 +4893,8 @@
         <v>164</v>
       </c>
       <c r="C20" s="103">
-        <f ca="1">L11</f>
-        <v>85205.728057540706</v>
+        <f>L11</f>
+        <v>84951.688542515811</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4902,8 +4902,8 @@
         <v>167</v>
       </c>
       <c r="C21" s="108">
-        <f ca="1">C19+C20</f>
-        <v>121176.02505862147</v>
+        <f>C19+C20</f>
+        <v>120904.07628301822</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4929,8 +4929,8 @@
         <v>168</v>
       </c>
       <c r="C24" s="108">
-        <f ca="1">C21+C22-C23</f>
-        <v>121838.02505862147</v>
+        <f>C21+C22-C23</f>
+        <v>121566.07628301822</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4947,8 +4947,8 @@
         <v>169</v>
       </c>
       <c r="C26" s="151">
-        <f ca="1">C24/C25</f>
-        <v>301.57926994708282</v>
+        <f>C24/C25</f>
+        <v>300.90612941341146</v>
       </c>
     </row>
   </sheetData>
@@ -4991,37 +4991,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215" t="s">
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="91"/>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="220" t="s">
         <v>253</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
+      <c r="D4" s="220"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="220"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5210,18 +5210,18 @@
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="212" t="s">
+      <c r="C10" s="220" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="212"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="212"/>
-      <c r="H10" s="212"/>
-      <c r="I10" s="212"/>
-      <c r="J10" s="212"/>
-      <c r="K10" s="212"/>
-      <c r="L10" s="212"/>
+      <c r="D10" s="220"/>
+      <c r="E10" s="220"/>
+      <c r="F10" s="220"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="220"/>
+      <c r="I10" s="220"/>
+      <c r="J10" s="220"/>
+      <c r="K10" s="220"/>
+      <c r="L10" s="220"/>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5403,18 +5403,18 @@
       <c r="N15" s="90"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="212" t="s">
+      <c r="C16" s="220" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-      <c r="F16" s="212"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="212"/>
-      <c r="I16" s="212"/>
-      <c r="J16" s="212"/>
-      <c r="K16" s="212"/>
-      <c r="L16" s="212"/>
+      <c r="D16" s="220"/>
+      <c r="E16" s="220"/>
+      <c r="F16" s="220"/>
+      <c r="G16" s="220"/>
+      <c r="H16" s="220"/>
+      <c r="I16" s="220"/>
+      <c r="J16" s="220"/>
+      <c r="K16" s="220"/>
+      <c r="L16" s="220"/>
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5548,18 +5548,18 @@
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="212" t="s">
+      <c r="C21" s="220" t="s">
         <v>254</v>
       </c>
-      <c r="D21" s="212"/>
-      <c r="E21" s="212"/>
-      <c r="F21" s="212"/>
-      <c r="G21" s="212"/>
-      <c r="H21" s="212"/>
-      <c r="I21" s="212"/>
-      <c r="J21" s="212"/>
-      <c r="K21" s="212"/>
-      <c r="L21" s="212"/>
+      <c r="D21" s="220"/>
+      <c r="E21" s="220"/>
+      <c r="F21" s="220"/>
+      <c r="G21" s="220"/>
+      <c r="H21" s="220"/>
+      <c r="I21" s="220"/>
+      <c r="J21" s="220"/>
+      <c r="K21" s="220"/>
+      <c r="L21" s="220"/>
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5643,18 +5643,18 @@
       <c r="N25" s="90"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="212" t="s">
+      <c r="C26" s="220" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="212"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="212"/>
-      <c r="G26" s="212"/>
-      <c r="H26" s="212"/>
-      <c r="I26" s="212"/>
-      <c r="J26" s="212"/>
-      <c r="K26" s="212"/>
-      <c r="L26" s="212"/>
+      <c r="D26" s="220"/>
+      <c r="E26" s="220"/>
+      <c r="F26" s="220"/>
+      <c r="G26" s="220"/>
+      <c r="H26" s="220"/>
+      <c r="I26" s="220"/>
+      <c r="J26" s="220"/>
+      <c r="K26" s="220"/>
+      <c r="L26" s="220"/>
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5924,10 +5924,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="213" t="s">
+      <c r="B37" s="215" t="s">
         <v>259</v>
       </c>
-      <c r="C37" s="213"/>
+      <c r="C37" s="215"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5944,8 +5944,8 @@
         <v>147</v>
       </c>
       <c r="C39" s="137">
-        <f ca="1">WACC!C20</f>
-        <v>0.11057876107335507</v>
+        <f>WACC!C20</f>
+        <v>0.11076337061687277</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5988,15 +5988,15 @@
         <v>262</v>
       </c>
       <c r="C44" s="151">
-        <f ca="1">C43/(1+C48)^5</f>
-        <v>558.68021955039728</v>
+        <f>C43/(1+C48)^5</f>
+        <v>558.2161088962647</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="213" t="s">
+      <c r="B46" s="215" t="s">
         <v>184</v>
       </c>
-      <c r="C46" s="213"/>
+      <c r="C46" s="215"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6012,8 +6012,8 @@
         <v>147</v>
       </c>
       <c r="C48" s="137">
-        <f ca="1">WACC!C20</f>
-        <v>0.11057876107335507</v>
+        <f>WACC!C20</f>
+        <v>0.11076337061687277</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6047,15 +6047,15 @@
         <v>262</v>
       </c>
       <c r="C52" s="151">
-        <f ca="1">C51/(1+C48)^5</f>
-        <v>552.99152720484551</v>
+        <f>C51/(1+C48)^5</f>
+        <v>552.5321423001368</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="213" t="s">
+      <c r="B54" s="215" t="s">
         <v>263</v>
       </c>
-      <c r="C54" s="213"/>
+      <c r="C54" s="215"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6071,8 +6071,8 @@
         <v>147</v>
       </c>
       <c r="C56" s="137">
-        <f ca="1">WACC!C20</f>
-        <v>0.11057876107335507</v>
+        <f>WACC!C20</f>
+        <v>0.11076337061687277</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6115,8 +6115,8 @@
         <v>262</v>
       </c>
       <c r="C61" s="151">
-        <f ca="1">C60/(1+C56)^5</f>
-        <v>521.85352510078474</v>
+        <f>C60/(1+C56)^5</f>
+        <v>521.42000737021101</v>
       </c>
     </row>
   </sheetData>
@@ -6165,10 +6165,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="215" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="213"/>
+      <c r="C4" s="215"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6176,8 +6176,8 @@
         <v>189</v>
       </c>
       <c r="C5" s="166">
-        <f ca="1">DCF!C26</f>
-        <v>301.57926994708282</v>
+        <f>DCF!C26</f>
+        <v>300.90612941341146</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6185,8 +6185,8 @@
         <v>266</v>
       </c>
       <c r="C6" s="166">
-        <f ca="1">Multiples!C44</f>
-        <v>558.68021955039728</v>
+        <f>Multiples!C44</f>
+        <v>558.2161088962647</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6194,8 +6194,8 @@
         <v>190</v>
       </c>
       <c r="C7" s="166">
-        <f ca="1">Multiples!C52</f>
-        <v>552.99152720484551</v>
+        <f>Multiples!C52</f>
+        <v>552.5321423001368</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6203,8 +6203,8 @@
         <v>267</v>
       </c>
       <c r="C8" s="166">
-        <f ca="1">Multiples!C61</f>
-        <v>521.85352510078474</v>
+        <f>Multiples!C61</f>
+        <v>521.42000737021101</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6212,8 +6212,8 @@
         <v>188</v>
       </c>
       <c r="C9" s="151">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>483.77613545077759</v>
+        <f>AVERAGE(C5:C8)</f>
+        <v>483.26859699500596</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6221,8 +6221,8 @@
         <v>335</v>
       </c>
       <c r="C10" s="34">
-        <f ca="1">Overview!C3</f>
-        <v>250.71</v>
+        <f>Overview!C3</f>
+        <v>250.17</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6230,8 +6230,8 @@
         <v>336</v>
       </c>
       <c r="C11" s="88">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>0.92962440848301853</v>
+        <f>(C9-C10)/C10</f>
+        <v>0.93176079064238715</v>
       </c>
     </row>
   </sheetData>
@@ -6275,60 +6275,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="213" t="s">
+      <c r="C3" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="213"/>
-      <c r="E3" s="213"/>
-      <c r="F3" s="213"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="215" t="s">
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="218"/>
+      <c r="H3" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="213"/>
-      <c r="J3" s="213"/>
-      <c r="K3" s="213"/>
-      <c r="L3" s="213"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="215"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="215"/>
+      <c r="P3" s="221"/>
+      <c r="Q3" s="221"/>
+      <c r="R3" s="221"/>
+      <c r="S3" s="221"/>
+      <c r="T3" s="221"/>
+      <c r="U3" s="221"/>
+      <c r="V3" s="221"/>
+      <c r="W3" s="221"/>
+      <c r="X3" s="221"/>
+      <c r="Y3" s="221"/>
+      <c r="Z3" s="221"/>
       <c r="AB3" s="121"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="104"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="212" t="s">
+      <c r="C5" s="220" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="216"/>
-      <c r="R5" s="216"/>
-      <c r="S5" s="216"/>
-      <c r="T5" s="216"/>
-      <c r="U5" s="216"/>
-      <c r="V5" s="216"/>
-      <c r="W5" s="216"/>
-      <c r="X5" s="216"/>
-      <c r="Y5" s="216"/>
-      <c r="Z5" s="216"/>
+      <c r="D5" s="220"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="220"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="220"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
+      <c r="L5" s="220"/>
+      <c r="P5" s="221"/>
+      <c r="Q5" s="221"/>
+      <c r="R5" s="221"/>
+      <c r="S5" s="221"/>
+      <c r="T5" s="221"/>
+      <c r="U5" s="221"/>
+      <c r="V5" s="221"/>
+      <c r="W5" s="221"/>
+      <c r="X5" s="221"/>
+      <c r="Y5" s="221"/>
+      <c r="Z5" s="221"/>
       <c r="AB5" s="122"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -6462,8 +6462,8 @@
       <c r="J8" s="129"/>
       <c r="K8" s="129"/>
       <c r="L8" s="132">
-        <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>115955.10484495721</v>
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>115705.50622470703</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -6516,24 +6516,24 @@
       <c r="F10" s="129"/>
       <c r="G10" s="149"/>
       <c r="H10" s="132">
-        <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7745.2196732615921</v>
+        <f>H7/(1+$C$21)^H9</f>
+        <v>7743.9324130708546</v>
       </c>
       <c r="I10" s="132">
-        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7183.2602450899121</v>
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>7180.8727191222506</v>
       </c>
       <c r="J10" s="132">
-        <f t="shared" ca="1" si="1"/>
-        <v>6662.0741470797066</v>
+        <f t="shared" si="1"/>
+        <v>6658.7529768723971</v>
       </c>
       <c r="K10" s="132">
-        <f t="shared" ca="1" si="1"/>
-        <v>6178.7030438617039</v>
+        <f t="shared" si="1"/>
+        <v>6174.5964510601652</v>
       </c>
       <c r="L10" s="132">
-        <f t="shared" ca="1" si="1"/>
-        <v>5730.4032440047731</v>
+        <f t="shared" si="1"/>
+        <v>5725.6428442180068</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -6551,8 +6551,8 @@
       <c r="J11" s="129"/>
       <c r="K11" s="129"/>
       <c r="L11" s="132">
-        <f ca="1">L8/(1+C21)^L9</f>
-        <v>68634.591707517204</v>
+        <f>L8/(1+C21)^L9</f>
+        <v>68429.958770403697</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6567,8 +6567,8 @@
         <v>339</v>
       </c>
       <c r="C15" s="197">
-        <f ca="1">Overview!C3</f>
-        <v>250.71</v>
+        <f>Overview!C3</f>
+        <v>250.17</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6576,8 +6576,8 @@
         <v>340</v>
       </c>
       <c r="C16" s="197">
-        <f ca="1">C36</f>
-        <v>254.44616846736361</v>
+        <f>C36</f>
+        <v>253.90038657115684</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6615,8 +6615,8 @@
         <v>147</v>
       </c>
       <c r="C21" s="202">
-        <f ca="1">WACC!C20</f>
-        <v>0.11057876107335507</v>
+        <f>WACC!C20</f>
+        <v>0.11076337061687277</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6633,8 +6633,8 @@
         <v>140</v>
       </c>
       <c r="C23" s="203">
-        <f ca="1">C15*C22</f>
-        <v>101286.84</v>
+        <f>C15*C22</f>
+        <v>101068.68</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6660,8 +6660,8 @@
         <v>343</v>
       </c>
       <c r="C26" s="204">
-        <f ca="1">C23+C25-C24</f>
-        <v>100624.84</v>
+        <f>C23+C25-C24</f>
+        <v>100406.68</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6676,8 +6676,8 @@
         <v>170</v>
       </c>
       <c r="C29" s="203">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>33499.660353297688</v>
+        <f>SUM(H10:L10)</f>
+        <v>33483.797404343677</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6685,8 +6685,8 @@
         <v>164</v>
       </c>
       <c r="C30" s="203">
-        <f ca="1">L11</f>
-        <v>68634.591707517204</v>
+        <f>L11</f>
+        <v>68429.958770403697</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6694,8 +6694,8 @@
         <v>167</v>
       </c>
       <c r="C31" s="206">
-        <f ca="1">C29+C30</f>
-        <v>102134.25206081489</v>
+        <f>C29+C30</f>
+        <v>101913.75617474737</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6721,8 +6721,8 @@
         <v>168</v>
       </c>
       <c r="C34" s="206">
-        <f ca="1">C31+C32-C33</f>
-        <v>102796.25206081489</v>
+        <f>C31+C32-C33</f>
+        <v>102575.75617474737</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6739,23 +6739,23 @@
         <v>169</v>
       </c>
       <c r="C36" s="209">
-        <f ca="1">C34/C35</f>
-        <v>254.44616846736361</v>
+        <f>C34/C35</f>
+        <v>253.90038657115684</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="212" t="s">
+      <c r="C39" s="220" t="s">
         <v>344</v>
       </c>
-      <c r="D39" s="212"/>
-      <c r="E39" s="212"/>
-      <c r="F39" s="212"/>
-      <c r="G39" s="212"/>
-      <c r="H39" s="212"/>
-      <c r="I39" s="212"/>
-      <c r="J39" s="212"/>
-      <c r="K39" s="212"/>
-      <c r="L39" s="212"/>
+      <c r="D39" s="220"/>
+      <c r="E39" s="220"/>
+      <c r="F39" s="220"/>
+      <c r="G39" s="220"/>
+      <c r="H39" s="220"/>
+      <c r="I39" s="220"/>
+      <c r="J39" s="220"/>
+      <c r="K39" s="220"/>
+      <c r="L39" s="220"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="61">
@@ -7187,17 +7187,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13874,11 +13874,11 @@
         <v>74</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="217" t="s">
+      <c r="P4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="218"/>
-      <c r="R4" s="219"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="214"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -25290,36 +25290,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215" t="s">
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
       <c r="O2" s="89"/>
-      <c r="S2" s="213" t="s">
+      <c r="S2" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="T2" s="213"/>
-      <c r="U2" s="213"/>
-      <c r="V2" s="213"/>
-      <c r="W2" s="213"/>
-      <c r="X2" s="213"/>
-      <c r="Y2" s="213"/>
-      <c r="Z2" s="213"/>
-      <c r="AA2" s="213" t="s">
+      <c r="T2" s="215"/>
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="W2" s="215"/>
+      <c r="X2" s="215"/>
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="215"/>
+      <c r="AA2" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="AB2" s="213"/>
-      <c r="AC2" s="213"/>
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="215"/>
       <c r="AE2" s="116" t="s">
         <v>74</v>
       </c>
@@ -25330,32 +25330,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="91"/>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="220" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
+      <c r="D4" s="220"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="220"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
       <c r="O4" s="89"/>
-      <c r="S4" s="220" t="s">
+      <c r="S4" s="216" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="221"/>
-      <c r="Y4" s="221"/>
-      <c r="Z4" s="221"/>
-      <c r="AA4" s="221"/>
-      <c r="AB4" s="221"/>
-      <c r="AC4" s="221"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="217"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="217"/>
+      <c r="Y4" s="217"/>
+      <c r="Z4" s="217"/>
+      <c r="AA4" s="217"/>
+      <c r="AB4" s="217"/>
+      <c r="AC4" s="217"/>
       <c r="AE4" s="118" t="s">
         <v>334</v>
       </c>
@@ -25835,33 +25835,33 @@
       <c r="Q10" s="90"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="212" t="s">
+      <c r="C11" s="220" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="212"/>
-      <c r="E11" s="212"/>
-      <c r="F11" s="212"/>
-      <c r="G11" s="212"/>
-      <c r="H11" s="212"/>
-      <c r="I11" s="212"/>
-      <c r="J11" s="212"/>
-      <c r="K11" s="212"/>
-      <c r="L11" s="212"/>
+      <c r="D11" s="220"/>
+      <c r="E11" s="220"/>
+      <c r="F11" s="220"/>
+      <c r="G11" s="220"/>
+      <c r="H11" s="220"/>
+      <c r="I11" s="220"/>
+      <c r="J11" s="220"/>
+      <c r="K11" s="220"/>
+      <c r="L11" s="220"/>
       <c r="O11" s="89"/>
       <c r="Q11" s="90"/>
-      <c r="S11" s="220" t="s">
+      <c r="S11" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="T11" s="221"/>
-      <c r="U11" s="221"/>
-      <c r="V11" s="221"/>
-      <c r="W11" s="221"/>
-      <c r="X11" s="221"/>
-      <c r="Y11" s="221"/>
-      <c r="Z11" s="221"/>
-      <c r="AA11" s="221"/>
-      <c r="AB11" s="221"/>
-      <c r="AC11" s="221"/>
+      <c r="T11" s="217"/>
+      <c r="U11" s="217"/>
+      <c r="V11" s="217"/>
+      <c r="W11" s="217"/>
+      <c r="X11" s="217"/>
+      <c r="Y11" s="217"/>
+      <c r="Z11" s="217"/>
+      <c r="AA11" s="217"/>
+      <c r="AB11" s="217"/>
+      <c r="AC11" s="217"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
@@ -26318,35 +26318,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="213"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215" t="s">
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
-      <c r="P2" s="213" t="s">
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
+      <c r="P2" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="Q2" s="213"/>
-      <c r="R2" s="213"/>
-      <c r="S2" s="213"/>
-      <c r="T2" s="213"/>
-      <c r="U2" s="213"/>
-      <c r="V2" s="213"/>
-      <c r="W2" s="213"/>
-      <c r="X2" s="213" t="s">
+      <c r="Q2" s="215"/>
+      <c r="R2" s="215"/>
+      <c r="S2" s="215"/>
+      <c r="T2" s="215"/>
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="W2" s="215"/>
+      <c r="X2" s="215" t="s">
         <v>103</v>
       </c>
-      <c r="Y2" s="213"/>
-      <c r="Z2" s="213"/>
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="215"/>
       <c r="AB2" s="116" t="s">
         <v>74</v>
       </c>
@@ -26355,31 +26355,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="91"/>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="220" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
-      <c r="P4" s="221" t="s">
+      <c r="D4" s="220"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="220"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
+      <c r="P4" s="217" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="221"/>
-      <c r="Y4" s="221"/>
-      <c r="Z4" s="221"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="217"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="217"/>
+      <c r="Y4" s="217"/>
+      <c r="Z4" s="217"/>
       <c r="AB4" s="118" t="str">
         <f>Revenue!AE4</f>
         <v>Q3-Q4-Q1</v>
@@ -26582,32 +26582,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="212" t="s">
+      <c r="C9" s="220" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="212"/>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="212"/>
-      <c r="H9" s="212"/>
-      <c r="I9" s="212"/>
-      <c r="J9" s="212"/>
-      <c r="K9" s="212"/>
-      <c r="L9" s="212"/>
+      <c r="D9" s="220"/>
+      <c r="E9" s="220"/>
+      <c r="F9" s="220"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="220"/>
+      <c r="I9" s="220"/>
+      <c r="J9" s="220"/>
+      <c r="K9" s="220"/>
+      <c r="L9" s="220"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="221" t="s">
+      <c r="P9" s="217" t="s">
         <v>124</v>
       </c>
-      <c r="Q9" s="221"/>
-      <c r="R9" s="221"/>
-      <c r="S9" s="221"/>
-      <c r="T9" s="221"/>
-      <c r="U9" s="221"/>
-      <c r="V9" s="221"/>
-      <c r="W9" s="221"/>
-      <c r="X9" s="221"/>
-      <c r="Y9" s="221"/>
-      <c r="Z9" s="221"/>
+      <c r="Q9" s="217"/>
+      <c r="R9" s="217"/>
+      <c r="S9" s="217"/>
+      <c r="T9" s="217"/>
+      <c r="U9" s="217"/>
+      <c r="V9" s="217"/>
+      <c r="W9" s="217"/>
+      <c r="X9" s="217"/>
+      <c r="Y9" s="217"/>
+      <c r="Z9" s="217"/>
       <c r="AB9" s="118" t="str">
         <f>AB4</f>
         <v>Q3-Q4-Q1</v>
@@ -27194,31 +27194,31 @@
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C19" s="212" t="s">
+      <c r="C19" s="220" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="212"/>
-      <c r="E19" s="212"/>
-      <c r="F19" s="212"/>
-      <c r="G19" s="212"/>
-      <c r="H19" s="212"/>
-      <c r="I19" s="212"/>
-      <c r="J19" s="212"/>
-      <c r="K19" s="212"/>
-      <c r="L19" s="212"/>
-      <c r="P19" s="221" t="s">
+      <c r="D19" s="220"/>
+      <c r="E19" s="220"/>
+      <c r="F19" s="220"/>
+      <c r="G19" s="220"/>
+      <c r="H19" s="220"/>
+      <c r="I19" s="220"/>
+      <c r="J19" s="220"/>
+      <c r="K19" s="220"/>
+      <c r="L19" s="220"/>
+      <c r="P19" s="217" t="s">
         <v>122</v>
       </c>
-      <c r="Q19" s="221"/>
-      <c r="R19" s="221"/>
-      <c r="S19" s="221"/>
-      <c r="T19" s="221"/>
-      <c r="U19" s="221"/>
-      <c r="V19" s="221"/>
-      <c r="W19" s="221"/>
-      <c r="X19" s="221"/>
-      <c r="Y19" s="221"/>
-      <c r="Z19" s="221"/>
+      <c r="Q19" s="217"/>
+      <c r="R19" s="217"/>
+      <c r="S19" s="217"/>
+      <c r="T19" s="217"/>
+      <c r="U19" s="217"/>
+      <c r="V19" s="217"/>
+      <c r="W19" s="217"/>
+      <c r="X19" s="217"/>
+      <c r="Y19" s="217"/>
+      <c r="Z19" s="217"/>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
@@ -27696,60 +27696,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="213" t="s">
+      <c r="C3" s="215" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="213"/>
-      <c r="E3" s="213"/>
-      <c r="F3" s="213"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="215" t="s">
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="218"/>
+      <c r="H3" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="213"/>
-      <c r="J3" s="213"/>
-      <c r="K3" s="213"/>
-      <c r="L3" s="213"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="215"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="215"/>
+      <c r="P3" s="221"/>
+      <c r="Q3" s="221"/>
+      <c r="R3" s="221"/>
+      <c r="S3" s="221"/>
+      <c r="T3" s="221"/>
+      <c r="U3" s="221"/>
+      <c r="V3" s="221"/>
+      <c r="W3" s="221"/>
+      <c r="X3" s="221"/>
+      <c r="Y3" s="221"/>
+      <c r="Z3" s="221"/>
       <c r="AB3" s="121"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="104"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="212" t="s">
+      <c r="C5" s="220" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="216"/>
-      <c r="R5" s="216"/>
-      <c r="S5" s="216"/>
-      <c r="T5" s="216"/>
-      <c r="U5" s="216"/>
-      <c r="V5" s="216"/>
-      <c r="W5" s="216"/>
-      <c r="X5" s="216"/>
-      <c r="Y5" s="216"/>
-      <c r="Z5" s="216"/>
+      <c r="D5" s="220"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="220"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="220"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
+      <c r="L5" s="220"/>
+      <c r="P5" s="221"/>
+      <c r="Q5" s="221"/>
+      <c r="R5" s="221"/>
+      <c r="S5" s="221"/>
+      <c r="T5" s="221"/>
+      <c r="U5" s="221"/>
+      <c r="V5" s="221"/>
+      <c r="W5" s="221"/>
+      <c r="X5" s="221"/>
+      <c r="Y5" s="221"/>
+      <c r="Z5" s="221"/>
       <c r="AB5" s="122"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -27935,30 +27935,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="212" t="s">
+      <c r="C11" s="220" t="s">
         <v>126</v>
       </c>
-      <c r="D11" s="212"/>
-      <c r="E11" s="212"/>
-      <c r="F11" s="212"/>
-      <c r="G11" s="212"/>
-      <c r="H11" s="212"/>
-      <c r="I11" s="212"/>
-      <c r="J11" s="212"/>
-      <c r="K11" s="212"/>
-      <c r="L11" s="212"/>
+      <c r="D11" s="220"/>
+      <c r="E11" s="220"/>
+      <c r="F11" s="220"/>
+      <c r="G11" s="220"/>
+      <c r="H11" s="220"/>
+      <c r="I11" s="220"/>
+      <c r="J11" s="220"/>
+      <c r="K11" s="220"/>
+      <c r="L11" s="220"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="216"/>
-      <c r="Q11" s="216"/>
-      <c r="R11" s="216"/>
-      <c r="S11" s="216"/>
-      <c r="T11" s="216"/>
-      <c r="U11" s="216"/>
-      <c r="V11" s="216"/>
-      <c r="W11" s="216"/>
-      <c r="X11" s="216"/>
-      <c r="Y11" s="216"/>
-      <c r="Z11" s="216"/>
+      <c r="P11" s="221"/>
+      <c r="Q11" s="221"/>
+      <c r="R11" s="221"/>
+      <c r="S11" s="221"/>
+      <c r="T11" s="221"/>
+      <c r="U11" s="221"/>
+      <c r="V11" s="221"/>
+      <c r="W11" s="221"/>
+      <c r="X11" s="221"/>
+      <c r="Y11" s="221"/>
+      <c r="Z11" s="221"/>
       <c r="AB11" s="122"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -28190,18 +28190,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="212" t="s">
+      <c r="C18" s="220" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="212"/>
-      <c r="E18" s="212"/>
-      <c r="F18" s="212"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="212"/>
-      <c r="I18" s="212"/>
-      <c r="J18" s="212"/>
-      <c r="K18" s="212"/>
-      <c r="L18" s="212"/>
+      <c r="D18" s="220"/>
+      <c r="E18" s="220"/>
+      <c r="F18" s="220"/>
+      <c r="G18" s="220"/>
+      <c r="H18" s="220"/>
+      <c r="I18" s="220"/>
+      <c r="J18" s="220"/>
+      <c r="K18" s="220"/>
+      <c r="L18" s="220"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -28414,23 +28414,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="216"/>
-      <c r="C25" s="216"/>
+      <c r="B25" s="221"/>
+      <c r="C25" s="221"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="121"/>
-      <c r="C26" s="212" t="s">
+      <c r="C26" s="220" t="s">
         <v>237</v>
       </c>
-      <c r="D26" s="212"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="212"/>
-      <c r="G26" s="212"/>
-      <c r="H26" s="212"/>
-      <c r="I26" s="212"/>
-      <c r="J26" s="212"/>
-      <c r="K26" s="212"/>
-      <c r="L26" s="212"/>
+      <c r="D26" s="220"/>
+      <c r="E26" s="220"/>
+      <c r="F26" s="220"/>
+      <c r="G26" s="220"/>
+      <c r="H26" s="220"/>
+      <c r="I26" s="220"/>
+      <c r="J26" s="220"/>
+      <c r="K26" s="220"/>
+      <c r="L26" s="220"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -28617,18 +28617,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="121"/>
-      <c r="C33" s="212" t="s">
+      <c r="C33" s="220" t="s">
         <v>240</v>
       </c>
-      <c r="D33" s="212"/>
-      <c r="E33" s="212"/>
-      <c r="F33" s="212"/>
-      <c r="G33" s="212"/>
-      <c r="H33" s="212"/>
-      <c r="I33" s="212"/>
-      <c r="J33" s="212"/>
-      <c r="K33" s="212"/>
-      <c r="L33" s="212"/>
+      <c r="D33" s="220"/>
+      <c r="E33" s="220"/>
+      <c r="F33" s="220"/>
+      <c r="G33" s="220"/>
+      <c r="H33" s="220"/>
+      <c r="I33" s="220"/>
+      <c r="J33" s="220"/>
+      <c r="K33" s="220"/>
+      <c r="L33" s="220"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -28812,18 +28812,18 @@
       <c r="C39" s="130"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="212" t="s">
+      <c r="C40" s="220" t="s">
         <v>243</v>
       </c>
-      <c r="D40" s="212"/>
-      <c r="E40" s="212"/>
-      <c r="F40" s="212"/>
-      <c r="G40" s="212"/>
-      <c r="H40" s="212"/>
-      <c r="I40" s="212"/>
-      <c r="J40" s="212"/>
-      <c r="K40" s="212"/>
-      <c r="L40" s="212"/>
+      <c r="D40" s="220"/>
+      <c r="E40" s="220"/>
+      <c r="F40" s="220"/>
+      <c r="G40" s="220"/>
+      <c r="H40" s="220"/>
+      <c r="I40" s="220"/>
+      <c r="J40" s="220"/>
+      <c r="K40" s="220"/>
+      <c r="L40" s="220"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -29087,12 +29087,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -29100,6 +29094,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED36E65-99B9-CA43-97BF-0427E7EC6B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E069D2ED-9DC9-D347-9879-ADAA00F3316F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,6 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId17"/>
-    <externalReference r:id="rId18"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -2320,99 +2319,25 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="8">
+          <cell r="C8">
+            <v>218.965</v>
+          </cell>
+        </row>
         <row r="10">
           <cell r="C10">
-            <v>44.16</v>
+            <v>43.92</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>250.17</v>
+            <v>252.47</v>
           </cell>
           <cell r="F18">
-            <v>1.4159999999999999</v>
+            <v>1.4196</v>
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Financials -&gt;"/>
-      <sheetName val="Statement Y"/>
-      <sheetName val="Statement Q"/>
-      <sheetName val="Statements"/>
-      <sheetName val="Forecast -&gt;"/>
-      <sheetName val="Revenue"/>
-      <sheetName val="COGS &amp; OpEx"/>
-      <sheetName val="WC &amp; Investments"/>
-      <sheetName val="FCF &amp; Other"/>
-      <sheetName val="Valuation -&gt;"/>
-      <sheetName val="WACC"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Multiples"/>
-      <sheetName val="AVG target price"/>
-      <sheetName val="Reverse DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
-        <row r="5">
-          <cell r="C5">
-            <v>2021</v>
-          </cell>
-          <cell r="D5">
-            <v>2022</v>
-          </cell>
-          <cell r="E5">
-            <v>2023</v>
-          </cell>
-          <cell r="F5">
-            <v>2024</v>
-          </cell>
-          <cell r="G5">
-            <v>2025</v>
-          </cell>
-          <cell r="H5">
-            <v>2026</v>
-          </cell>
-          <cell r="I5">
-            <v>2027</v>
-          </cell>
-          <cell r="J5">
-            <v>2028</v>
-          </cell>
-          <cell r="K5">
-            <v>2029</v>
-          </cell>
-          <cell r="L5">
-            <v>2030</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2881,8 +2806,8 @@
         <v>73</v>
       </c>
       <c r="C3" s="34">
-        <f>[1]Sheet1!$C$18</f>
-        <v>250.17</v>
+        <f ca="1">[1]Sheet1!$C$18</f>
+        <v>252.47</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2915,8 +2840,8 @@
         <v>107</v>
       </c>
       <c r="C11" s="92">
-        <f>$C$3/'Statement Q'!$N$24</f>
-        <v>14.585730091564928</v>
+        <f ca="1">$C$3/'Statement Q'!$N$24</f>
+        <v>14.719827622086571</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2924,8 +2849,8 @@
         <v>181</v>
       </c>
       <c r="C12" s="92">
-        <f>$C$3/Statements!W24</f>
-        <v>14.585730091564928</v>
+        <f ca="1">$C$3/Statements!W24</f>
+        <v>14.719827622086571</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2933,8 +2858,8 @@
         <v>108</v>
       </c>
       <c r="C13" s="97">
-        <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
-        <v>4.2994292111397368</v>
+        <f ca="1">$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
+        <v>4.3389570809307649</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2942,8 +2867,8 @@
         <v>140</v>
       </c>
       <c r="C15" s="20">
-        <f>C3*'Statement Q'!N116</f>
-        <v>101068.68</v>
+        <f ca="1">C3*'Statement Q'!N116</f>
+        <v>101997.88</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2969,8 +2894,8 @@
         <v>142</v>
       </c>
       <c r="C18" s="20">
-        <f>C15+C17-C16</f>
-        <v>100406.68</v>
+        <f ca="1">C15+C17-C16</f>
+        <v>101335.88</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4392,8 +4317,8 @@
         <v>73</v>
       </c>
       <c r="C6" s="144">
-        <f>Overview!C3</f>
-        <v>250.17</v>
+        <f ca="1">Overview!C3</f>
+        <v>252.47</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4401,8 +4326,8 @@
         <v>138</v>
       </c>
       <c r="C7" s="146">
-        <f>C5*C6</f>
-        <v>101068.68</v>
+        <f ca="1">C5*C6</f>
+        <v>101997.88</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4419,8 +4344,8 @@
         <v>153</v>
       </c>
       <c r="C9" s="169">
-        <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.4159999999999998E-2</v>
+        <f ca="1">[1]Sheet1!$C$10/1000</f>
+        <v>4.3920000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4428,8 +4353,8 @@
         <v>154</v>
       </c>
       <c r="C10" s="144">
-        <f>[1]Sheet1!$F$18</f>
-        <v>1.4159999999999999</v>
+        <f ca="1">[1]Sheet1!$F$18</f>
+        <v>1.4196</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4468,8 +4393,8 @@
         <v>148</v>
       </c>
       <c r="C16" s="147">
-        <f>C8/(C8+C7)</f>
-        <v>5.8044666433295047E-2</v>
+        <f ca="1">C8/(C8+C7)</f>
+        <v>5.7546309625756797E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4477,8 +4402,8 @@
         <v>149</v>
       </c>
       <c r="C17" s="147">
-        <f>C7/(C8+C7)</f>
-        <v>0.94195533356670491</v>
+        <f ca="1">C7/(C8+C7)</f>
+        <v>0.9424536903742432</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4495,8 +4420,8 @@
         <v>150</v>
       </c>
       <c r="C19" s="147">
-        <f>C9+C10*C11</f>
-        <v>0.11496000000000001</v>
+        <f ca="1">C9+C10*C11</f>
+        <v>0.1149</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4504,8 +4429,8 @@
         <v>147</v>
       </c>
       <c r="C20" s="147">
-        <f>(C17*C19)+(C16*C18)</f>
-        <v>0.11076337061687277</v>
+        <f ca="1">(C17*C19)+(C16*C18)</f>
+        <v>0.11074285459263533</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4757,8 +4682,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="132">
-        <f>L7*(1+C14)/(C15-C14)</f>
-        <v>143641.44453798345</v>
+        <f ca="1">L7*(1+C14)/(C15-C14)</f>
+        <v>143675.81418163067</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -4811,24 +4736,24 @@
       <c r="F10" s="129"/>
       <c r="G10" s="149"/>
       <c r="H10" s="132">
-        <f>H7/(1+$C$15)^H9</f>
-        <v>7138.839663015875</v>
+        <f ca="1">H7/(1+$C$15)^H9</f>
+        <v>7138.971521264566</v>
       </c>
       <c r="I10" s="132">
-        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>7264.8572874901329</v>
+        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
+        <v>7265.1256616940354</v>
       </c>
       <c r="J10" s="132">
-        <f t="shared" si="0"/>
-        <v>7256.1870102873463</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7256.5890948679034</v>
       </c>
       <c r="K10" s="132">
-        <f t="shared" si="0"/>
-        <v>7184.4616831227731</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7184.9925014780983</v>
       </c>
       <c r="L10" s="132">
-        <f t="shared" si="0"/>
-        <v>7108.0420965862731</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7108.6985678410865</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -4846,8 +4771,8 @@
       <c r="J11" s="129"/>
       <c r="K11" s="129"/>
       <c r="L11" s="132">
-        <f>L8/(1+C15)^L9</f>
-        <v>84951.688542515811</v>
+        <f ca="1">L8/(1+C15)^L9</f>
+        <v>84979.862947821224</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -4869,8 +4794,8 @@
         <v>147</v>
       </c>
       <c r="C15" s="148">
-        <f>WACC!C20</f>
-        <v>0.11076337061687277</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11074285459263533</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -4884,8 +4809,8 @@
         <v>170</v>
       </c>
       <c r="C19" s="103">
-        <f>SUM(H10:L10)</f>
-        <v>35952.387740502403</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>35954.377347145688</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4893,8 +4818,8 @@
         <v>164</v>
       </c>
       <c r="C20" s="103">
-        <f>L11</f>
-        <v>84951.688542515811</v>
+        <f ca="1">L11</f>
+        <v>84979.862947821224</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4902,8 +4827,8 @@
         <v>167</v>
       </c>
       <c r="C21" s="108">
-        <f>C19+C20</f>
-        <v>120904.07628301822</v>
+        <f ca="1">C19+C20</f>
+        <v>120934.2402949669</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4929,8 +4854,8 @@
         <v>168</v>
       </c>
       <c r="C24" s="108">
-        <f>C21+C22-C23</f>
-        <v>121566.07628301822</v>
+        <f ca="1">C21+C22-C23</f>
+        <v>121596.2402949669</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4947,8 +4872,8 @@
         <v>169</v>
       </c>
       <c r="C26" s="151">
-        <f>C24/C25</f>
-        <v>300.90612941341146</v>
+        <f ca="1">C24/C25</f>
+        <v>300.98079280932404</v>
       </c>
     </row>
   </sheetData>
@@ -5944,8 +5869,8 @@
         <v>147</v>
       </c>
       <c r="C39" s="137">
-        <f>WACC!C20</f>
-        <v>0.11076337061687277</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11074285459263533</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5988,8 +5913,8 @@
         <v>262</v>
       </c>
       <c r="C44" s="151">
-        <f>C43/(1+C48)^5</f>
-        <v>558.2161088962647</v>
+        <f ca="1">C43/(1+C48)^5</f>
+        <v>558.2676635753852</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -6012,8 +5937,8 @@
         <v>147</v>
       </c>
       <c r="C48" s="137">
-        <f>WACC!C20</f>
-        <v>0.11076337061687277</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11074285459263533</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6047,8 +5972,8 @@
         <v>262</v>
       </c>
       <c r="C52" s="151">
-        <f>C51/(1+C48)^5</f>
-        <v>552.5321423001368</v>
+        <f ca="1">C51/(1+C48)^5</f>
+        <v>552.58317203010347</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -6071,8 +5996,8 @@
         <v>147</v>
       </c>
       <c r="C56" s="137">
-        <f>WACC!C20</f>
-        <v>0.11076337061687277</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11074285459263533</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6115,8 +6040,8 @@
         <v>262</v>
       </c>
       <c r="C61" s="151">
-        <f>C60/(1+C56)^5</f>
-        <v>521.42000737021101</v>
+        <f ca="1">C60/(1+C56)^5</f>
+        <v>521.46816370382192</v>
       </c>
     </row>
   </sheetData>
@@ -6176,8 +6101,8 @@
         <v>189</v>
       </c>
       <c r="C5" s="166">
-        <f>DCF!C26</f>
-        <v>300.90612941341146</v>
+        <f ca="1">DCF!C26</f>
+        <v>300.98079280932404</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6185,8 +6110,8 @@
         <v>266</v>
       </c>
       <c r="C6" s="166">
-        <f>Multiples!C44</f>
-        <v>558.2161088962647</v>
+        <f ca="1">Multiples!C44</f>
+        <v>558.2676635753852</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6194,8 +6119,8 @@
         <v>190</v>
       </c>
       <c r="C7" s="166">
-        <f>Multiples!C52</f>
-        <v>552.5321423001368</v>
+        <f ca="1">Multiples!C52</f>
+        <v>552.58317203010347</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6203,8 +6128,8 @@
         <v>267</v>
       </c>
       <c r="C8" s="166">
-        <f>Multiples!C61</f>
-        <v>521.42000737021101</v>
+        <f ca="1">Multiples!C61</f>
+        <v>521.46816370382192</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6212,8 +6137,8 @@
         <v>188</v>
       </c>
       <c r="C9" s="151">
-        <f>AVERAGE(C5:C8)</f>
-        <v>483.26859699500596</v>
+        <f ca="1">AVERAGE(C5:C8)</f>
+        <v>483.32494802965869</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6221,8 +6146,8 @@
         <v>335</v>
       </c>
       <c r="C10" s="34">
-        <f>Overview!C3</f>
-        <v>250.17</v>
+        <f ca="1">Overview!C3</f>
+        <v>252.47</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6230,8 +6155,8 @@
         <v>336</v>
       </c>
       <c r="C11" s="88">
-        <f>(C9-C10)/C10</f>
-        <v>0.93176079064238715</v>
+        <f ca="1">(C9-C10)/C10</f>
+        <v>0.91438566178024594</v>
       </c>
     </row>
   </sheetData>
@@ -6336,43 +6261,43 @@
         <v>125</v>
       </c>
       <c r="C6" s="61">
-        <f>[2]Revenue!C5</f>
+        <f>Revenue!C5</f>
         <v>2021</v>
       </c>
       <c r="D6" s="61">
-        <f>[2]Revenue!D5</f>
+        <f>Revenue!D5</f>
         <v>2022</v>
       </c>
       <c r="E6" s="61">
-        <f>[2]Revenue!E5</f>
+        <f>Revenue!E5</f>
         <v>2023</v>
       </c>
       <c r="F6" s="61">
-        <f>[2]Revenue!F5</f>
+        <f>Revenue!F5</f>
         <v>2024</v>
       </c>
       <c r="G6" s="61">
-        <f>[2]Revenue!G5</f>
+        <f>Revenue!G5</f>
         <v>2025</v>
       </c>
       <c r="H6" s="61">
-        <f>[2]Revenue!H5</f>
+        <f>Revenue!H5</f>
         <v>2026</v>
       </c>
       <c r="I6" s="61">
-        <f>[2]Revenue!I5</f>
+        <f>Revenue!I5</f>
         <v>2027</v>
       </c>
       <c r="J6" s="61">
-        <f>[2]Revenue!J5</f>
+        <f>Revenue!J5</f>
         <v>2028</v>
       </c>
       <c r="K6" s="61">
-        <f>[2]Revenue!K5</f>
+        <f>Revenue!K5</f>
         <v>2029</v>
       </c>
       <c r="L6" s="61">
-        <f>[2]Revenue!L5</f>
+        <f>Revenue!L5</f>
         <v>2030</v>
       </c>
       <c r="O6" s="7"/>
@@ -6462,8 +6387,8 @@
       <c r="J8" s="129"/>
       <c r="K8" s="129"/>
       <c r="L8" s="132">
-        <f>L7*(1+C20)/(C21-C20)</f>
-        <v>115705.50622470703</v>
+        <f ca="1">L7*(1+C20)/(C21-C20)</f>
+        <v>115733.19152841414</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -6516,24 +6441,24 @@
       <c r="F10" s="129"/>
       <c r="G10" s="149"/>
       <c r="H10" s="132">
-        <f>H7/(1+$C$21)^H9</f>
-        <v>7743.9324130708546</v>
+        <f ca="1">H7/(1+$C$21)^H9</f>
+        <v>7744.0754477115197</v>
       </c>
       <c r="I10" s="132">
-        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>7180.8727191222506</v>
+        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
+        <v>7181.1379908162517</v>
       </c>
       <c r="J10" s="132">
-        <f t="shared" si="1"/>
-        <v>6658.7529768723971</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>6659.1219560475402</v>
       </c>
       <c r="K10" s="132">
-        <f t="shared" si="1"/>
-        <v>6174.5964510601652</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>6175.0526563094254</v>
       </c>
       <c r="L10" s="132">
-        <f t="shared" si="1"/>
-        <v>5725.6428442180068</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>5726.1716424287497</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -6551,8 +6476,8 @@
       <c r="J11" s="129"/>
       <c r="K11" s="129"/>
       <c r="L11" s="132">
-        <f>L8/(1+C21)^L9</f>
-        <v>68429.958770403697</v>
+        <f ca="1">L8/(1+C21)^L9</f>
+        <v>68452.653709450882</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6567,8 +6492,8 @@
         <v>339</v>
       </c>
       <c r="C15" s="197">
-        <f>Overview!C3</f>
-        <v>250.17</v>
+        <f ca="1">Overview!C3</f>
+        <v>252.47</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6576,8 +6501,8 @@
         <v>340</v>
       </c>
       <c r="C16" s="197">
-        <f>C36</f>
-        <v>253.90038657115684</v>
+        <f ca="1">C36</f>
+        <v>253.96092426426827</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6615,8 +6540,8 @@
         <v>147</v>
       </c>
       <c r="C21" s="202">
-        <f>WACC!C20</f>
-        <v>0.11076337061687277</v>
+        <f ca="1">WACC!C20</f>
+        <v>0.11074285459263533</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6633,8 +6558,8 @@
         <v>140</v>
       </c>
       <c r="C23" s="203">
-        <f>C15*C22</f>
-        <v>101068.68</v>
+        <f ca="1">C15*C22</f>
+        <v>101997.88</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6660,8 +6585,8 @@
         <v>343</v>
       </c>
       <c r="C26" s="204">
-        <f>C23+C25-C24</f>
-        <v>100406.68</v>
+        <f ca="1">C23+C25-C24</f>
+        <v>101335.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6676,8 +6601,8 @@
         <v>170</v>
       </c>
       <c r="C29" s="203">
-        <f>SUM(H10:L10)</f>
-        <v>33483.797404343677</v>
+        <f ca="1">SUM(H10:L10)</f>
+        <v>33485.559693313488</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6685,8 +6610,8 @@
         <v>164</v>
       </c>
       <c r="C30" s="203">
-        <f>L11</f>
-        <v>68429.958770403697</v>
+        <f ca="1">L11</f>
+        <v>68452.653709450882</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6694,8 +6619,8 @@
         <v>167</v>
       </c>
       <c r="C31" s="206">
-        <f>C29+C30</f>
-        <v>101913.75617474737</v>
+        <f ca="1">C29+C30</f>
+        <v>101938.21340276438</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6721,8 +6646,8 @@
         <v>168</v>
       </c>
       <c r="C34" s="206">
-        <f>C31+C32-C33</f>
-        <v>102575.75617474737</v>
+        <f ca="1">C31+C32-C33</f>
+        <v>102600.21340276438</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6739,8 +6664,8 @@
         <v>169</v>
       </c>
       <c r="C36" s="209">
-        <f>C34/C35</f>
-        <v>253.90038657115684</v>
+        <f ca="1">C34/C35</f>
+        <v>253.96092426426827</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E069D2ED-9DC9-D347-9879-ADAA00F3316F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E326E05-26D3-C94F-927F-BA461B9FA5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2319,22 +2319,17 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="8">
-          <cell r="C8">
-            <v>218.965</v>
-          </cell>
-        </row>
         <row r="10">
           <cell r="C10">
-            <v>43.92</v>
+            <v>45.95</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>252.47</v>
+            <v>247.6</v>
           </cell>
           <cell r="F18">
-            <v>1.4196</v>
+            <v>1.4156</v>
           </cell>
         </row>
       </sheetData>
@@ -2806,8 +2801,8 @@
         <v>73</v>
       </c>
       <c r="C3" s="34">
-        <f ca="1">[1]Sheet1!$C$18</f>
-        <v>252.47</v>
+        <f>[1]Sheet1!$C$18</f>
+        <v>247.6</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2840,8 +2835,8 @@
         <v>107</v>
       </c>
       <c r="C11" s="92">
-        <f ca="1">$C$3/'Statement Q'!$N$24</f>
-        <v>14.719827622086571</v>
+        <f>$C$3/'Statement Q'!$N$24</f>
+        <v>14.435890677025528</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2849,8 +2844,8 @@
         <v>181</v>
       </c>
       <c r="C12" s="92">
-        <f ca="1">$C$3/Statements!W24</f>
-        <v>14.719827622086571</v>
+        <f>$C$3/Statements!W24</f>
+        <v>14.435890677025528</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2858,8 +2853,8 @@
         <v>108</v>
       </c>
       <c r="C13" s="97">
-        <f ca="1">$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
-        <v>4.3389570809307649</v>
+        <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
+        <v>4.25526111315585</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2867,8 +2862,8 @@
         <v>140</v>
       </c>
       <c r="C15" s="20">
-        <f ca="1">C3*'Statement Q'!N116</f>
-        <v>101997.88</v>
+        <f>C3*'Statement Q'!N116</f>
+        <v>100030.39999999999</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2894,8 +2889,8 @@
         <v>142</v>
       </c>
       <c r="C18" s="20">
-        <f ca="1">C15+C17-C16</f>
-        <v>101335.88</v>
+        <f>C15+C17-C16</f>
+        <v>99368.4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4317,8 +4312,8 @@
         <v>73</v>
       </c>
       <c r="C6" s="144">
-        <f ca="1">Overview!C3</f>
-        <v>252.47</v>
+        <f>Overview!C3</f>
+        <v>247.6</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4326,8 +4321,8 @@
         <v>138</v>
       </c>
       <c r="C7" s="146">
-        <f ca="1">C5*C6</f>
-        <v>101997.88</v>
+        <f>C5*C6</f>
+        <v>100030.39999999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4344,8 +4339,8 @@
         <v>153</v>
       </c>
       <c r="C9" s="169">
-        <f ca="1">[1]Sheet1!$C$10/1000</f>
-        <v>4.3920000000000001E-2</v>
+        <f>[1]Sheet1!$C$10/1000</f>
+        <v>4.5950000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4353,8 +4348,8 @@
         <v>154</v>
       </c>
       <c r="C10" s="144">
-        <f ca="1">[1]Sheet1!$F$18</f>
-        <v>1.4196</v>
+        <f>[1]Sheet1!$F$18</f>
+        <v>1.4156</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4393,8 +4388,8 @@
         <v>148</v>
       </c>
       <c r="C16" s="147">
-        <f ca="1">C8/(C8+C7)</f>
-        <v>5.7546309625756797E-2</v>
+        <f>C8/(C8+C7)</f>
+        <v>5.8611836805372568E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4402,8 +4397,8 @@
         <v>149</v>
       </c>
       <c r="C17" s="147">
-        <f ca="1">C7/(C8+C7)</f>
-        <v>0.9424536903742432</v>
+        <f>C7/(C8+C7)</f>
+        <v>0.94138816319462748</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4420,8 +4415,8 @@
         <v>150</v>
       </c>
       <c r="C19" s="147">
-        <f ca="1">C9+C10*C11</f>
-        <v>0.1149</v>
+        <f>C9+C10*C11</f>
+        <v>0.11673</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4429,8 +4424,8 @@
         <v>147</v>
       </c>
       <c r="C20" s="147">
-        <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11074285459263533</v>
+        <f>(C17*C19)+(C16*C18)</f>
+        <v>0.11238862124782606</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4682,8 +4677,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="132">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>143675.81418163067</v>
+        <f>L7*(1+C14)/(C15-C14)</f>
+        <v>140970.0057964985</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -4736,24 +4731,24 @@
       <c r="F10" s="129"/>
       <c r="G10" s="149"/>
       <c r="H10" s="132">
-        <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7138.971521264566</v>
+        <f>H7/(1+$C$15)^H9</f>
+        <v>7128.4094919003383</v>
       </c>
       <c r="I10" s="132">
-        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7265.1256616940354</v>
+        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
+        <v>7243.6442181989341</v>
       </c>
       <c r="J10" s="132">
-        <f t="shared" ca="1" si="0"/>
-        <v>7256.5890948679034</v>
+        <f t="shared" si="0"/>
+        <v>7224.4285931511376</v>
       </c>
       <c r="K10" s="132">
-        <f t="shared" ca="1" si="0"/>
-        <v>7184.9925014780983</v>
+        <f t="shared" si="0"/>
+        <v>7142.5663037011691</v>
       </c>
       <c r="L10" s="132">
-        <f t="shared" ca="1" si="0"/>
-        <v>7108.6985678410865</v>
+        <f t="shared" si="0"/>
+        <v>7056.2677348922662</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -4771,8 +4766,8 @@
       <c r="J11" s="129"/>
       <c r="K11" s="129"/>
       <c r="L11" s="132">
-        <f ca="1">L8/(1+C15)^L9</f>
-        <v>84979.862947821224</v>
+        <f>L8/(1+C15)^L9</f>
+        <v>82764.487240888891</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -4794,8 +4789,8 @@
         <v>147</v>
       </c>
       <c r="C15" s="148">
-        <f ca="1">WACC!C20</f>
-        <v>0.11074285459263533</v>
+        <f>WACC!C20</f>
+        <v>0.11238862124782606</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -4809,8 +4804,8 @@
         <v>170</v>
       </c>
       <c r="C19" s="103">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>35954.377347145688</v>
+        <f>SUM(H10:L10)</f>
+        <v>35795.316341843849</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4818,8 +4813,8 @@
         <v>164</v>
       </c>
       <c r="C20" s="103">
-        <f ca="1">L11</f>
-        <v>84979.862947821224</v>
+        <f>L11</f>
+        <v>82764.487240888891</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4827,8 +4822,8 @@
         <v>167</v>
       </c>
       <c r="C21" s="108">
-        <f ca="1">C19+C20</f>
-        <v>120934.2402949669</v>
+        <f>C19+C20</f>
+        <v>118559.80358273274</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4854,8 +4849,8 @@
         <v>168</v>
       </c>
       <c r="C24" s="108">
-        <f ca="1">C21+C22-C23</f>
-        <v>121596.2402949669</v>
+        <f>C21+C22-C23</f>
+        <v>119221.80358273274</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4872,8 +4867,8 @@
         <v>169</v>
       </c>
       <c r="C26" s="151">
-        <f ca="1">C24/C25</f>
-        <v>300.98079280932404</v>
+        <f>C24/C25</f>
+        <v>295.10347421468498</v>
       </c>
     </row>
   </sheetData>
@@ -5869,8 +5864,8 @@
         <v>147</v>
       </c>
       <c r="C39" s="137">
-        <f ca="1">WACC!C20</f>
-        <v>0.11074285459263533</v>
+        <f>WACC!C20</f>
+        <v>0.11238862124782606</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5913,8 +5908,8 @@
         <v>262</v>
       </c>
       <c r="C44" s="151">
-        <f ca="1">C43/(1+C48)^5</f>
-        <v>558.2676635753852</v>
+        <f>C43/(1+C48)^5</f>
+        <v>554.15011120903989</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -5937,8 +5932,8 @@
         <v>147</v>
       </c>
       <c r="C48" s="137">
-        <f ca="1">WACC!C20</f>
-        <v>0.11074285459263533</v>
+        <f>WACC!C20</f>
+        <v>0.11238862124782606</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -5972,8 +5967,8 @@
         <v>262</v>
       </c>
       <c r="C52" s="151">
-        <f ca="1">C51/(1+C48)^5</f>
-        <v>552.58317203010347</v>
+        <f>C51/(1+C48)^5</f>
+        <v>548.50754613226229</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -5996,8 +5991,8 @@
         <v>147</v>
       </c>
       <c r="C56" s="137">
-        <f ca="1">WACC!C20</f>
-        <v>0.11074285459263533</v>
+        <f>WACC!C20</f>
+        <v>0.11238862124782606</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6040,8 +6035,8 @@
         <v>262</v>
       </c>
       <c r="C61" s="151">
-        <f ca="1">C60/(1+C56)^5</f>
-        <v>521.46816370382192</v>
+        <f>C60/(1+C56)^5</f>
+        <v>517.62202929281023</v>
       </c>
     </row>
   </sheetData>
@@ -6101,8 +6096,8 @@
         <v>189</v>
       </c>
       <c r="C5" s="166">
-        <f ca="1">DCF!C26</f>
-        <v>300.98079280932404</v>
+        <f>DCF!C26</f>
+        <v>295.10347421468498</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6110,8 +6105,8 @@
         <v>266</v>
       </c>
       <c r="C6" s="166">
-        <f ca="1">Multiples!C44</f>
-        <v>558.2676635753852</v>
+        <f>Multiples!C44</f>
+        <v>554.15011120903989</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6119,8 +6114,8 @@
         <v>190</v>
       </c>
       <c r="C7" s="166">
-        <f ca="1">Multiples!C52</f>
-        <v>552.58317203010347</v>
+        <f>Multiples!C52</f>
+        <v>548.50754613226229</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6128,8 +6123,8 @@
         <v>267</v>
       </c>
       <c r="C8" s="166">
-        <f ca="1">Multiples!C61</f>
-        <v>521.46816370382192</v>
+        <f>Multiples!C61</f>
+        <v>517.62202929281023</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6137,8 +6132,8 @@
         <v>188</v>
       </c>
       <c r="C9" s="151">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>483.32494802965869</v>
+        <f>AVERAGE(C5:C8)</f>
+        <v>478.84579021219929</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6146,8 +6141,8 @@
         <v>335</v>
       </c>
       <c r="C10" s="34">
-        <f ca="1">Overview!C3</f>
-        <v>252.47</v>
+        <f>Overview!C3</f>
+        <v>247.6</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6155,8 +6150,8 @@
         <v>336</v>
       </c>
       <c r="C11" s="88">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>0.91438566178024594</v>
+        <f>(C9-C10)/C10</f>
+        <v>0.93394907193941556</v>
       </c>
     </row>
   </sheetData>
@@ -6387,8 +6382,8 @@
       <c r="J8" s="129"/>
       <c r="K8" s="129"/>
       <c r="L8" s="132">
-        <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>115733.19152841414</v>
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>113553.6191218864</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -6441,24 +6436,24 @@
       <c r="F10" s="129"/>
       <c r="G10" s="149"/>
       <c r="H10" s="132">
-        <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7744.0754477115197</v>
+        <f>H7/(1+$C$21)^H9</f>
+        <v>7732.6181737843317</v>
       </c>
       <c r="I10" s="132">
-        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7181.1379908162517</v>
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>7159.9048811408602</v>
       </c>
       <c r="J10" s="132">
-        <f t="shared" ca="1" si="1"/>
-        <v>6659.1219560475402</v>
+        <f t="shared" si="1"/>
+        <v>6629.6093709611014</v>
       </c>
       <c r="K10" s="132">
-        <f t="shared" ca="1" si="1"/>
-        <v>6175.0526563094254</v>
+        <f t="shared" si="1"/>
+        <v>6138.5899870407175</v>
       </c>
       <c r="L10" s="132">
-        <f t="shared" ca="1" si="1"/>
-        <v>5726.1716424287497</v>
+        <f t="shared" si="1"/>
+        <v>5683.9377586938772</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -6476,8 +6471,8 @@
       <c r="J11" s="129"/>
       <c r="K11" s="129"/>
       <c r="L11" s="132">
-        <f ca="1">L8/(1+C21)^L9</f>
-        <v>68452.653709450882</v>
+        <f>L8/(1+C21)^L9</f>
+        <v>66668.132755397542</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6492,8 +6487,8 @@
         <v>339</v>
       </c>
       <c r="C15" s="197">
-        <f ca="1">Overview!C3</f>
-        <v>252.47</v>
+        <f>Overview!C3</f>
+        <v>247.6</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6501,8 +6496,8 @@
         <v>340</v>
       </c>
       <c r="C16" s="197">
-        <f ca="1">C36</f>
-        <v>253.96092426426827</v>
+        <f>C36</f>
+        <v>249.19503199757037</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6540,8 +6535,8 @@
         <v>147</v>
       </c>
       <c r="C21" s="202">
-        <f ca="1">WACC!C20</f>
-        <v>0.11074285459263533</v>
+        <f>WACC!C20</f>
+        <v>0.11238862124782606</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6558,8 +6553,8 @@
         <v>140</v>
       </c>
       <c r="C23" s="203">
-        <f ca="1">C15*C22</f>
-        <v>101997.88</v>
+        <f>C15*C22</f>
+        <v>100030.39999999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6585,8 +6580,8 @@
         <v>343</v>
       </c>
       <c r="C26" s="204">
-        <f ca="1">C23+C25-C24</f>
-        <v>101335.88</v>
+        <f>C23+C25-C24</f>
+        <v>99368.4</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6601,8 +6596,8 @@
         <v>170</v>
       </c>
       <c r="C29" s="203">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>33485.559693313488</v>
+        <f>SUM(H10:L10)</f>
+        <v>33344.66017162089</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6610,8 +6605,8 @@
         <v>164</v>
       </c>
       <c r="C30" s="203">
-        <f ca="1">L11</f>
-        <v>68452.653709450882</v>
+        <f>L11</f>
+        <v>66668.132755397542</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6619,8 +6614,8 @@
         <v>167</v>
       </c>
       <c r="C31" s="206">
-        <f ca="1">C29+C30</f>
-        <v>101938.21340276438</v>
+        <f>C29+C30</f>
+        <v>100012.79292701842</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6646,8 +6641,8 @@
         <v>168</v>
       </c>
       <c r="C34" s="206">
-        <f ca="1">C31+C32-C33</f>
-        <v>102600.21340276438</v>
+        <f>C31+C32-C33</f>
+        <v>100674.79292701842</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6664,8 +6659,8 @@
         <v>169</v>
       </c>
       <c r="C36" s="209">
-        <f ca="1">C34/C35</f>
-        <v>253.96092426426827</v>
+        <f>C34/C35</f>
+        <v>249.19503199757037</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -7112,17 +7107,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29012,6 +29007,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -29019,12 +29020,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E326E05-26D3-C94F-927F-BA461B9FA5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20929129-E17A-0B46-A19C-499A5700A2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="1" activeTab="11" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2321,15 +2321,15 @@
       <sheetData sheetId="0">
         <row r="10">
           <cell r="C10">
-            <v>45.95</v>
+            <v>45.86</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>247.6</v>
+            <v>244.1</v>
           </cell>
           <cell r="F18">
-            <v>1.4156</v>
+            <v>1.4184000000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C3" s="34">
         <f>[1]Sheet1!$C$18</f>
-        <v>247.6</v>
+        <v>244.1</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C11" s="92">
         <f>$C$3/'Statement Q'!$N$24</f>
-        <v>14.435890677025528</v>
+        <v>14.231829217536072</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C12" s="92">
         <f>$C$3/Statements!W24</f>
-        <v>14.435890677025528</v>
+        <v>14.231829217536072</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C13" s="97">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
-        <v>4.25526111315585</v>
+        <v>4.1951100069521123</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N116</f>
-        <v>100030.39999999999</v>
+        <v>98616.4</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>99368.4</v>
+        <v>97954.4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="C6" s="144">
         <f>Overview!C3</f>
-        <v>247.6</v>
+        <v>244.1</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C7" s="146">
         <f>C5*C6</f>
-        <v>100030.39999999999</v>
+        <v>98616.4</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C9" s="169">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.5950000000000005E-2</v>
+        <v>4.5859999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C10" s="144">
         <f>[1]Sheet1!$F$18</f>
-        <v>1.4156</v>
+        <v>1.4184000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="C16" s="147">
         <f>C8/(C8+C7)</f>
-        <v>5.8611836805372568E-2</v>
+        <v>5.9402314286695332E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C17" s="147">
         <f>C7/(C8+C7)</f>
-        <v>0.94138816319462748</v>
+        <v>0.94059768571330471</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="C19" s="147">
         <f>C9+C10*C11</f>
-        <v>0.11673</v>
+        <v>0.11678000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C20" s="147">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>0.11238862124782606</v>
+        <v>0.11237710046507016</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="L8" s="132">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>140970.0057964985</v>
+        <v>140988.59287255429</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -4732,23 +4732,23 @@
       <c r="G10" s="149"/>
       <c r="H10" s="132">
         <f>H7/(1+$C$15)^H9</f>
-        <v>7128.4094919003383</v>
+        <v>7128.4833201525698</v>
       </c>
       <c r="I10" s="132">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>7243.6442181989341</v>
+        <v>7243.7942624303687</v>
       </c>
       <c r="J10" s="132">
         <f t="shared" si="0"/>
-        <v>7224.4285931511376</v>
+        <v>7224.6530636144562</v>
       </c>
       <c r="K10" s="132">
         <f t="shared" si="0"/>
-        <v>7142.5663037011691</v>
+        <v>7142.8622077899918</v>
       </c>
       <c r="L10" s="132">
         <f t="shared" si="0"/>
-        <v>7056.2677348922662</v>
+        <v>7056.633147896212</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -4767,7 +4767,7 @@
       <c r="K11" s="129"/>
       <c r="L11" s="132">
         <f>L8/(1+C15)^L9</f>
-        <v>82764.487240888891</v>
+        <v>82779.686417782854</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="C15" s="148">
         <f>WACC!C20</f>
-        <v>0.11238862124782606</v>
+        <v>0.11237710046507016</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C19" s="103">
         <f>SUM(H10:L10)</f>
-        <v>35795.316341843849</v>
+        <v>35796.426001883599</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="C20" s="103">
         <f>L11</f>
-        <v>82764.487240888891</v>
+        <v>82779.686417782854</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="C21" s="108">
         <f>C19+C20</f>
-        <v>118559.80358273274</v>
+        <v>118576.11241966646</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C24" s="108">
         <f>C21+C22-C23</f>
-        <v>119221.80358273274</v>
+        <v>119238.11241966646</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C26" s="151">
         <f>C24/C25</f>
-        <v>295.10347421468498</v>
+        <v>295.1438426229368</v>
       </c>
     </row>
   </sheetData>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="C39" s="137">
         <f>WACC!C20</f>
-        <v>0.11238862124782606</v>
+        <v>0.11237710046507016</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C44" s="151">
         <f>C43/(1+C48)^5</f>
-        <v>554.15011120903989</v>
+        <v>554.17880820076152</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C48" s="137">
         <f>WACC!C20</f>
-        <v>0.11238862124782606</v>
+        <v>0.11237710046507016</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C52" s="151">
         <f>C51/(1+C48)^5</f>
-        <v>548.50754613226229</v>
+        <v>548.53595092040939</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="C56" s="137">
         <f>WACC!C20</f>
-        <v>0.11238862124782606</v>
+        <v>0.11237710046507016</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="C61" s="151">
         <f>C60/(1+C56)^5</f>
-        <v>517.62202929281023</v>
+        <v>517.64883465617493</v>
       </c>
     </row>
   </sheetData>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C5" s="166">
         <f>DCF!C26</f>
-        <v>295.10347421468498</v>
+        <v>295.1438426229368</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C6" s="166">
         <f>Multiples!C44</f>
-        <v>554.15011120903989</v>
+        <v>554.17880820076152</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C7" s="166">
         <f>Multiples!C52</f>
-        <v>548.50754613226229</v>
+        <v>548.53595092040939</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C8" s="166">
         <f>Multiples!C61</f>
-        <v>517.62202929281023</v>
+        <v>517.64883465617493</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C9" s="151">
         <f>AVERAGE(C5:C8)</f>
-        <v>478.84579021219929</v>
+        <v>478.87685910007065</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C10" s="34">
         <f>Overview!C3</f>
-        <v>247.6</v>
+        <v>244.1</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="C11" s="88">
         <f>(C9-C10)/C10</f>
-        <v>0.93394907193941556</v>
+        <v>0.9618060594021739</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +6383,7 @@
       <c r="K8" s="129"/>
       <c r="L8" s="132">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>113553.6191218864</v>
+        <v>113568.59131219813</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -6437,23 +6437,23 @@
       <c r="G10" s="149"/>
       <c r="H10" s="132">
         <f>H7/(1+$C$21)^H9</f>
-        <v>7732.6181737843317</v>
+        <v>7732.6982597678316</v>
       </c>
       <c r="I10" s="132">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>7159.9048811408602</v>
+        <v>7160.053190802776</v>
       </c>
       <c r="J10" s="132">
         <f t="shared" si="1"/>
-        <v>6629.6093709611014</v>
+        <v>6629.8153597764003</v>
       </c>
       <c r="K10" s="132">
         <f t="shared" si="1"/>
-        <v>6138.5899870407175</v>
+        <v>6138.8442981383732</v>
       </c>
       <c r="L10" s="132">
         <f t="shared" si="1"/>
-        <v>5683.9377586938772</v>
+        <v>5684.2321047772002</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="K11" s="129"/>
       <c r="L11" s="132">
         <f>L8/(1+C21)^L9</f>
-        <v>66668.132755397542</v>
+        <v>66680.375938152865</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C15" s="197">
         <f>Overview!C3</f>
-        <v>247.6</v>
+        <v>244.1</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="C16" s="197">
         <f>C36</f>
-        <v>249.19503199757037</v>
+        <v>249.22777017677089</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="C21" s="202">
         <f>WACC!C20</f>
-        <v>0.11238862124782606</v>
+        <v>0.11237710046507016</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C23" s="203">
         <f>C15*C22</f>
-        <v>100030.39999999999</v>
+        <v>98616.4</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="C26" s="204">
         <f>C23+C25-C24</f>
-        <v>99368.4</v>
+        <v>97954.4</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="C29" s="203">
         <f>SUM(H10:L10)</f>
-        <v>33344.66017162089</v>
+        <v>33345.643213262585</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C30" s="203">
         <f>L11</f>
-        <v>66668.132755397542</v>
+        <v>66680.375938152865</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C31" s="206">
         <f>C29+C30</f>
-        <v>100012.79292701842</v>
+        <v>100026.01915141544</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="C34" s="206">
         <f>C31+C32-C33</f>
-        <v>100674.79292701842</v>
+        <v>100688.01915141544</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C36" s="209">
         <f>C34/C35</f>
-        <v>249.19503199757037</v>
+        <v>249.22777017677089</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -7107,17 +7107,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29007,12 +29007,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -29020,6 +29014,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20929129-E17A-0B46-A19C-499A5700A2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E4D048-4665-CF44-8185-958E4EB4E381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="1" activeTab="11" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2181,6 +2181,9 @@
     <xf numFmtId="169" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2188,9 +2191,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2321,15 +2321,15 @@
       <sheetData sheetId="0">
         <row r="10">
           <cell r="C10">
-            <v>45.86</v>
+            <v>44.55</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>244.1</v>
+            <v>257.0668</v>
           </cell>
           <cell r="F18">
-            <v>1.4184000000000001</v>
+            <v>1.4020999999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C3" s="34">
         <f>[1]Sheet1!$C$18</f>
-        <v>244.1</v>
+        <v>257.0668</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C11" s="92">
         <f>$C$3/'Statement Q'!$N$24</f>
-        <v>14.231829217536072</v>
+        <v>14.987836112652609</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C12" s="92">
         <f>$C$3/Statements!W24</f>
-        <v>14.231829217536072</v>
+        <v>14.987836112652609</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C13" s="97">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$22)</f>
-        <v>4.1951100069521123</v>
+        <v>4.4179578252157201</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N116</f>
-        <v>98616.4</v>
+        <v>103854.9872</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>97954.4</v>
+        <v>103192.9872</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3112,20 +3112,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
       <c r="G2" s="218"/>
       <c r="H2" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
       <c r="S2" s="221"/>
       <c r="T2" s="221"/>
       <c r="U2" s="221"/>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="212" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="215"/>
+      <c r="C4" s="212"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="C6" s="144">
         <f>Overview!C3</f>
-        <v>244.1</v>
+        <v>257.0668</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C7" s="146">
         <f>C5*C6</f>
-        <v>98616.4</v>
+        <v>103854.9872</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C9" s="169">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.5859999999999998E-2</v>
+        <v>4.4549999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C10" s="144">
         <f>[1]Sheet1!$F$18</f>
-        <v>1.4184000000000001</v>
+        <v>1.4020999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4378,10 +4378,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="215" t="s">
+      <c r="B15" s="212" t="s">
         <v>157</v>
       </c>
-      <c r="C15" s="215"/>
+      <c r="C15" s="212"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="C16" s="147">
         <f>C8/(C8+C7)</f>
-        <v>5.9402314286695332E-2</v>
+        <v>5.6575499615439215E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C17" s="147">
         <f>C7/(C8+C7)</f>
-        <v>0.94059768571330471</v>
+        <v>0.94342450038456083</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="C19" s="147">
         <f>C9+C10*C11</f>
-        <v>0.11678000000000001</v>
+        <v>0.11465500000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C20" s="147">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>0.11237710046507016</v>
+        <v>0.11058184690518646</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4472,20 +4472,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="215" t="s">
+      <c r="C3" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="215"/>
-      <c r="E3" s="215"/>
-      <c r="F3" s="215"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
       <c r="G3" s="218"/>
       <c r="H3" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="215"/>
-      <c r="K3" s="215"/>
-      <c r="L3" s="215"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
       <c r="P3" s="221"/>
       <c r="Q3" s="221"/>
       <c r="R3" s="221"/>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="L8" s="132">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>140988.59287255429</v>
+        <v>143946.11578670522</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -4732,23 +4732,23 @@
       <c r="G10" s="149"/>
       <c r="H10" s="132">
         <f>H7/(1+$C$15)^H9</f>
-        <v>7128.4833201525698</v>
+        <v>7140.0065006302075</v>
       </c>
       <c r="I10" s="132">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>7243.7942624303687</v>
+        <v>7267.2323517633049</v>
       </c>
       <c r="J10" s="132">
         <f t="shared" si="0"/>
-        <v>7224.6530636144562</v>
+        <v>7259.7456457123099</v>
       </c>
       <c r="K10" s="132">
         <f t="shared" si="0"/>
-        <v>7142.8622077899918</v>
+        <v>7189.1600128608643</v>
       </c>
       <c r="L10" s="132">
         <f t="shared" si="0"/>
-        <v>7056.633147896212</v>
+        <v>7113.8530147396978</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -4767,14 +4767,14 @@
       <c r="K11" s="129"/>
       <c r="L11" s="132">
         <f>L8/(1+C15)^L9</f>
-        <v>82779.686417782854</v>
+        <v>85201.472085387941</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="215" t="s">
+      <c r="B13" s="212" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="215"/>
+      <c r="C13" s="212"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4790,14 +4790,14 @@
       </c>
       <c r="C15" s="148">
         <f>WACC!C20</f>
-        <v>0.11237710046507016</v>
+        <v>0.11058184690518646</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="215" t="s">
+      <c r="B18" s="212" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="215"/>
+      <c r="C18" s="212"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C19" s="103">
         <f>SUM(H10:L10)</f>
-        <v>35796.426001883599</v>
+        <v>35969.997525706378</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="C20" s="103">
         <f>L11</f>
-        <v>82779.686417782854</v>
+        <v>85201.472085387941</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="C21" s="108">
         <f>C19+C20</f>
-        <v>118576.11241966646</v>
+        <v>121171.46961109432</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C24" s="108">
         <f>C21+C22-C23</f>
-        <v>119238.11241966646</v>
+        <v>121833.46961109432</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C26" s="151">
         <f>C24/C25</f>
-        <v>295.1438426229368</v>
+        <v>301.56799408686715</v>
       </c>
     </row>
   </sheetData>
@@ -4911,20 +4911,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
       <c r="G2" s="218"/>
       <c r="H2" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5844,10 +5844,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="215" t="s">
+      <c r="B37" s="212" t="s">
         <v>259</v>
       </c>
-      <c r="C37" s="215"/>
+      <c r="C37" s="212"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="C39" s="137">
         <f>WACC!C20</f>
-        <v>0.11237710046507016</v>
+        <v>0.11058184690518646</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5909,14 +5909,14 @@
       </c>
       <c r="C44" s="151">
         <f>C43/(1+C48)^5</f>
-        <v>554.17880820076152</v>
+        <v>558.672457926932</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="215" t="s">
+      <c r="B46" s="212" t="s">
         <v>184</v>
       </c>
-      <c r="C46" s="215"/>
+      <c r="C46" s="212"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C48" s="137">
         <f>WACC!C20</f>
-        <v>0.11237710046507016</v>
+        <v>0.11058184690518646</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -5968,14 +5968,14 @@
       </c>
       <c r="C52" s="151">
         <f>C51/(1+C48)^5</f>
-        <v>548.53595092040939</v>
+        <v>552.98384461315277</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="215" t="s">
+      <c r="B54" s="212" t="s">
         <v>263</v>
       </c>
-      <c r="C54" s="215"/>
+      <c r="C54" s="212"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="C56" s="137">
         <f>WACC!C20</f>
-        <v>0.11237710046507016</v>
+        <v>0.11058184690518646</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="C61" s="151">
         <f>C60/(1+C56)^5</f>
-        <v>517.64883465617493</v>
+        <v>521.84627510262101</v>
       </c>
     </row>
   </sheetData>
@@ -6085,10 +6085,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="212" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="215"/>
+      <c r="C4" s="212"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C5" s="166">
         <f>DCF!C26</f>
-        <v>295.1438426229368</v>
+        <v>301.56799408686715</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C6" s="166">
         <f>Multiples!C44</f>
-        <v>554.17880820076152</v>
+        <v>558.672457926932</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C7" s="166">
         <f>Multiples!C52</f>
-        <v>548.53595092040939</v>
+        <v>552.98384461315277</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C8" s="166">
         <f>Multiples!C61</f>
-        <v>517.64883465617493</v>
+        <v>521.84627510262101</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C9" s="151">
         <f>AVERAGE(C5:C8)</f>
-        <v>478.87685910007065</v>
+        <v>483.76764293239319</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C10" s="34">
         <f>Overview!C3</f>
-        <v>244.1</v>
+        <v>257.0668</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="C11" s="88">
         <f>(C9-C10)/C10</f>
-        <v>0.9618060594021739</v>
+        <v>0.88187522827682607</v>
       </c>
     </row>
   </sheetData>
@@ -6195,20 +6195,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="215" t="s">
+      <c r="C3" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="215"/>
-      <c r="E3" s="215"/>
-      <c r="F3" s="215"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
       <c r="G3" s="218"/>
       <c r="H3" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="215"/>
-      <c r="K3" s="215"/>
-      <c r="L3" s="215"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
       <c r="P3" s="221"/>
       <c r="Q3" s="221"/>
       <c r="R3" s="221"/>
@@ -6383,7 +6383,7 @@
       <c r="K8" s="129"/>
       <c r="L8" s="132">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>113568.59131219813</v>
+        <v>115950.92384201694</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="7"/>
@@ -6437,23 +6437,23 @@
       <c r="G10" s="149"/>
       <c r="H10" s="132">
         <f>H7/(1+$C$21)^H9</f>
-        <v>7732.6982597678316</v>
+        <v>7745.1981526096242</v>
       </c>
       <c r="I10" s="132">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>7160.053190802776</v>
+        <v>7183.2203267311097</v>
       </c>
       <c r="J10" s="132">
         <f t="shared" si="1"/>
-        <v>6629.8153597764003</v>
+        <v>6662.0186140722089</v>
       </c>
       <c r="K10" s="132">
         <f t="shared" si="1"/>
-        <v>6138.8442981383732</v>
+        <v>6178.634372258196</v>
       </c>
       <c r="L10" s="132">
         <f t="shared" si="1"/>
-        <v>5684.2321047772002</v>
+        <v>5730.3236327518107</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="K11" s="129"/>
       <c r="L11" s="132">
         <f>L8/(1+C21)^L9</f>
-        <v>66680.375938152865</v>
+        <v>68631.163453130051</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C15" s="197">
         <f>Overview!C3</f>
-        <v>244.1</v>
+        <v>257.0668</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="C16" s="197">
         <f>C36</f>
-        <v>249.22777017677089</v>
+        <v>254.43702611770544</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="C21" s="202">
         <f>WACC!C20</f>
-        <v>0.11237710046507016</v>
+        <v>0.11058184690518646</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C23" s="203">
         <f>C15*C22</f>
-        <v>98616.4</v>
+        <v>103854.9872</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="C26" s="204">
         <f>C23+C25-C24</f>
-        <v>97954.4</v>
+        <v>103192.9872</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="C29" s="203">
         <f>SUM(H10:L10)</f>
-        <v>33345.643213262585</v>
+        <v>33499.395098422945</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C30" s="203">
         <f>L11</f>
-        <v>66680.375938152865</v>
+        <v>68631.163453130051</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C31" s="206">
         <f>C29+C30</f>
-        <v>100026.01915141544</v>
+        <v>102130.558551553</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="C34" s="206">
         <f>C31+C32-C33</f>
-        <v>100688.01915141544</v>
+        <v>102792.558551553</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C36" s="209">
         <f>C34/C35</f>
-        <v>249.22777017677089</v>
+        <v>254.43702611770544</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -7107,17 +7107,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13794,11 +13794,11 @@
         <v>74</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="212" t="s">
+      <c r="P4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="213"/>
-      <c r="R4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="215"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -25210,36 +25210,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
       <c r="G2" s="218"/>
       <c r="H2" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
       <c r="O2" s="89"/>
-      <c r="S2" s="215" t="s">
+      <c r="S2" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="T2" s="215"/>
-      <c r="U2" s="215"/>
-      <c r="V2" s="215"/>
-      <c r="W2" s="215"/>
-      <c r="X2" s="215"/>
-      <c r="Y2" s="215"/>
-      <c r="Z2" s="215"/>
-      <c r="AA2" s="215" t="s">
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
+      <c r="W2" s="212"/>
+      <c r="X2" s="212"/>
+      <c r="Y2" s="212"/>
+      <c r="Z2" s="212"/>
+      <c r="AA2" s="212" t="s">
         <v>103</v>
       </c>
-      <c r="AB2" s="215"/>
-      <c r="AC2" s="215"/>
+      <c r="AB2" s="212"/>
+      <c r="AC2" s="212"/>
       <c r="AE2" s="116" t="s">
         <v>74</v>
       </c>
@@ -26238,35 +26238,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="99"/>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="215"/>
-      <c r="E2" s="215"/>
-      <c r="F2" s="215"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
       <c r="G2" s="218"/>
       <c r="H2" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="215"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215"/>
-      <c r="P2" s="215" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="P2" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="Q2" s="215"/>
-      <c r="R2" s="215"/>
-      <c r="S2" s="215"/>
-      <c r="T2" s="215"/>
-      <c r="U2" s="215"/>
-      <c r="V2" s="215"/>
-      <c r="W2" s="215"/>
-      <c r="X2" s="215" t="s">
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
+      <c r="S2" s="212"/>
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
+      <c r="W2" s="212"/>
+      <c r="X2" s="212" t="s">
         <v>103</v>
       </c>
-      <c r="Y2" s="215"/>
-      <c r="Z2" s="215"/>
+      <c r="Y2" s="212"/>
+      <c r="Z2" s="212"/>
       <c r="AB2" s="116" t="s">
         <v>74</v>
       </c>
@@ -27616,20 +27616,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="99"/>
-      <c r="C3" s="215" t="s">
+      <c r="C3" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="215"/>
-      <c r="E3" s="215"/>
-      <c r="F3" s="215"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
       <c r="G3" s="218"/>
       <c r="H3" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="215"/>
-      <c r="K3" s="215"/>
-      <c r="L3" s="215"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
       <c r="P3" s="221"/>
       <c r="Q3" s="221"/>
       <c r="R3" s="221"/>
@@ -29007,6 +29007,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -29014,12 +29020,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A1671C-9EE2-984B-BCD3-DF606CCA9C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15BAD06-5B19-1C45-BC2B-42CF339A6519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="5" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C15" s="20">
         <f>C3*'Statement Q'!N116</f>
-        <v>87957.6</v>
+        <v>87082.400000000009</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C18" s="20">
         <f>C15+C17-C16</f>
-        <v>88976.6</v>
+        <v>88101.400000000009</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C19" s="91">
         <f>C16/'Statement Q'!J116</f>
-        <v>13.99502487562189</v>
+        <v>14.135678391959798</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C34" s="20">
         <f>'Statement Q'!N116</f>
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C35" s="157">
         <f>C33/C34</f>
-        <v>2.4875621890547263E-3</v>
+        <v>2.5125628140703518E-3</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C5" s="130">
         <f>'Statement Q'!N116</f>
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="C7" s="145">
         <f>C5*C6</f>
-        <v>87957.6</v>
+        <v>87082.400000000009</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="C16" s="146">
         <f>C8/(C8+C7)</f>
-        <v>7.024119844486304E-2</v>
+        <v>7.0897090925385736E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C17" s="146">
         <f>C7/(C8+C7)</f>
-        <v>0.92975880155513702</v>
+        <v>0.92910290907461424</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C20" s="146">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>0.10492134463407983</v>
+        <v>0.104877422761327</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="L8" s="131">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>148659.76545752934</v>
+        <v>148736.69304427112</v>
       </c>
       <c r="N8" s="89"/>
       <c r="O8" s="7"/>
@@ -4734,23 +4734,23 @@
       <c r="G10" s="148"/>
       <c r="H10" s="131">
         <f>H7/(1+$C$15)^H9</f>
-        <v>7288.9293754717046</v>
+        <v>7289.2191301738449</v>
       </c>
       <c r="I10" s="131">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>7542.698605632313</v>
+        <v>7543.2983029858324</v>
       </c>
       <c r="J10" s="131">
         <f t="shared" si="0"/>
-        <v>7590.379566469991</v>
+        <v>7591.2848169484878</v>
       </c>
       <c r="K10" s="131">
         <f t="shared" si="0"/>
-        <v>7555.7593812742616</v>
+        <v>7556.9609005902312</v>
       </c>
       <c r="L10" s="131">
         <f t="shared" si="0"/>
-        <v>7515.4210576381238</v>
+        <v>7516.9149682098905</v>
       </c>
       <c r="N10" s="89"/>
     </row>
@@ -4769,7 +4769,7 @@
       <c r="K11" s="128"/>
       <c r="L11" s="131">
         <f>L8/(1+C15)^L9</f>
-        <v>90268.583379384567</v>
+        <v>90333.247854782254</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C15" s="147">
         <f>WACC!C20</f>
-        <v>0.10492134463407983</v>
+        <v>0.104877422761327</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="C19" s="102">
         <f>SUM(H10:L10)</f>
-        <v>37493.187986486395</v>
+        <v>37497.678118908283</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="C20" s="102">
         <f>L11</f>
-        <v>90268.583379384567</v>
+        <v>90333.247854782254</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="C21" s="107">
         <f>C19+C20</f>
-        <v>127761.77136587095</v>
+        <v>127830.92597369054</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C24" s="107">
         <f>C21+C22-C23</f>
-        <v>126742.77136587095</v>
+        <v>126811.92597369052</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C25" s="102">
         <f>'Statement Q'!N116</f>
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C26" s="150">
         <f>C24/C25</f>
-        <v>315.28052578574864</v>
+        <v>318.62292958213698</v>
       </c>
     </row>
   </sheetData>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="C39" s="136">
         <f>WACC!C20</f>
-        <v>0.10492134463407983</v>
+        <v>0.104877422761327</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="C44" s="150">
         <f>C43/(1+C48)^5</f>
-        <v>590.20914466880004</v>
+        <v>590.32646606357116</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="C48" s="136">
         <f>WACC!C20</f>
-        <v>0.10492134463407983</v>
+        <v>0.104877422761327</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="C52" s="150">
         <f>C51/(1+C48)^5</f>
-        <v>584.13935905348831</v>
+        <v>584.25547390017255</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="C56" s="136">
         <f>WACC!C20</f>
-        <v>0.10492134463407983</v>
+        <v>0.104877422761327</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C61" s="150">
         <f>C60/(1+C56)^5</f>
-        <v>551.28493570955231</v>
+        <v>551.39451977506189</v>
       </c>
     </row>
   </sheetData>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="C5" s="165">
         <f>DCF!C26</f>
-        <v>315.28052578574864</v>
+        <v>318.62292958213698</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C6" s="165">
         <f>Multiples!C44</f>
-        <v>590.20914466880004</v>
+        <v>590.32646606357116</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="C7" s="165">
         <f>Multiples!C52</f>
-        <v>584.13935905348831</v>
+        <v>584.25547390017255</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C8" s="165">
         <f>Multiples!C61</f>
-        <v>551.28493570955231</v>
+        <v>551.39451977506189</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C9" s="150">
         <f>AVERAGE(C5:C8)</f>
-        <v>510.22849130439738</v>
+        <v>511.14984733023562</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="C11" s="87">
         <f>(C9-C10)/C10</f>
-        <v>1.3319400882285071</v>
+        <v>1.3361510389864515</v>
       </c>
     </row>
   </sheetData>
@@ -6385,7 +6385,7 @@
       <c r="K8" s="128"/>
       <c r="L8" s="131">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>93392.121267046983</v>
+        <v>93435.355544992402</v>
       </c>
       <c r="N8" s="89"/>
       <c r="O8" s="7"/>
@@ -6439,23 +6439,23 @@
       <c r="G10" s="148"/>
       <c r="H10" s="131">
         <f>H7/(1+$C$21)^H9</f>
-        <v>7633.7140791749825</v>
+        <v>7634.0175400037679</v>
       </c>
       <c r="I10" s="131">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>6977.918616026097</v>
+        <v>6978.473409415823</v>
       </c>
       <c r="J10" s="131">
         <f t="shared" si="1"/>
-        <v>6378.4610881242106</v>
+        <v>6379.2218017224604</v>
       </c>
       <c r="K10" s="131">
         <f t="shared" si="1"/>
-        <v>5830.501628275586</v>
+        <v>5831.4287965421563</v>
       </c>
       <c r="L10" s="131">
         <f t="shared" si="1"/>
-        <v>5329.616151553807</v>
+        <v>5330.6755692299694</v>
       </c>
       <c r="N10" s="89"/>
     </row>
@@ -6474,7 +6474,7 @@
       <c r="K11" s="128"/>
       <c r="L11" s="131">
         <f>L8/(1+C21)^L9</f>
-        <v>56709.187315249066</v>
+        <v>56746.717693483079</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="C16" s="196">
         <f>C36</f>
-        <v>218.50845492140238</v>
+        <v>220.80787640803328</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="C21" s="201">
         <f>WACC!C20</f>
-        <v>0.10492134463407983</v>
+        <v>0.104877422761327</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C22" s="202">
         <f>'Statement Q'!N116</f>
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C23" s="202">
         <f>C15*C22</f>
-        <v>87957.6</v>
+        <v>87082.400000000009</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="C26" s="203">
         <f>C23+C25-C24</f>
-        <v>88976.6</v>
+        <v>88101.400000000009</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="C29" s="202">
         <f>SUM(H10:L10)</f>
-        <v>32150.211563154684</v>
+        <v>32153.817116914179</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C30" s="202">
         <f>L11</f>
-        <v>56709.187315249066</v>
+        <v>56746.717693483079</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="C31" s="205">
         <f>C29+C30</f>
-        <v>88859.39887840375</v>
+        <v>88900.53481039725</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="C34" s="205">
         <f>C31+C32-C33</f>
-        <v>87840.39887840375</v>
+        <v>87881.53481039725</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C35" s="202">
         <f>C22</f>
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="C36" s="208">
         <f>C34/C35</f>
-        <v>218.50845492140238</v>
+        <v>220.80787640803328</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -7109,17 +7109,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -17535,14 +17535,14 @@
         <v>404</v>
       </c>
       <c r="J116" s="27">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K116" s="20"/>
       <c r="L116" s="20"/>
       <c r="M116" s="20"/>
       <c r="N116" s="20">
         <f>J116</f>
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="117" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -29109,12 +29109,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -29122,6 +29116,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C20E23C-5B8F-D349-9408-DA08814D1205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8524FF-716C-4247-8CE3-AC760EBDEA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -15187,14 +15187,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8524FF-716C-4247-8CE3-AC760EBDEA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAAEA81-2FB0-F448-A9A9-8D52F4148653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -4286,43 +4286,11 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="57930431"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -12689,11 +12657,11 @@
     <v>Powered by Refinitiv</v>
     <v>392.58</v>
     <v>190.12</v>
-    <v>1.4390000000000001</v>
-    <v>-1.1200000000000001</v>
-    <v>-5.7060000000000001E-3</v>
-    <v>0.11990000000000001</v>
-    <v>6.1439999999999997E-4</v>
+    <v>1.4596</v>
+    <v>-3.16</v>
+    <v>-1.6076E-2</v>
+    <v>0.99</v>
+    <v>5.1190000000000003E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's products, services and solutions are used around the world to imagine, create, manage, deliver, measure, optimize and engage with content across surfaces and fuel digital experiences. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment is centered around Adobe Creative Cloud and Adobe Document Cloud, which include Adobe Express, Adobe Firefly, Photoshop and other products, offering a variety of tools for creative professionals, communicators and other consumers. The Digital Experience segment provides an integrated platform and set of products, services and solutions through Adobe Experience Cloud. The Publishing and Advertising segment contains legacy products and services. In addition, its Adobe GenStudio solution allows businesses to simplify their content supply chain process with generative artificial intelligence (AI) capabilities and intelligent automation.</v>
     <v>31360</v>
@@ -12701,26 +12669,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>196.78</v>
+    <v>199.29900000000001</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.999931932813</v>
+    <v>46198.911558240623</v>
     <v>4</v>
-    <v>190.12</v>
-    <v>77576100000</v>
+    <v>191.8</v>
+    <v>76880475000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>193.6</v>
-    <v>11.2325</v>
-    <v>196.28</v>
-    <v>195.16</v>
-    <v>195.2799</v>
+    <v>193</v>
+    <v>11.068300000000001</v>
+    <v>196.57</v>
+    <v>193.41</v>
+    <v>194.4</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>15852478</v>
-    <v>7067597</v>
+    <v>6955350</v>
+    <v>7752319</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12744,17 +12712,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.12</v>
-    <v>-2.6889999999999996E-3</v>
+    <v>-0.91</v>
+    <v>-2.0253999999999998E-2</v>
     <v>US</v>
-    <v>44.53</v>
+    <v>44.55</v>
     <v>Index</v>
     <v>7</v>
-    <v>44.2</v>
+    <v>43.98</v>
     <v>10 Y TSY YLD NDX</v>
     <v>44.53</v>
-    <v>44.63</v>
-    <v>44.51</v>
+    <v>44.93</v>
+    <v>44.02</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12996,9 +12964,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13611,7 +13579,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>77673.679999999993</v>
+        <v>76977.179999999993</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13619,7 +13587,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>323.42914232415444</v>
+        <v>321.98282836975369</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13635,7 +13603,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>78692.679999999993</v>
+        <v>77996.179999999993</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13643,7 +13611,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>507.95806113609035</v>
+        <v>507.13900561869167</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13652,7 +13620,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>195.16</v>
+        <v>193.41</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13676,14 +13644,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>195.2799</v>
+        <v>194.4</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>11.16475972540046</v>
+        <v>11.064645308924486</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13691,7 +13659,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>381.5574703663172</v>
+        <v>380.94261799560172</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13700,14 +13668,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.1200000000000001</v>
+        <v>-3.16</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>3.2025819509484879</v>
+        <v>3.1738643939995237</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13715,7 +13683,7 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>384.08408048572329</v>
+        <v>383.36402502509458</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13724,14 +13692,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.11990000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>0.10529950428510662</v>
+        <v>0.10625226852945251</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13739,7 +13707,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.96804714329638908</v>
+        <v>0.98213135321386991</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13748,14 +13716,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-5.7060000000000001E-3</v>
+        <v>-1.6076E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>8.9567534330805484E-2</v>
+        <v>9.0377953570135963E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13764,14 +13732,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>6.1439999999999997E-4</v>
+        <v>5.1190000000000003E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>0.11741429014307035</v>
+        <v>0.1184766706184872</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13812,7 +13780,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4390000000000001</v>
+        <v>1.4596</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13828,7 +13796,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>7067597</v>
+        <v>7752319</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13844,7 +13812,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.311898702366104E-2</v>
+        <v>-1.3237689403534919E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13954,7 +13922,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.51</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13969,7 +13937,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.4020000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19770,7 +19738,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>195.16</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19779,7 +19747,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>77673.679999999993</v>
+        <v>76977.179999999993</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19797,7 +19765,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.4020000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19806,7 +19774,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4390000000000001</v>
+        <v>1.4596</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19849,7 +19817,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.8808159710280101E-2</v>
+        <v>7.9464563109930886E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19858,7 +19826,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9211918402897199</v>
+        <v>0.92053543689006911</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19876,7 +19844,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.109265</v>
+        <v>0.10970200000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19885,7 +19853,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10382920718398343</v>
+        <v>0.10418620574541348</v>
       </c>
     </row>
   </sheetData>
@@ -20136,7 +20104,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>151016.64621285163</v>
+        <v>150376.24764668968</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20190,23 +20158,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7350.407980388406</v>
+        <v>7348.0314925630119</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7528.9835891361308</v>
+        <v>7524.1159286108023</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7573.703436352208</v>
+        <v>7566.359764237236</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7562.7002285352801</v>
+        <v>7552.9244714711022</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7573.7436602897133</v>
+        <v>7561.5080981124747</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20225,7 +20193,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>92154.259750311729</v>
+        <v>91615.225936167335</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20248,7 +20216,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10382920718398343</v>
+        <v>0.10418620574541348</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20263,7 +20231,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37589.538894701735</v>
+        <v>37552.93975499463</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20272,7 +20240,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>92154.259750311729</v>
+        <v>91615.225936167335</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20281,7 +20249,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>129743.79864501346</v>
+        <v>129168.16569116196</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20308,7 +20276,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>128724.79864501348</v>
+        <v>128149.16569116196</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20326,7 +20294,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>323.42914232415444</v>
+        <v>321.98282836975369</v>
       </c>
     </row>
   </sheetData>
@@ -21335,7 +21303,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10382920718398343</v>
+        <v>0.10418620574541348</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21370,7 +21338,7 @@
       </c>
       <c r="C43" s="24">
         <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>202167.30833216396</v>
+        <v>201841.32423623928</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21388,7 +21356,7 @@
       </c>
       <c r="C45" s="144">
         <f ca="1">C43/C44</f>
-        <v>507.95806113609035</v>
+        <v>507.13900561869167</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
@@ -21471,7 +21439,7 @@
       </c>
       <c r="C57" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10382920718398343</v>
+        <v>0.10418620574541348</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -21497,7 +21465,7 @@
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>151859.87320579425</v>
+        <v>151615.16196224949</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -21515,7 +21483,7 @@
       </c>
       <c r="C62" s="144">
         <f ca="1">C60/C61</f>
-        <v>381.5574703663172</v>
+        <v>380.94261799560172</v>
       </c>
     </row>
   </sheetData>
@@ -21579,7 +21547,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>323.42914232415444</v>
+        <v>321.98282836975369</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21588,7 +21556,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C45</f>
-        <v>507.95806113609035</v>
+        <v>507.13900561869167</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21606,7 +21574,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C62</f>
-        <v>381.5574703663172</v>
+        <v>380.94261799560172</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21615,7 +21583,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>384.08408048572329</v>
+        <v>383.36402502509458</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21624,7 +21592,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>195.16</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21633,7 +21601,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.96804714329638908</v>
+        <v>0.98213135321386991</v>
       </c>
     </row>
   </sheetData>
@@ -21886,7 +21854,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>78468.234266978048</v>
+        <v>78135.483236055225</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21940,23 +21908,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9311.6610545701133</v>
+        <v>9308.650466696703</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7507.8447685848205</v>
+        <v>7502.9907747916795</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6053.4562779753969</v>
+        <v>6047.5866795099491</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4880.8058822274988</v>
+        <v>4874.4968165313558</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3935.3164483338774</v>
+        <v>3928.9588514504289</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21975,7 +21943,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>47883.34414866662</v>
+        <v>47603.262232753259</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21991,7 +21959,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>195.16</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22000,7 +21968,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>197.37042356873954</v>
+        <v>196.60036638626477</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22039,7 +22007,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10382920718398343</v>
+        <v>0.10418620574541348</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22057,7 +22025,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>77673.679999999993</v>
+        <v>76977.179999999993</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22084,7 +22052,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>78692.679999999993</v>
+        <v>77996.179999999993</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22100,7 +22068,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31689.084431691706</v>
+        <v>31662.683588980115</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22109,7 +22077,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>47883.34414866662</v>
+        <v>47603.262232753259</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22118,7 +22086,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>79572.428580358333</v>
+        <v>79265.945821733374</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22145,7 +22113,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>78553.428580358333</v>
+        <v>78246.945821733374</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22163,7 +22131,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>197.37042356873954</v>
+        <v>196.60036638626477</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -29118,7 +29086,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>195.16</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29165,7 +29133,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>195.16</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30471,7 +30439,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>11.16475972540046</v>
+        <v>11.064645308924486</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30508,7 +30476,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.2025819509484879</v>
+        <v>3.1738643939995237</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30545,7 +30513,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>6.7436777218267059</v>
+        <v>6.6832071540197946</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30582,7 +30550,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>77673.679999999993</v>
+        <v>76977.179999999993</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30619,7 +30587,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>78692.679999999993</v>
+        <v>77996.179999999993</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30656,7 +30624,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>3.1229732518453841</v>
+        <v>3.0953321692197791</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30693,7 +30661,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>8.6570605060506036</v>
+        <v>8.5804378437843773</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30828,7 +30796,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="92">AC153/AC157</f>
-        <v>9.4967208705220685</v>
+        <v>9.4115637608509584</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30865,7 +30833,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="92"/>
-        <v>9.6955895152961222</v>
+        <v>9.6097749503657663</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -30902,7 +30870,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="95">AC157/AC153</f>
-        <v>0.10529950428510662</v>
+        <v>0.10625226852945251</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30939,7 +30907,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>8.9567534330805484E-2</v>
+        <v>9.0377953570135963E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31013,7 +30981,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>0.11741429014307035</v>
+        <v>0.1184766706184872</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31050,7 +31018,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>0.11741429014307035</v>
+        <v>0.1184766706184872</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31553,7 +31521,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.311898702366104E-2</v>
+        <v>-1.3237689403534919E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32830,7 +32798,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>195.16</v>
+        <v>193.41</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -32846,7 +32814,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>77673.679999999993</v>
+        <v>76977.179999999993</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32866,7 +32834,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>78692.679999999993</v>
+        <v>77996.179999999993</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -32886,7 +32854,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>11.16475972540046</v>
+        <v>11.064645308924486</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -32906,7 +32874,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.2025819509484879</v>
+        <v>3.1738643939995237</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -32926,7 +32894,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>6.7436777218267059</v>
+        <v>6.6832071540197946</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32946,7 +32914,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.1229732518453841</v>
+        <v>3.0953321692197791</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32955,7 +32923,7 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>8.6570605060506036</v>
+        <v>8.5804378437843773</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33191,7 +33159,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>8.9567534330805484E-2</v>
+        <v>9.0377953570135963E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33207,7 +33175,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>0.10529950428510662</v>
+        <v>0.10625226852945251</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -33239,7 +33207,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.11741429014307035</v>
+        <v>0.1184766706184872</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33248,7 +33216,7 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.11741429014307035</v>
+        <v>0.1184766706184872</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33292,7 +33260,7 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-1.311898702366104E-2</v>
+        <v>-1.3237689403534919E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33471,7 +33439,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>195.16</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33500,7 +33468,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>77673.679999999993</v>
+        <v>76977.179999999993</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33529,7 +33497,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>78692.679999999993</v>
+        <v>77996.179999999993</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33558,7 +33526,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>11.16475972540046</v>
+        <v>11.064645308924486</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33587,7 +33555,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.2025819509484879</v>
+        <v>3.1738643939995237</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33616,7 +33584,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>6.7436777218267059</v>
+        <v>6.6832071540197946</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33645,7 +33613,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.1229732518453841</v>
+        <v>3.0953321692197791</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33674,7 +33642,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>8.6570605060506036</v>
+        <v>8.5804378437843773</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34447,7 +34415,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>8.9567534330805484E-2</v>
+        <v>9.0377953570135963E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34476,7 +34444,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>0.10529950428510662</v>
+        <v>0.10625226852945251</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34534,7 +34502,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.11741429014307035</v>
+        <v>0.1184766706184872</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34563,7 +34531,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.11741429014307035</v>
+        <v>0.1184766706184872</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34799,7 +34767,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-1.311898702366104E-2</v>
+        <v>-1.3237689403534919E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAAEA81-2FB0-F448-A9A9-8D52F4148653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A67411F-25AC-2043-8BD2-E2CEB6E943D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2289,9 +2289,6 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="40" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2301,6 +2298,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2308,12 +2314,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12657,38 +12657,38 @@
     <v>Powered by Refinitiv</v>
     <v>392.58</v>
     <v>190.12</v>
-    <v>1.4596</v>
-    <v>-3.16</v>
-    <v>-1.6076E-2</v>
-    <v>0.99</v>
-    <v>5.1190000000000003E-3</v>
+    <v>1.4394</v>
+    <v>-1.41</v>
+    <v>-6.8300000000000001E-3</v>
+    <v>-0.22</v>
+    <v>-1.0730000000000002E-3</v>
     <v>USD</v>
-    <v>Adobe Inc. is a global technology company. The Company's products, services and solutions are used around the world to imagine, create, manage, deliver, measure, optimize and engage with content across surfaces and fuel digital experiences. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment is centered around Adobe Creative Cloud and Adobe Document Cloud, which include Adobe Express, Adobe Firefly, Photoshop and other products, offering a variety of tools for creative professionals, communicators and other consumers. The Digital Experience segment provides an integrated platform and set of products, services and solutions through Adobe Experience Cloud. The Publishing and Advertising segment contains legacy products and services. In addition, its Adobe GenStudio solution allows businesses to simplify their content supply chain process with generative artificial intelligence (AI) capabilities and intelligent automation.</v>
+    <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>199.29900000000001</v>
+    <v>205.6</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46198.911558240623</v>
+    <v>46203.951406214845</v>
     <v>4</v>
-    <v>191.8</v>
-    <v>76880475000</v>
+    <v>201.31</v>
+    <v>81495450000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>193</v>
-    <v>11.068300000000001</v>
-    <v>196.57</v>
-    <v>193.41</v>
-    <v>194.4</v>
+    <v>204.095</v>
+    <v>11.732699999999999</v>
+    <v>206.43</v>
+    <v>205.02</v>
+    <v>204.8</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>6955350</v>
-    <v>7752319</v>
+    <v>6116780</v>
+    <v>8107787</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12712,17 +12712,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.91</v>
-    <v>-2.0253999999999998E-2</v>
+    <v>0.02</v>
+    <v>4.5750000000000001E-4</v>
     <v>US</v>
-    <v>44.55</v>
+    <v>43.9</v>
     <v>Index</v>
     <v>7</v>
-    <v>43.98</v>
+    <v>43.67</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.53</v>
-    <v>44.93</v>
-    <v>44.02</v>
+    <v>43.78</v>
+    <v>43.72</v>
+    <v>43.74</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13553,18 +13553,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>76977.179999999993</v>
+        <v>81597.960000000006</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>321.98282836975369</v>
+        <v>325.28494816353077</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>77996.179999999993</v>
+        <v>82616.960000000006</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>507.13900561869167</v>
+        <v>509.0011235350978</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>193.41</v>
+        <v>205.02</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13644,14 +13644,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>194.4</v>
+        <v>204.8</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>11.064645308924486</v>
+        <v>11.728832951945083</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>380.94261799560172</v>
+        <v>382.34048125533576</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13668,14 +13668,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.16</v>
+        <v>-1.41</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>3.1738643939995237</v>
+        <v>3.3643848718152238</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>383.36402502509458</v>
+        <v>385.0045502675739</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13692,14 +13692,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.99</v>
+        <v>-0.22</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>0.10625226852945251</v>
+        <v>0.10023534902098041</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.98213135321386991</v>
+        <v>0.87788776835222848</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13716,14 +13716,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.6076E-2</v>
+        <v>-6.8300000000000001E-3</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>9.0377953570135963E-2</v>
+        <v>8.52599746366208E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13732,14 +13732,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>5.1190000000000003E-3</v>
+        <v>-1.0730000000000002E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>0.1184766706184872</v>
+        <v>0.11176750006985468</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4596</v>
+        <v>1.4394</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>7752319</v>
+        <v>8107787</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.3237689403534919E-2</v>
+        <v>-1.2488057299471701E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13825,10 +13825,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="234" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="186" t="s">
         <v>302</v>
       </c>
@@ -13901,14 +13901,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.02</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.4020000000000004E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13957,15 +13957,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="235" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13984,24 +13984,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="235" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14016,24 +14016,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14059,28 +14059,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="235"/>
+      <c r="C59" s="235"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14150,36 +14150,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15199,35 +15199,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -17168,20 +17168,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -18574,6 +18574,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18581,12 +18587,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18624,20 +18624,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -19646,16 +19646,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19718,10 +19718,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>193.41</v>
+        <v>205.02</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>76977.179999999993</v>
+        <v>81597.960000000006</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.4020000000000004E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4596</v>
+        <v>1.4394</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19806,10 +19806,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.9464563109930886E-2</v>
+        <v>7.5303457635600618E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92053543689006911</v>
+        <v>0.92469654236439935</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.10970200000000001</v>
+        <v>0.108513</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10418620574541348</v>
+        <v>0.1033755722097264</v>
       </c>
     </row>
   </sheetData>
@@ -19898,20 +19898,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20104,7 +20104,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>150376.24764668968</v>
+        <v>151838.30692955205</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20158,23 +20158,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7348.0314925630119</v>
+        <v>7353.4299814358683</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7524.1159286108023</v>
+        <v>7535.1757007941287</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7566.359764237236</v>
+        <v>7583.0486935099889</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7552.9244714711022</v>
+        <v>7575.1450268730132</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7561.5080981124747</v>
+        <v>7589.3255769811822</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20193,14 +20193,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>91615.225936167335</v>
+        <v>92846.284389491077</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="235" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20216,14 +20216,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10418620574541348</v>
+        <v>0.1033755722097264</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="235" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37552.93975499463</v>
+        <v>37636.124979594177</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>91615.225936167335</v>
+        <v>92846.284389491077</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>129168.16569116196</v>
+        <v>130482.40936908525</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>128149.16569116196</v>
+        <v>129463.40936908525</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20294,7 +20294,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>321.98282836975369</v>
+        <v>325.28494816353077</v>
       </c>
     </row>
   </sheetData>
@@ -20337,20 +20337,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21282,10 +21282,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21303,7 +21303,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10418620574541348</v>
+        <v>0.1033755722097264</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="C43" s="24">
         <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>201841.32423623928</v>
+        <v>202582.44716696892</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21356,14 +21356,14 @@
       </c>
       <c r="C45" s="144">
         <f ca="1">C43/C44</f>
-        <v>507.13900561869167</v>
+        <v>509.0011235350978</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="232" t="s">
+      <c r="B47" s="235" t="s">
         <v>211</v>
       </c>
-      <c r="C47" s="232"/>
+      <c r="C47" s="235"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -21419,10 +21419,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="232" t="s">
+      <c r="B55" s="235" t="s">
         <v>328</v>
       </c>
-      <c r="C55" s="232"/>
+      <c r="C55" s="235"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="C57" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10418620574541348</v>
+        <v>0.1033755722097264</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>151615.16196224949</v>
+        <v>152171.51153962364</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="C62" s="144">
         <f ca="1">C60/C61</f>
-        <v>380.94261799560172</v>
+        <v>382.34048125533576</v>
       </c>
     </row>
   </sheetData>
@@ -21535,10 +21535,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>321.98282836975369</v>
+        <v>325.28494816353077</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C45</f>
-        <v>507.13900561869167</v>
+        <v>509.0011235350978</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C62</f>
-        <v>380.94261799560172</v>
+        <v>382.34048125533576</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>383.36402502509458</v>
+        <v>385.0045502675739</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>193.41</v>
+        <v>205.02</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.98213135321386991</v>
+        <v>0.87788776835222848</v>
       </c>
     </row>
   </sheetData>
@@ -21666,20 +21666,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21854,7 +21854,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>78135.483236055225</v>
+        <v>78895.169093190168</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21908,23 +21908,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9308.650466696703</v>
+        <v>9315.4893930154904</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7502.9907747916795</v>
+        <v>7514.0194949031347</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6047.5866795099491</v>
+        <v>6060.9256892200374</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4874.4968165313558</v>
+        <v>4888.8374903958038</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3928.9588514504289</v>
+        <v>3943.4128106882063</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21943,7 +21943,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>47603.262232753259</v>
+        <v>48242.920081965458</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>193.41</v>
+        <v>205.02</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>196.60036638626477</v>
+        <v>198.35830392007065</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10418620574541348</v>
+        <v>0.1033755722097264</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>76977.179999999993</v>
+        <v>81597.960000000006</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>77996.179999999993</v>
+        <v>82616.960000000006</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22068,7 +22068,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31662.683588980115</v>
+        <v>31722.684878222673</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>47603.262232753259</v>
+        <v>48242.920081965458</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>79265.945821733374</v>
+        <v>79965.604960188124</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22113,7 +22113,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>78246.945821733374</v>
+        <v>78946.604960188124</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>196.60036638626477</v>
+        <v>198.35830392007065</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22578,17 +22578,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29086,7 +29086,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>193.41</v>
+        <v>205.02</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29133,7 +29133,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>193.41</v>
+        <v>205.02</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30439,7 +30439,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>11.064645308924486</v>
+        <v>11.728832951945083</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30476,7 +30476,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.1738643939995237</v>
+        <v>3.3643848718152238</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30513,7 +30513,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>6.6832071540197946</v>
+        <v>7.0843861781559303</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30550,7 +30550,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>76977.179999999993</v>
+        <v>81597.960000000006</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30587,7 +30587,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>77996.179999999993</v>
+        <v>82616.960000000006</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30624,7 +30624,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>3.0953321692197791</v>
+        <v>3.2787110088102231</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30661,7 +30661,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>8.5804378437843773</v>
+        <v>9.0887744774477461</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30796,7 +30796,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="92">AC153/AC157</f>
-        <v>9.4115637608509584</v>
+        <v>9.9765203570118608</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30833,7 +30833,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="92"/>
-        <v>9.6097749503657663</v>
+        <v>10.179093292560875</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -30870,7 +30870,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="95">AC157/AC153</f>
-        <v>0.10625226852945251</v>
+        <v>0.10023534902098041</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30907,7 +30907,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>9.0377953570135963E-2</v>
+        <v>8.52599746366208E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30981,7 +30981,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>0.1184766706184872</v>
+        <v>0.11176750006985468</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31018,7 +31018,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>0.1184766706184872</v>
+        <v>0.11176750006985468</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31521,7 +31521,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.3237689403534919E-2</v>
+        <v>-1.2488057299471701E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32782,15 +32782,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32798,7 +32798,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>193.41</v>
+        <v>205.02</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>76977.179999999993</v>
+        <v>81597.960000000006</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32834,7 +32834,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>77996.179999999993</v>
+        <v>82616.960000000006</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -32854,7 +32854,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>11.064645308924486</v>
+        <v>11.728832951945083</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.1738643939995237</v>
+        <v>3.3643848718152238</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>6.6832071540197946</v>
+        <v>7.0843861781559303</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32914,7 +32914,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.0953321692197791</v>
+        <v>3.2787110088102231</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32923,18 +32923,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>8.5804378437843773</v>
+        <v>9.0887744774477461</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32985,14 +32985,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="235" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33061,14 +33061,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="235" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33144,14 +33144,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33159,7 +33159,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>9.0377953570135963E-2</v>
+        <v>8.52599746366208E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>0.10625226852945251</v>
+        <v>0.10023534902098041</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -33207,7 +33207,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.1184766706184872</v>
+        <v>0.11176750006985468</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33216,18 +33216,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.1184766706184872</v>
+        <v>0.11176750006985468</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="235" t="s">
         <v>285</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33260,18 +33260,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-1.3237689403534919E-2</v>
+        <v>-1.2488057299471701E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="235" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>309</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33439,7 +33439,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>193.41</v>
+        <v>205.02</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33468,7 +33468,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>76977.179999999993</v>
+        <v>81597.960000000006</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>77996.179999999993</v>
+        <v>82616.960000000006</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33526,7 +33526,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>11.064645308924486</v>
+        <v>11.728832951945083</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33555,7 +33555,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.1738643939995237</v>
+        <v>3.3643848718152238</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33584,7 +33584,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>6.6832071540197946</v>
+        <v>7.0843861781559303</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33613,7 +33613,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.0953321692197791</v>
+        <v>3.2787110088102231</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33642,7 +33642,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>8.5804378437843773</v>
+        <v>9.0887744774477461</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34415,7 +34415,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>9.0377953570135963E-2</v>
+        <v>8.52599746366208E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34444,7 +34444,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>0.10625226852945251</v>
+        <v>0.10023534902098041</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34502,7 +34502,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.1184766706184872</v>
+        <v>0.11176750006985468</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34531,7 +34531,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.1184766706184872</v>
+        <v>0.11176750006985468</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34767,7 +34767,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-1.3237689403534919E-2</v>
+        <v>-1.2488057299471701E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35253,14 +35253,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="238" t="s">
         <v>319</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="239"/>
+      <c r="F3" s="240" t="s">
         <v>320</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="239"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35327,19 +35327,19 @@
       <c r="B7" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="236">
         <f>Statement!AA89</f>
         <v>3.4385745545482967E-2</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="237"/>
+      <c r="F7" s="236">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1268516941937681</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="237"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -35366,19 +35366,19 @@
       <c r="B9" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="236">
         <f>Statement!AA90</f>
         <v>7.6807228915662648E-2</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="237"/>
+      <c r="F9" s="236">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1206896551724138</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="237"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -35405,19 +35405,19 @@
       <c r="B11" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="236">
         <f>Statement!AA91</f>
         <v>2.9473317056156263E-2</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="237"/>
+      <c r="F11" s="236">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12760267430754538</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="237"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -35444,19 +35444,19 @@
       <c r="B13" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="236">
         <f>Statement!AA95</f>
         <v>0.10524728588661038</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="237"/>
+      <c r="F13" s="236">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.172424824056302</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="237"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -35483,19 +35483,19 @@
       <c r="B15" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="236">
         <f>Statement!AA96</f>
         <v>-7.4441687344913146E-2</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="237"/>
+      <c r="F15" s="236">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.1166429587482217E-2</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -35522,19 +35522,19 @@
       <c r="B17" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="236">
         <f>Statement!AA98</f>
         <v>-9.3700370566437263E-2</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="237"/>
+      <c r="F17" s="236">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2418687167356593E-2</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="237"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -35561,22 +35561,22 @@
       <c r="B19" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="236">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.1897810218978103E-2</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="237"/>
+      <c r="F19" s="236">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.2937062937062943E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="237"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -35603,22 +35603,22 @@
       <c r="B21" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="236">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-7.6086956521739066E-2</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="237"/>
+      <c r="F21" s="236">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>7.8680203045685293E-2</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="237"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35666,22 +35666,22 @@
       <c r="B25" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="236">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5172636334301385E-2</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="237"/>
+      <c r="F25" s="236">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13738698812267328</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="237"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -35708,22 +35708,22 @@
       <c r="B27" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="236">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-1.1111111111111112E-2</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="237"/>
+      <c r="F27" s="236">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="237"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35750,49 +35750,49 @@
       <c r="B29" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="236">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="237"/>
+      <c r="F29" s="236">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.21527777777777779</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A67411F-25AC-2043-8BD2-E2CEB6E943D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082A2F33-8027-0648-8349-622539FC8545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -12655,13 +12655,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>392.58</v>
+    <v>386.88</v>
     <v>190.12</v>
-    <v>1.4394</v>
-    <v>-1.41</v>
-    <v>-6.8300000000000001E-3</v>
-    <v>-0.22</v>
-    <v>-1.0730000000000002E-3</v>
+    <v>1.4171</v>
+    <v>8.74</v>
+    <v>4.1425999999999998E-2</v>
+    <v>-0.02</v>
+    <v>-9.1020000000000006E-5</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12669,26 +12669,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>205.6</v>
+    <v>222.15</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46203.951406214845</v>
+    <v>46205.999882488279</v>
     <v>4</v>
-    <v>201.31</v>
-    <v>81495450000</v>
+    <v>213.73500000000001</v>
+    <v>87338700000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>204.095</v>
-    <v>11.732699999999999</v>
-    <v>206.43</v>
-    <v>205.02</v>
-    <v>204.8</v>
+    <v>215.55</v>
+    <v>12.0738</v>
+    <v>210.98</v>
+    <v>219.72</v>
+    <v>219.7</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>6116780</v>
-    <v>8107787</v>
+    <v>7907502</v>
+    <v>8313078</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12712,17 +12712,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.02</v>
-    <v>4.5750000000000001E-4</v>
+    <v>0.1</v>
+    <v>2.235E-3</v>
     <v>US</v>
-    <v>43.9</v>
+    <v>45.05</v>
     <v>Index</v>
     <v>7</v>
-    <v>43.67</v>
+    <v>44.53</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>43.78</v>
-    <v>43.72</v>
-    <v>43.74</v>
+    <v>45.03</v>
+    <v>44.75</v>
+    <v>44.85</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12964,9 +12964,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>81597.960000000006</v>
+        <v>87448.56</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>325.28494816353077</v>
+        <v>323.57249540330463</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>82616.960000000006</v>
+        <v>88467.56</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>509.0011235350978</v>
+        <v>508.03894820809109</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>205.02</v>
+        <v>219.72</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13644,14 +13644,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>204.8</v>
+        <v>219.7</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>11.728832951945083</v>
+        <v>12.569794050343251</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>382.34048125533576</v>
+        <v>381.61819104632423</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13668,14 +13668,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.41</v>
+        <v>8.74</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>3.3643848718152238</v>
+        <v>3.6056123501865227</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>385.0045502675739</v>
+        <v>384.15532069351281</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13692,14 +13692,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.22</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>0.10023534902098041</v>
+        <v>9.3529270236125103E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.87788776835222848</v>
+        <v>0.74838576685560176</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13716,14 +13716,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.8300000000000001E-3</v>
+        <v>4.1425999999999998E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>8.52599746366208E-2</v>
+        <v>7.9555798288731092E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13732,14 +13732,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.0730000000000002E-3</v>
+        <v>-9.1020000000000006E-5</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>0.11176750006985468</v>
+        <v>0.10428988196032045</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="C11" s="211" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>392.58</v>
+        <v>386.88</v>
       </c>
       <c r="E11" s="188" t="s">
         <v>295</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4394</v>
+        <v>1.4171</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>8107787</v>
+        <v>8313078</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.2488057299471701E-2</v>
+        <v>-1.1652564662013875E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>43.74</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18492,23 +18492,23 @@
         <v>60</v>
       </c>
       <c r="C45" s="116">
-        <f>-Statement!M60</f>
+        <f>-Statement!M110</f>
         <v>348</v>
       </c>
       <c r="D45" s="116">
-        <f>-Statement!N60</f>
+        <f>-Statement!N110</f>
         <v>442</v>
       </c>
       <c r="E45" s="116">
-        <f>-Statement!O60</f>
+        <f>-Statement!O110</f>
         <v>360</v>
       </c>
       <c r="F45" s="116">
-        <f>-Statement!P60</f>
+        <f>-Statement!P110</f>
         <v>183</v>
       </c>
       <c r="G45" s="117">
-        <f>-Statement!Q60</f>
+        <f>-Statement!Q110</f>
         <v>179</v>
       </c>
       <c r="H45" s="25">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>205.02</v>
+        <v>219.72</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>81597.960000000006</v>
+        <v>87448.56</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4394</v>
+        <v>1.4171</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.5303457635600618E-2</v>
+        <v>7.0621198730285051E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92469654236439935</v>
+        <v>0.92937880126971495</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.108513</v>
+        <v>0.10861949999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1033755722097264</v>
+        <v>0.10379398880135898</v>
       </c>
     </row>
   </sheetData>
@@ -20104,7 +20104,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>151838.30692955205</v>
+        <v>151080.11809317462</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20158,23 +20158,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7353.4299814358683</v>
+        <v>7350.6425073774326</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7535.1757007941287</v>
+        <v>7529.4640462824264</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7583.0486935099889</v>
+        <v>7574.428414288891</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7575.1450268730132</v>
+        <v>7563.665476835662</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7589.3255769811822</v>
+        <v>7574.9520018218518</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20193,7 +20193,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>92846.284389491077</v>
+        <v>92207.700723908973</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1033755722097264</v>
+        <v>0.10379398880135898</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37636.124979594177</v>
+        <v>37593.152446606262</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>92846.284389491077</v>
+        <v>92207.700723908973</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>130482.40936908525</v>
+        <v>129800.85317051524</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>129463.40936908525</v>
+        <v>128781.85317051524</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20294,7 +20294,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>325.28494816353077</v>
+        <v>323.57249540330463</v>
       </c>
     </row>
   </sheetData>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1033755722097264</v>
+        <v>0.10379398880135898</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="C43" s="24">
         <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>202582.44716696892</v>
+        <v>202199.50138682025</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="C45" s="144">
         <f ca="1">C43/C44</f>
-        <v>509.0011235350978</v>
+        <v>508.03894820809109</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="C57" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1033755722097264</v>
+        <v>0.10379398880135898</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>152171.51153962364</v>
+        <v>151884.04003643704</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="C62" s="144">
         <f ca="1">C60/C61</f>
-        <v>382.34048125533576</v>
+        <v>381.61819104632423</v>
       </c>
     </row>
   </sheetData>
@@ -21547,7 +21547,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>325.28494816353077</v>
+        <v>323.57249540330463</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C45</f>
-        <v>509.0011235350978</v>
+        <v>508.03894820809109</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C62</f>
-        <v>382.34048125533576</v>
+        <v>381.61819104632423</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>385.0045502675739</v>
+        <v>384.15532069351281</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>205.02</v>
+        <v>219.72</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.87788776835222848</v>
+        <v>0.74838576685560176</v>
       </c>
     </row>
   </sheetData>
@@ -21854,7 +21854,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>78895.169093190168</v>
+        <v>78501.214249645185</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21908,23 +21908,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9315.4893930154904</v>
+        <v>9311.9581585996839</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7514.0194949031347</v>
+        <v>7508.3238767711573</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6060.9256892200374</v>
+        <v>6054.0357332285757</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4888.8374903958038</v>
+        <v>4881.4288329514402</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3943.4128106882063</v>
+        <v>3935.944302473114</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21943,7 +21943,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>48242.920081965458</v>
+        <v>47911.112073202392</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>205.02</v>
+        <v>219.72</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>198.35830392007065</v>
+        <v>197.44674114880993</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1033755722097264</v>
+        <v>0.10379398880135898</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>81597.960000000006</v>
+        <v>87448.56</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>82616.960000000006</v>
+        <v>88467.56</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22068,7 +22068,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31722.684878222673</v>
+        <v>31691.69090402397</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>48242.920081965458</v>
+        <v>47911.112073202392</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>79965.604960188124</v>
+        <v>79602.802977226354</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22113,7 +22113,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>78946.604960188124</v>
+        <v>78583.802977226354</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>198.35830392007065</v>
+        <v>197.44674114880993</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -29086,7 +29086,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>205.02</v>
+        <v>219.72</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29133,7 +29133,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>205.02</v>
+        <v>219.72</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30439,7 +30439,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>11.728832951945083</v>
+        <v>12.569794050343251</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30476,7 +30476,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.3643848718152238</v>
+        <v>3.6056123501865227</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30513,7 +30513,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.0843861781559303</v>
+        <v>7.5923389477339809</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30550,7 +30550,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>81597.960000000006</v>
+        <v>87448.56</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30587,7 +30587,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>82616.960000000006</v>
+        <v>88467.56</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30624,7 +30624,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>3.2787110088102231</v>
+        <v>3.5108961028653067</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30661,7 +30661,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>9.0887744774477461</v>
+        <v>9.7324048404840475</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30796,7 +30796,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="92">AC153/AC157</f>
-        <v>9.9765203570118608</v>
+        <v>10.691840078249175</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30833,7 +30833,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="92"/>
-        <v>10.179093292560875</v>
+        <v>10.899935637975865</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -30870,7 +30870,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="95">AC157/AC153</f>
-        <v>0.10023534902098041</v>
+        <v>9.3529270236125103E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30907,7 +30907,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>8.52599746366208E-2</v>
+        <v>7.9555798288731092E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30981,7 +30981,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>0.11176750006985468</v>
+        <v>0.10428988196032045</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31018,7 +31018,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>0.11176750006985468</v>
+        <v>0.10428988196032045</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31521,7 +31521,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.2488057299471701E-2</v>
+        <v>-1.1652564662013875E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32798,7 +32798,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>205.02</v>
+        <v>219.72</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>81597.960000000006</v>
+        <v>87448.56</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32834,7 +32834,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>82616.960000000006</v>
+        <v>88467.56</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -32854,7 +32854,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>11.728832951945083</v>
+        <v>12.569794050343251</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.3643848718152238</v>
+        <v>3.6056123501865227</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>7.0843861781559303</v>
+        <v>7.5923389477339809</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32914,7 +32914,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.2787110088102231</v>
+        <v>3.5108961028653067</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32923,7 +32923,7 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>9.0887744774477461</v>
+        <v>9.7324048404840475</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33159,7 +33159,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>8.52599746366208E-2</v>
+        <v>7.9555798288731092E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>0.10023534902098041</v>
+        <v>9.3529270236125103E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -33207,7 +33207,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.11176750006985468</v>
+        <v>0.10428988196032045</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.11176750006985468</v>
+        <v>0.10428988196032045</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33260,7 +33260,7 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-1.2488057299471701E-2</v>
+        <v>-1.1652564662013875E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33439,7 +33439,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>205.02</v>
+        <v>219.72</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33468,7 +33468,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>81597.960000000006</v>
+        <v>87448.56</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>82616.960000000006</v>
+        <v>88467.56</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33526,7 +33526,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>11.728832951945083</v>
+        <v>12.569794050343251</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33555,7 +33555,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.3643848718152238</v>
+        <v>3.6056123501865227</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33584,7 +33584,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>7.0843861781559303</v>
+        <v>7.5923389477339809</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33613,7 +33613,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.2787110088102231</v>
+        <v>3.5108961028653067</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33642,7 +33642,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>9.0887744774477461</v>
+        <v>9.7324048404840475</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34415,7 +34415,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>8.52599746366208E-2</v>
+        <v>7.9555798288731092E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34444,7 +34444,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>0.10023534902098041</v>
+        <v>9.3529270236125103E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34502,7 +34502,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.11176750006985468</v>
+        <v>0.10428988196032045</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34531,7 +34531,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.11176750006985468</v>
+        <v>0.10428988196032045</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34767,7 +34767,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-1.2488057299471701E-2</v>
+        <v>-1.1652564662013875E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082A2F33-8027-0648-8349-622539FC8545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712170F3-ADB1-094E-B9F9-490969C368A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,7 +128,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -138,19 +159,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="407">
   <si>
     <t>Ticker</t>
   </si>
@@ -2289,6 +2319,9 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="40" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2296,9 +2329,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12618,7 +12648,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12655,13 +12685,11 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>386.88</v>
+    <v>386.60109999999997</v>
     <v>190.12</v>
-    <v>1.4171</v>
-    <v>8.74</v>
-    <v>4.1425999999999998E-2</v>
-    <v>-0.02</v>
-    <v>-9.1020000000000006E-5</v>
+    <v>1.4237</v>
+    <v>7.6150000000000002</v>
+    <v>3.492E-2</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12669,36 +12697,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>222.15</v>
+    <v>230.74</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46205.999882488279</v>
+    <v>46210.767642164064</v>
     <v>4</v>
-    <v>213.73500000000001</v>
-    <v>87338700000</v>
+    <v>220.29</v>
+    <v>89709787500</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>215.55</v>
-    <v>12.0738</v>
-    <v>210.98</v>
-    <v>219.72</v>
-    <v>219.7</v>
+    <v>221.16</v>
+    <v>12.9153</v>
+    <v>218.07</v>
+    <v>225.685</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>7907502</v>
-    <v>8313078</v>
+    <v>5805189</v>
+    <v>8549189</v>
     <v>1997</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12712,28 +12754,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.1</v>
-    <v>2.235E-3</v>
+    <v>-0.06</v>
+    <v>-1.338E-3</v>
     <v>US</v>
-    <v>45.05</v>
+    <v>44.91</v>
     <v>Index</v>
-    <v>7</v>
-    <v>44.53</v>
+    <v>10</v>
+    <v>44.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.03</v>
-    <v>44.75</v>
+    <v>44.57</v>
     <v>44.85</v>
+    <v>44.79</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12767,8 +12809,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12790,7 +12830,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12800,6 +12839,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12835,7 +12879,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12846,16 +12890,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12956,19 +12997,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13049,9 +13084,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13059,9 +13091,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13553,18 +13582,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13579,7 +13608,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>87448.56</v>
+        <v>89822.63</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13587,7 +13616,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>323.57249540330463</v>
+        <v>322.19590416860262</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13603,7 +13632,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>88467.56</v>
+        <v>90841.63</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13611,7 +13640,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>508.03894820809109</v>
+        <v>438.66153573978517</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13620,7 +13649,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>219.72</v>
+        <v>225.685</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13642,16 +13671,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>219.7</v>
+      <c r="C6" s="210" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>12.569794050343251</v>
+        <v>12.911041189931353</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13659,7 +13688,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>381.61819104632423</v>
+        <v>321.4632364868404</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13668,14 +13697,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>8.74</v>
+        <v>7.6150000000000002</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>3.6056123501865227</v>
+        <v>3.7034981943011349</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13683,23 +13712,23 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>384.15532069351281</v>
+        <v>351.42808112788987</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.02</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>9.3529270236125103E-2</v>
+        <v>9.1057231345820083E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13707,7 +13736,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.74838576685560176</v>
+        <v>0.55716188992573656</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13716,30 +13745,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.1425999999999998E-2</v>
+        <v>3.492E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>7.9555798288731092E-2</v>
+        <v>7.7453087267651807E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-9.1020000000000006E-5</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>0.10428988196032045</v>
+        <v>0.10153343316712057</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13748,7 +13777,7 @@
       </c>
       <c r="C11" s="211" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>386.88</v>
+        <v>386.60109999999997</v>
       </c>
       <c r="E11" s="188" t="s">
         <v>295</v>
@@ -13780,7 +13809,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4171</v>
+        <v>1.4237</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13796,7 +13825,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>8313078</v>
+        <v>8549189</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13812,7 +13841,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1652564662013875E-2</v>
+        <v>-1.1344579868124547E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13825,10 +13854,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="235" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="186" t="s">
         <v>302</v>
       </c>
@@ -13901,14 +13930,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -13917,12 +13946,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="2">
+      <c r="E26" s="187" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.85</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13937,7 +13966,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13957,15 +13986,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="232" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13984,24 +14013,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="232" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14016,24 +14045,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="232"/>
+      <c r="C49" s="232"/>
+      <c r="D49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="232"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14059,13 +14088,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="235"/>
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
+      <c r="H59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14150,36 +14179,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15199,35 +15228,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -17168,20 +17197,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -18624,20 +18653,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -19718,10 +19747,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19738,7 +19767,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>219.72</v>
+        <v>225.685</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19747,7 +19776,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>87448.56</v>
+        <v>89822.63</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19765,7 +19794,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19774,7 +19803,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4171</v>
+        <v>1.4237</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19806,10 +19835,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19817,7 +19846,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.0621198730285051E-2</v>
+        <v>6.8883209839404158E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19826,7 +19855,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92937880126971495</v>
+        <v>0.9311167901605959</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19844,7 +19873,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.10861949999999999</v>
+        <v>0.10885649999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19853,7 +19882,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10379398880135898</v>
+        <v>0.10413341939254649</v>
       </c>
     </row>
   </sheetData>
@@ -19898,20 +19927,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20104,7 +20133,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>151080.11809317462</v>
+        <v>150470.59557321406</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20158,23 +20187,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7350.6425073774326</v>
+        <v>7348.3827868689641</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7529.4640462824264</v>
+        <v>7524.8353708908762</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7574.428414288891</v>
+        <v>7567.4450125167714</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7563.665476835662</v>
+        <v>7554.3689343273445</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7574.9520018218518</v>
+        <v>7563.3157718683815</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20193,14 +20222,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>92207.700723908973</v>
+        <v>91694.621982631506</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="232" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20216,14 +20245,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10379398880135898</v>
+        <v>0.10413341939254649</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="232" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20231,7 +20260,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37593.152446606262</v>
+        <v>37558.347876472333</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20240,7 +20269,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>92207.700723908973</v>
+        <v>91694.621982631506</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20249,7 +20278,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>129800.85317051524</v>
+        <v>129252.96985910385</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20276,7 +20305,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>128781.85317051524</v>
+        <v>128233.96985910385</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20294,7 +20323,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>323.57249540330463</v>
+        <v>322.19590416860262</v>
       </c>
     </row>
   </sheetData>
@@ -20315,7 +20344,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -20337,20 +20366,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21282,10 +21311,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="232"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21303,7 +21332,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10379398880135898</v>
+        <v>0.10413341939254649</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21311,187 +21340,232 @@
         <v>208</v>
       </c>
       <c r="C40" s="105">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41" s="24">
+        <f>(C38*C40)</f>
+        <v>287537.60556036036</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C42" s="24">
+        <f ca="1">C41/(1+C39)^5-G30+G31</f>
+        <v>175606.29122443451</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="88">
+        <f>Statement!AC107</f>
+        <v>5626</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="88">
+        <f>Statement!AC108</f>
+        <v>6645</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C45" s="24">
+        <f ca="1">C42+C43-C44</f>
+        <v>174587.29122443451</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="88">
+        <f>Statement!AC78</f>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="143" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" s="144">
+        <f ca="1">C45/C46</f>
+        <v>438.66153573978517</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="232" t="s">
+        <v>211</v>
+      </c>
+      <c r="C49" s="232"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C50" s="64">
+        <f>L6</f>
+        <v>39388.713090460325</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C51" s="137">
+        <f>Overview!C29</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="C52" s="105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C53" s="24">
         <f>L18</f>
         <v>378.13734504559994</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" s="24">
+        <f>(C50*C52)/C53</f>
+        <v>520.82548320783292</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="143" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" s="144">
+        <f>C54/(1+C51)^5</f>
+        <v>323.39164811633128</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="232" t="s">
+        <v>328</v>
+      </c>
+      <c r="C57" s="232"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="64">
+        <f>L8</f>
+        <v>12411.378160399478</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C59" s="137">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.10413341939254649</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="39" t="s">
+        <v>360</v>
+      </c>
+      <c r="C60" s="105">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C42" s="24">
-        <f>(C38*C40)</f>
-        <v>330668.24639441445</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B43" s="1" t="s">
+      <c r="C61" s="24">
+        <f>(C58*C60)</f>
+        <v>210993.42872679111</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C43" s="24">
-        <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>202199.50138682025</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
+      <c r="C62" s="24">
+        <f ca="1">C61/(1+C59)^5-G30+G31</f>
+        <v>128961.36812176248</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C63" s="88">
+        <f>Statement!AC107</f>
+        <v>5626</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C64" s="88">
+        <f>Statement!AC108</f>
+        <v>6645</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" s="24">
+        <f ca="1">C62+C63-C64</f>
+        <v>127942.36812176247</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C44" s="88">
+      <c r="C66" s="88">
         <f>Statement!AC78</f>
         <v>398</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="143" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="143" t="s">
         <v>210</v>
       </c>
-      <c r="C45" s="144">
-        <f ca="1">C43/C44</f>
-        <v>508.03894820809109</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="235" t="s">
-        <v>211</v>
-      </c>
-      <c r="C47" s="235"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C48" s="64">
-        <f>L6</f>
-        <v>39388.713090460325</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C49" s="137">
-        <f>Overview!C29</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="C50" s="105">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C51" s="24">
-        <f>L18</f>
-        <v>378.13734504559994</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C52" s="24">
-        <f>(C48*C50)/C51</f>
-        <v>520.82548320783292</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="143" t="s">
-        <v>210</v>
-      </c>
-      <c r="C53" s="144">
-        <f>C52/(1+C49)^5</f>
-        <v>323.39164811633128</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="235" t="s">
-        <v>328</v>
-      </c>
-      <c r="C55" s="235"/>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C56" s="64">
-        <f>L8</f>
-        <v>12411.378160399478</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C57" s="137">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10379398880135898</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="39" t="s">
-        <v>360</v>
-      </c>
-      <c r="C58" s="105">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C59" s="24">
-        <f>(C56*C58)</f>
-        <v>248227.56320798956</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C60" s="24">
-        <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>151884.04003643704</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="88">
-        <f>Statement!AC78</f>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="143" t="s">
-        <v>210</v>
-      </c>
-      <c r="C62" s="144">
-        <f ca="1">C60/C61</f>
-        <v>381.61819104632423</v>
+      <c r="C67" s="144">
+        <f ca="1">C65/C66</f>
+        <v>321.4632364868404</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -21535,10 +21609,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21547,7 +21621,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>323.57249540330463</v>
+        <v>322.19590416860262</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21555,8 +21629,8 @@
         <v>218</v>
       </c>
       <c r="C6" s="135">
-        <f ca="1">Multiples!C45</f>
-        <v>508.03894820809109</v>
+        <f ca="1">Multiples!C47</f>
+        <v>438.66153573978517</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21564,7 +21638,7 @@
         <v>219</v>
       </c>
       <c r="C7" s="135">
-        <f>Multiples!C53</f>
+        <f>Multiples!C55</f>
         <v>323.39164811633128</v>
       </c>
     </row>
@@ -21573,8 +21647,8 @@
         <v>329</v>
       </c>
       <c r="C8" s="135">
-        <f ca="1">Multiples!C62</f>
-        <v>381.61819104632423</v>
+        <f ca="1">Multiples!C67</f>
+        <v>321.4632364868404</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21583,7 +21657,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>384.15532069351281</v>
+        <v>351.42808112788987</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21592,7 +21666,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>219.72</v>
+        <v>225.685</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21601,7 +21675,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.74838576685560176</v>
+        <v>0.55716188992573656</v>
       </c>
     </row>
   </sheetData>
@@ -21666,20 +21740,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21854,7 +21928,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>78501.214249645185</v>
+        <v>78184.50640924029</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21908,23 +21982,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9311.9581585996839</v>
+        <v>9309.0954941722048</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7508.3238767711573</v>
+        <v>7503.7081971229682</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6054.0357332285757</v>
+        <v>6048.4540891023798</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4881.4288329514402</v>
+        <v>4875.4290421376027</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3935.944302473114</v>
+        <v>3929.8981185531879</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21943,7 +22017,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>47911.112073202392</v>
+        <v>47644.516410554577</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21959,7 +22033,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>219.72</v>
+        <v>225.685</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21968,7 +22042,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>197.44674114880993</v>
+        <v>196.71382249156514</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22007,7 +22081,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10379398880135898</v>
+        <v>0.10413341939254649</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22025,7 +22099,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>87448.56</v>
+        <v>89822.63</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22052,7 +22126,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>88467.56</v>
+        <v>90841.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22068,7 +22142,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31691.69090402397</v>
+        <v>31666.584941088342</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22077,7 +22151,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>47911.112073202392</v>
+        <v>47644.516410554577</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22086,7 +22160,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>79602.802977226354</v>
+        <v>79311.101351642923</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22113,7 +22187,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>78583.802977226354</v>
+        <v>78292.101351642923</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22131,7 +22205,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>197.44674114880993</v>
+        <v>196.71382249156514</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -29086,7 +29160,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>219.72</v>
+        <v>225.685</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29133,7 +29207,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>219.72</v>
+        <v>225.685</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30439,7 +30513,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>12.569794050343251</v>
+        <v>12.911041189931353</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30476,7 +30550,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.6056123501865227</v>
+        <v>3.7034981943011349</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30513,7 +30587,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.5923389477339809</v>
+        <v>7.7984571974301096</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30550,7 +30624,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>87448.56</v>
+        <v>89822.63</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30587,7 +30661,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>88467.56</v>
+        <v>90841.63</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30624,7 +30698,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>3.5108961028653067</v>
+        <v>3.6051127073577272</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30661,7 +30735,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>9.7324048404840475</v>
+        <v>9.9935786578657879</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30796,7 +30870,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="92">AC153/AC157</f>
-        <v>10.691840078249175</v>
+        <v>10.982104169213841</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30833,7 +30907,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="92"/>
-        <v>10.899935637975865</v>
+        <v>11.192440712152766</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -30870,7 +30944,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="95">AC157/AC153</f>
-        <v>9.3529270236125103E-2</v>
+        <v>9.1057231345820083E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30907,7 +30981,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.9555798288731092E-2</v>
+        <v>7.7453087267651807E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30981,7 +31055,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>0.10428988196032045</v>
+        <v>0.10153343316712057</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31018,7 +31092,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>0.10428988196032045</v>
+        <v>0.10153343316712057</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31521,7 +31595,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.1652564662013875E-2</v>
+        <v>-1.1344579868124547E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32782,15 +32856,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32798,7 +32872,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>219.72</v>
+        <v>225.685</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -32814,7 +32888,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>87448.56</v>
+        <v>89822.63</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32834,7 +32908,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>88467.56</v>
+        <v>90841.63</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -32854,7 +32928,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>12.569794050343251</v>
+        <v>12.911041189931353</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -32874,7 +32948,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.6056123501865227</v>
+        <v>3.7034981943011349</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -32894,7 +32968,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>7.5923389477339809</v>
+        <v>7.7984571974301096</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32914,7 +32988,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.5108961028653067</v>
+        <v>3.6051127073577272</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32923,18 +32997,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>9.7324048404840475</v>
+        <v>9.9935786578657879</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32985,14 +33059,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="232" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33061,14 +33135,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="232" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33144,14 +33218,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33159,7 +33233,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>7.9555798288731092E-2</v>
+        <v>7.7453087267651807E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33175,7 +33249,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>9.3529270236125103E-2</v>
+        <v>9.1057231345820083E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -33207,7 +33281,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.10428988196032045</v>
+        <v>0.10153343316712057</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33216,18 +33290,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.10428988196032045</v>
+        <v>0.10153343316712057</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="232" t="s">
         <v>285</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33260,18 +33334,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1652564662013875E-2</v>
+        <v>-1.1344579868124547E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="232" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>309</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33439,7 +33513,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>219.72</v>
+        <v>225.685</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33468,7 +33542,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>87448.56</v>
+        <v>89822.63</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33497,7 +33571,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>88467.56</v>
+        <v>90841.63</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33526,7 +33600,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>12.569794050343251</v>
+        <v>12.911041189931353</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33555,7 +33629,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.6056123501865227</v>
+        <v>3.7034981943011349</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33584,7 +33658,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>7.5923389477339809</v>
+        <v>7.7984571974301096</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33613,7 +33687,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.5108961028653067</v>
+        <v>3.6051127073577272</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33642,7 +33716,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>9.7324048404840475</v>
+        <v>9.9935786578657879</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34415,7 +34489,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>7.9555798288731092E-2</v>
+        <v>7.7453087267651807E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34444,7 +34518,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>9.3529270236125103E-2</v>
+        <v>9.1057231345820083E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34502,7 +34576,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.10428988196032045</v>
+        <v>0.10153343316712057</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34531,7 +34605,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.10428988196032045</v>
+        <v>0.10153343316712057</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34767,7 +34841,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1652564662013875E-2</v>
+        <v>-1.1344579868124547E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712170F3-ADB1-094E-B9F9-490969C368A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030B36E1-17AB-384A-A94B-431869577E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -128,28 +128,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -159,21 +138,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2319,9 +2289,6 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="40" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2329,6 +2296,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12648,7 +12618,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12685,11 +12655,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>386.60109999999997</v>
+    <v>376.16</v>
     <v>190.12</v>
-    <v>1.4237</v>
-    <v>7.6150000000000002</v>
-    <v>3.492E-2</v>
+    <v>1.4235</v>
+    <v>0.99</v>
+    <v>4.4460000000000003E-3</v>
+    <v>0.32</v>
+    <v>1.431E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12697,50 +12669,36 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>230.74</v>
+    <v>228.4</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46210.767642164064</v>
+    <v>46213.886339964847</v>
     <v>4</v>
-    <v>220.29</v>
-    <v>89709787500</v>
+    <v>222.82</v>
+    <v>88896900000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>221.16</v>
-    <v>12.9153</v>
-    <v>218.07</v>
-    <v>225.685</v>
+    <v>226.5</v>
+    <v>12.7982</v>
+    <v>222.65</v>
+    <v>223.64</v>
+    <v>223.96</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>5805189</v>
-    <v>8549189</v>
+    <v>3188001</v>
+    <v>8249601</v>
     <v>1997</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12754,28 +12712,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.06</v>
-    <v>-1.338E-3</v>
+    <v>-0.3</v>
+    <v>-6.5659999999999998E-3</v>
     <v>US</v>
-    <v>44.91</v>
+    <v>45.81</v>
     <v>Index</v>
-    <v>10</v>
-    <v>44.57</v>
+    <v>7</v>
+    <v>45.29</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.57</v>
-    <v>44.85</v>
-    <v>44.79</v>
+    <v>45.77</v>
+    <v>45.69</v>
+    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12809,6 +12767,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12830,6 +12790,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12839,11 +12800,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12879,7 +12835,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12890,13 +12846,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12997,13 +12956,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13084,6 +13049,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13091,6 +13059,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13582,18 +13553,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13608,7 +13579,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>89822.63</v>
+        <v>89008.72</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13616,7 +13587,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>322.19590416860262</v>
+        <v>320.14942405013142</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13632,7 +13603,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>90841.63</v>
+        <v>90027.72</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13640,7 +13611,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>438.66153573978517</v>
+        <v>437.64666034595507</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13649,7 +13620,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>225.685</v>
+        <v>223.64</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13671,16 +13642,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="210" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>223.96</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>12.911041189931353</v>
+        <v>12.794050343249429</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13688,7 +13659,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>321.4632364868404</v>
+        <v>320.7185268038848</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13697,14 +13668,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>7.6150000000000002</v>
+        <v>0.99</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>3.7034981943011349</v>
+        <v>3.6699396777522022</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13712,23 +13683,23 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>351.42808112788987</v>
+        <v>350.47656482907564</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.32</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>9.1057231345820083E-2</v>
+        <v>9.1889873261855687E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13736,7 +13707,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.55716188992573656</v>
+        <v>0.56714614929831719</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13745,30 +13716,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.492E-2</v>
+        <v>4.4460000000000003E-3</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>7.7453087267651807E-2</v>
+        <v>7.816133071006974E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>1.431E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>0.10153343316712057</v>
+        <v>0.10246187115150066</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13777,7 +13748,7 @@
       </c>
       <c r="C11" s="211" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>386.60109999999997</v>
+        <v>376.16</v>
       </c>
       <c r="E11" s="188" t="s">
         <v>295</v>
@@ -13809,7 +13780,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4237</v>
+        <v>1.4235</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13825,7 +13796,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>8549189</v>
+        <v>8249601</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13841,7 +13812,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1344579868124547E-2</v>
+        <v>-1.1448316524493331E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13854,10 +13825,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="234" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="186" t="s">
         <v>302</v>
       </c>
@@ -13930,14 +13901,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -13946,12 +13917,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="5">
+      <c r="E26" s="187" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.79</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13966,7 +13937,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13986,15 +13957,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="235" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14013,24 +13984,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="235" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14045,24 +14016,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="235"/>
+      <c r="E49" s="235"/>
+      <c r="F49" s="235"/>
+      <c r="G49" s="235"/>
+      <c r="H49" s="235"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="235"/>
+      <c r="D52" s="235"/>
+      <c r="E52" s="235"/>
+      <c r="F52" s="235"/>
+      <c r="G52" s="235"/>
+      <c r="H52" s="235"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14088,13 +14059,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="235"/>
+      <c r="C59" s="235"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14179,36 +14150,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15228,35 +15199,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -17197,20 +17168,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -18653,20 +18624,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -19747,10 +19718,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19767,7 +19738,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>225.685</v>
+        <v>223.64</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19776,7 +19747,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>89822.63</v>
+        <v>89008.72</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19794,7 +19765,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19803,7 +19774,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4237</v>
+        <v>1.4235</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19835,10 +19806,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19846,7 +19817,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.8883209839404158E-2</v>
+        <v>6.9469331668439036E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19855,7 +19826,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9311167901605959</v>
+        <v>0.93053066833156095</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19873,7 +19844,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.10885649999999999</v>
+        <v>0.1094475</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19882,7 +19853,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10413341939254649</v>
+        <v>0.10464317469513994</v>
       </c>
     </row>
   </sheetData>
@@ -19927,20 +19898,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20133,7 +20104,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>150470.59557321406</v>
+        <v>149564.4010187907</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20187,23 +20158,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7348.3827868689641</v>
+        <v>7344.9917578227505</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7524.8353708908762</v>
+        <v>7517.8920614713361</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7567.4450125167714</v>
+        <v>7556.9734897890421</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7554.3689343273445</v>
+        <v>7540.4342449908418</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7563.3157718683815</v>
+        <v>7545.8808039968326</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20222,14 +20193,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>91694.621982631506</v>
+        <v>90932.298413881508</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="235" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20245,14 +20216,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10413341939254649</v>
+        <v>0.10464317469513994</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="235" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20260,7 +20231,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37558.347876472333</v>
+        <v>37506.172358070806</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20269,7 +20240,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>91694.621982631506</v>
+        <v>90932.298413881508</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20278,7 +20249,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>129252.96985910385</v>
+        <v>128438.47077195231</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20305,7 +20276,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>128233.96985910385</v>
+        <v>127419.4707719523</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20323,7 +20294,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>322.19590416860262</v>
+        <v>320.14942405013142</v>
       </c>
     </row>
   </sheetData>
@@ -20366,20 +20337,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21311,10 +21282,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21332,7 +21303,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10413341939254649</v>
+        <v>0.10464317469513994</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21358,7 +21329,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>175606.29122443451</v>
+        <v>175202.37081769013</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21385,7 +21356,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>174587.29122443451</v>
+        <v>174183.37081769013</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21403,14 +21374,14 @@
       </c>
       <c r="C47" s="144">
         <f ca="1">C45/C46</f>
-        <v>438.66153573978517</v>
+        <v>437.64666034595507</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="232" t="s">
+      <c r="B49" s="235" t="s">
         <v>211</v>
       </c>
-      <c r="C49" s="232"/>
+      <c r="C49" s="235"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21466,10 +21437,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="232" t="s">
+      <c r="B57" s="235" t="s">
         <v>328</v>
       </c>
-      <c r="C57" s="232"/>
+      <c r="C57" s="235"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21486,7 +21457,7 @@
       </c>
       <c r="C59" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10413341939254649</v>
+        <v>0.10464317469513994</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21512,7 +21483,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>128961.36812176248</v>
+        <v>128664.97366794615</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21539,7 +21510,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>127942.36812176247</v>
+        <v>127645.97366794615</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21557,7 +21528,7 @@
       </c>
       <c r="C67" s="144">
         <f ca="1">C65/C66</f>
-        <v>321.4632364868404</v>
+        <v>320.7185268038848</v>
       </c>
     </row>
   </sheetData>
@@ -21609,10 +21580,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21621,7 +21592,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>322.19590416860262</v>
+        <v>320.14942405013142</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21630,7 +21601,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C47</f>
-        <v>438.66153573978517</v>
+        <v>437.64666034595507</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21648,7 +21619,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C67</f>
-        <v>321.4632364868404</v>
+        <v>320.7185268038848</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21657,7 +21628,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>351.42808112788987</v>
+        <v>350.47656482907564</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21666,7 +21637,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>225.685</v>
+        <v>223.64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21675,7 +21646,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.55716188992573656</v>
+        <v>0.56714614929831719</v>
       </c>
     </row>
   </sheetData>
@@ -21740,20 +21711,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21928,7 +21899,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>78184.50640924029</v>
+        <v>77713.647809402697</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21982,23 +21953,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9309.0954941722048</v>
+        <v>9304.7996628130768</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7503.7081971229682</v>
+        <v>7496.7843821504684</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6048.4540891023798</v>
+        <v>6040.0844842546539</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4875.4290421376027</v>
+        <v>4866.4358900060406</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3929.8981185531879</v>
+        <v>3920.8389109910381</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22017,7 +21988,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>47644.516410554577</v>
+        <v>47248.413160482385</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22033,7 +22004,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>225.685</v>
+        <v>223.64</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22042,7 +22013,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>196.71382249156514</v>
+        <v>195.62401128315994</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22081,7 +22052,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10413341939254649</v>
+        <v>0.10464317469513994</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22099,7 +22070,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>89822.63</v>
+        <v>89008.72</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22126,7 +22097,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>90841.63</v>
+        <v>90027.72</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22142,7 +22113,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31666.584941088342</v>
+        <v>31628.943330215276</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22151,7 +22122,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>47644.516410554577</v>
+        <v>47248.413160482385</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22160,7 +22131,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>79311.101351642923</v>
+        <v>78877.356490697653</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22187,7 +22158,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>78292.101351642923</v>
+        <v>77858.356490697653</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22205,7 +22176,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>196.71382249156514</v>
+        <v>195.62401128315994</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -29160,7 +29131,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>225.685</v>
+        <v>223.64</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29207,7 +29178,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>225.685</v>
+        <v>223.64</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30513,7 +30484,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>12.911041189931353</v>
+        <v>12.794050343249429</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30550,7 +30521,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7034981943011349</v>
+        <v>3.6699396777522022</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30587,7 +30558,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.7984571974301096</v>
+        <v>7.727793019621461</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30624,7 +30595,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>89822.63</v>
+        <v>89008.72</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30661,7 +30632,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>90841.63</v>
+        <v>90027.72</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30698,7 +30669,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>3.6051127073577272</v>
+        <v>3.5728121279466625</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30735,7 +30706,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>9.9935786578657879</v>
+        <v>9.9040396039603955</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30870,7 +30841,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="92">AC153/AC157</f>
-        <v>10.982104169213841</v>
+        <v>10.882592003912459</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30907,7 +30878,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="92"/>
-        <v>11.192440712152766</v>
+        <v>11.092160263419865</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -30944,7 +30915,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="95">AC157/AC153</f>
-        <v>9.1057231345820083E-2</v>
+        <v>9.1889873261855687E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30981,7 +30952,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.7453087267651807E-2</v>
+        <v>7.816133071006974E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31055,7 +31026,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>0.10153343316712057</v>
+        <v>0.10246187115150066</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31092,7 +31063,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>0.10153343316712057</v>
+        <v>0.10246187115150066</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31595,7 +31566,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.1344579868124547E-2</v>
+        <v>-1.1448316524493331E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32856,15 +32827,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32872,7 +32843,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>225.685</v>
+        <v>223.64</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -32888,7 +32859,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>89822.63</v>
+        <v>89008.72</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32908,7 +32879,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>90841.63</v>
+        <v>90027.72</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -32928,7 +32899,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>12.911041189931353</v>
+        <v>12.794050343249429</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -32948,7 +32919,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.7034981943011349</v>
+        <v>3.6699396777522022</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -32968,7 +32939,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>7.7984571974301096</v>
+        <v>7.727793019621461</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32988,7 +32959,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.6051127073577272</v>
+        <v>3.5728121279466625</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32997,18 +32968,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>9.9935786578657879</v>
+        <v>9.9040396039603955</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33059,14 +33030,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="235" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33135,14 +33106,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="235" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33218,14 +33189,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33233,7 +33204,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>7.7453087267651807E-2</v>
+        <v>7.816133071006974E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33249,7 +33220,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>9.1057231345820083E-2</v>
+        <v>9.1889873261855687E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -33281,7 +33252,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.10153343316712057</v>
+        <v>0.10246187115150066</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33290,18 +33261,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.10153343316712057</v>
+        <v>0.10246187115150066</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="235" t="s">
         <v>285</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33334,18 +33305,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1344579868124547E-2</v>
+        <v>-1.1448316524493331E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="235" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>309</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33513,7 +33484,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>225.685</v>
+        <v>223.64</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33542,7 +33513,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>89822.63</v>
+        <v>89008.72</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33571,7 +33542,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>90841.63</v>
+        <v>90027.72</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33600,7 +33571,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>12.911041189931353</v>
+        <v>12.794050343249429</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33629,7 +33600,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.7034981943011349</v>
+        <v>3.6699396777522022</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33658,7 +33629,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>7.7984571974301096</v>
+        <v>7.727793019621461</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33687,7 +33658,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.6051127073577272</v>
+        <v>3.5728121279466625</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33716,7 +33687,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>9.9935786578657879</v>
+        <v>9.9040396039603955</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34489,7 +34460,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>7.7453087267651807E-2</v>
+        <v>7.816133071006974E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34518,7 +34489,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>9.1057231345820083E-2</v>
+        <v>9.1889873261855687E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34576,7 +34547,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.10153343316712057</v>
+        <v>0.10246187115150066</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34605,7 +34576,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.10153343316712057</v>
+        <v>0.10246187115150066</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34841,7 +34812,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1344579868124547E-2</v>
+        <v>-1.1448316524493331E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030B36E1-17AB-384A-A94B-431869577E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C2EE74-6FB9-BD46-AB88-31C8E85F10FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -32,10 +32,12 @@
     <sheet name="DCF" sheetId="11" r:id="rId17"/>
     <sheet name="Multiples" sheetId="12" r:id="rId18"/>
     <sheet name="AVG target price" sheetId="13" r:id="rId19"/>
-    <sheet name="Reverse DCF" sheetId="14" r:id="rId20"/>
+    <sheet name="DDM" sheetId="21" r:id="rId20"/>
+    <sheet name="Reverse DCF" sheetId="14" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -150,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="418">
   <si>
     <t>Ticker</t>
   </si>
@@ -1371,6 +1373,39 @@
   </si>
   <si>
     <t>Services Growth Rate</t>
+  </si>
+  <si>
+    <t>Manual Cost of Equity</t>
+  </si>
+  <si>
+    <t>DDM price</t>
+  </si>
+  <si>
+    <t>Dividend discount model</t>
+  </si>
+  <si>
+    <t>Dividend per share</t>
+  </si>
+  <si>
+    <t>Ratios</t>
+  </si>
+  <si>
+    <t>Payout</t>
+  </si>
+  <si>
+    <t>DDM valuation</t>
+  </si>
+  <si>
+    <t>Latest dividend</t>
+  </si>
+  <si>
+    <t>Year 1 growth rate</t>
+  </si>
+  <si>
+    <t>Year 1 dividend</t>
+  </si>
+  <si>
+    <t>Perpetual dividend growth</t>
   </si>
 </sst>
 </file>
@@ -1980,7 +2015,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2289,6 +2324,9 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="40" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2298,15 +2336,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2314,6 +2343,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2343,6 +2378,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12501,6 +12541,95 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Financials -&gt;"/>
+      <sheetName val="Statement"/>
+      <sheetName val="Analysis -&gt;"/>
+      <sheetName val="Basic"/>
+      <sheetName val="Yearly Analysis"/>
+      <sheetName val="Quarter analysis"/>
+      <sheetName val="Graphs Year"/>
+      <sheetName val="Graphs Quarter"/>
+      <sheetName val="Forecast -&gt;"/>
+      <sheetName val="Revenue"/>
+      <sheetName val="COGS &amp; OpEx"/>
+      <sheetName val="WC &amp; Investments"/>
+      <sheetName val="FCF &amp; Other"/>
+      <sheetName val="Valuation -&gt;"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Multiples"/>
+      <sheetName val="AVG target price"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Reverse DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="5">
+          <cell r="C5">
+            <v>2021</v>
+          </cell>
+          <cell r="D5">
+            <v>2022</v>
+          </cell>
+          <cell r="E5">
+            <v>2023</v>
+          </cell>
+          <cell r="F5">
+            <v>2024</v>
+          </cell>
+          <cell r="G5">
+            <v>2025</v>
+          </cell>
+          <cell r="H5">
+            <v>2026</v>
+          </cell>
+          <cell r="I5">
+            <v>2027</v>
+          </cell>
+          <cell r="J5">
+            <v>2028</v>
+          </cell>
+          <cell r="K5">
+            <v>2029</v>
+          </cell>
+          <cell r="L5">
+            <v>2030</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="adi dumitras" id="{A0F62302-F8D3-B346-B5DF-839B413AE710}" userId="b24535bb88af1c42" providerId="Windows Live"/>
@@ -12657,11 +12786,11 @@
     <v>Powered by Refinitiv</v>
     <v>376.16</v>
     <v>190.12</v>
-    <v>1.4235</v>
+    <v>1.4271</v>
     <v>0.99</v>
     <v>4.4460000000000003E-3</v>
-    <v>0.32</v>
-    <v>1.431E-3</v>
+    <v>-0.04</v>
+    <v>-1.7889999999999998E-4</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12673,21 +12802,21 @@
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46213.886339964847</v>
+    <v>46213.999230381247</v>
     <v>4</v>
     <v>222.82</v>
     <v>88896900000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
     <v>226.5</v>
-    <v>12.7982</v>
+    <v>12.7416</v>
     <v>222.65</v>
     <v>223.64</v>
-    <v>223.96</v>
+    <v>223.6</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>3188001</v>
+    <v>3206786</v>
     <v>8249601</v>
     <v>1997</v>
   </rv>
@@ -12712,17 +12841,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.3</v>
-    <v>-6.5659999999999998E-3</v>
+    <v>0.3</v>
+    <v>6.6090000000000003E-3</v>
     <v>US</v>
-    <v>45.81</v>
+    <v>45.71</v>
     <v>Index</v>
     <v>7</v>
-    <v>45.29</v>
+    <v>45.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.77</v>
+    <v>45.41</v>
+    <v>45.39</v>
     <v>45.69</v>
-    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12964,9 +13093,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13553,18 +13682,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="233"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13587,7 +13716,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>320.14942405013142</v>
+        <v>318.44270346254751</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13611,7 +13740,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>437.64666034595507</v>
+        <v>436.79294069561087</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13644,7 +13773,7 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>223.96</v>
+        <v>223.6</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
@@ -13659,7 +13788,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>320.7185268038848</v>
+        <v>320.09207227162801</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13683,7 +13812,7 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>350.47656482907564</v>
+        <v>349.67984113652943</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13692,7 +13821,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
@@ -13707,7 +13836,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.56714614929831719</v>
+        <v>0.56358362160852016</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13732,7 +13861,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.431E-3</v>
+        <v>-1.7889999999999998E-4</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
@@ -13741,6 +13870,13 @@
         <f ca="1">Statement!AC164</f>
         <v>0.10246187115150066</v>
       </c>
+      <c r="H10" s="186" t="s">
+        <v>408</v>
+      </c>
+      <c r="I10" s="214">
+        <f>DDM!C26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="187" t="s">
@@ -13780,7 +13916,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4235</v>
+        <v>1.4271</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13825,10 +13961,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="235" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="186" t="s">
         <v>302</v>
       </c>
@@ -13901,14 +14037,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -13922,7 +14058,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.39</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13937,7 +14073,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13950,22 +14086,22 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="186" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="C29" s="223">
         <v>0.1</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="232" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13984,24 +14120,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="232" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14016,24 +14152,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="235"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="235"/>
+      <c r="B49" s="232"/>
+      <c r="C49" s="232"/>
+      <c r="D49" s="232"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="232"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="235"/>
-      <c r="D52" s="235"/>
-      <c r="E52" s="235"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="235"/>
-      <c r="H52" s="235"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14059,28 +14195,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="235"/>
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
+      <c r="H59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14150,36 +14286,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15199,35 +15335,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -17168,20 +17304,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -18574,12 +18710,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18587,6 +18717,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18624,20 +18760,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -19646,16 +19782,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19718,10 +19854,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19765,7 +19901,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19774,7 +19910,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4235</v>
+        <v>1.4271</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19806,10 +19942,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19844,7 +19980,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1094475</v>
+        <v>0.10990949999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19853,7 +19989,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10464317469513994</v>
+        <v>0.10507307986390911</v>
       </c>
     </row>
   </sheetData>
@@ -19898,20 +20034,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20104,7 +20240,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>149564.4010187907</v>
+        <v>148808.59778274116</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20158,23 +20294,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7344.9917578227505</v>
+        <v>7342.1343450608329</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7517.8920614713361</v>
+        <v>7512.0438473618779</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7556.9734897890421</v>
+        <v>7548.1572812040658</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7540.4342449908418</v>
+        <v>7528.7073083702689</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7545.8808039968326</v>
+        <v>7531.2143978887025</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20193,14 +20329,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>90932.298413881508</v>
+        <v>90296.938798208168</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="232" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20216,14 +20352,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10464317469513994</v>
+        <v>0.10507307986390911</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="232" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20231,7 +20367,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37506.172358070806</v>
+        <v>37462.257179885746</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20240,7 +20376,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>90932.298413881508</v>
+        <v>90296.938798208168</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20249,7 +20385,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>128438.47077195231</v>
+        <v>127759.19597809392</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20276,7 +20412,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>127419.4707719523</v>
+        <v>126740.19597809392</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20294,7 +20430,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>320.14942405013142</v>
+        <v>318.44270346254751</v>
       </c>
     </row>
   </sheetData>
@@ -20337,20 +20473,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21282,10 +21418,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="232"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21303,7 +21439,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10464317469513994</v>
+        <v>0.10507307986390911</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21329,7 +21465,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>175202.37081769013</v>
+        <v>174862.59039685313</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21356,7 +21492,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>174183.37081769013</v>
+        <v>173843.59039685313</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21374,14 +21510,14 @@
       </c>
       <c r="C47" s="144">
         <f ca="1">C45/C46</f>
-        <v>437.64666034595507</v>
+        <v>436.79294069561087</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="232" t="s">
         <v>211</v>
       </c>
-      <c r="C49" s="235"/>
+      <c r="C49" s="232"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21397,7 +21533,7 @@
         <v>358</v>
       </c>
       <c r="C51" s="137">
-        <f>Overview!C29</f>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.1</v>
       </c>
     </row>
@@ -21437,10 +21573,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="235" t="s">
+      <c r="B57" s="232" t="s">
         <v>328</v>
       </c>
-      <c r="C57" s="235"/>
+      <c r="C57" s="232"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21457,7 +21593,7 @@
       </c>
       <c r="C59" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10464317469513994</v>
+        <v>0.10507307986390911</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21483,7 +21619,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>128664.97366794615</v>
+        <v>128415.64476410794</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21510,7 +21646,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>127645.97366794615</v>
+        <v>127396.64476410794</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21528,7 +21664,7 @@
       </c>
       <c r="C67" s="144">
         <f ca="1">C65/C66</f>
-        <v>320.7185268038848</v>
+        <v>320.09207227162801</v>
       </c>
     </row>
   </sheetData>
@@ -21580,10 +21716,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21592,7 +21728,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>320.14942405013142</v>
+        <v>318.44270346254751</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21601,7 +21737,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C47</f>
-        <v>437.64666034595507</v>
+        <v>436.79294069561087</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21619,7 +21755,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C67</f>
-        <v>320.7185268038848</v>
+        <v>320.09207227162801</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21628,7 +21764,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>350.47656482907564</v>
+        <v>349.67984113652943</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21646,7 +21782,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.56714614929831719</v>
+        <v>0.56358362160852016</v>
       </c>
     </row>
   </sheetData>
@@ -21679,6 +21815,477 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B6E4A1-F7CC-5043-8E79-210959816CC1}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="83" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
+      <c r="B1" s="82" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
+      <c r="C2" s="232" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
+        <v>115</v>
+      </c>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+    </row>
+    <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="86"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="241" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="12">
+        <f>[2]Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D5" s="12">
+        <f>[2]Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E5" s="12">
+        <f>[2]Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F5" s="12">
+        <f>[2]Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G5" s="12">
+        <f>[2]Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H5" s="12">
+        <f>[2]Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I5" s="12">
+        <f>[2]Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J5" s="12">
+        <f>[2]Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K5" s="12">
+        <f>[2]Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L5" s="12">
+        <f>[2]Revenue!L5</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="250">
+        <f>Statement!M26</f>
+        <v>10.02</v>
+      </c>
+      <c r="D6" s="250">
+        <f>Statement!N26</f>
+        <v>10.1</v>
+      </c>
+      <c r="E6" s="250">
+        <f>Statement!O26</f>
+        <v>11.82</v>
+      </c>
+      <c r="F6" s="250">
+        <f>Statement!P26</f>
+        <v>14.577777777777778</v>
+      </c>
+      <c r="G6" s="251">
+        <f>Statement!Q26</f>
+        <v>16.7</v>
+      </c>
+      <c r="H6" s="139"/>
+      <c r="I6" s="139"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
+      <c r="N6" s="91"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="C7" s="250">
+        <f>Statement!M82</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="250">
+        <f>Statement!N82</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="250">
+        <f>Statement!O82</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="250">
+        <f>Statement!P82</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="251">
+        <f>Statement!Q82</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
+      <c r="N7" s="91"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="91"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C9" s="241" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="N9" s="91"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:L10" si="0">C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="N10" s="91"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="139"/>
+      <c r="D11" s="95">
+        <f>(D6-C6)/C6</f>
+        <v>7.9840319361277525E-3</v>
+      </c>
+      <c r="E11" s="95">
+        <f>(E6-D6)/D6</f>
+        <v>0.17029702970297037</v>
+      </c>
+      <c r="F11" s="95">
+        <f>(F6-E6)/E6</f>
+        <v>0.23331453280691855</v>
+      </c>
+      <c r="G11" s="96">
+        <f>(G6-F6)/F6</f>
+        <v>0.14557926829268289</v>
+      </c>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="139"/>
+      <c r="L11" s="139"/>
+      <c r="N11" s="91"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="139"/>
+      <c r="D12" s="95">
+        <f>IF(C7=0,
+IF(D7=0,0,IF(D7&gt;0,1,-1)),
+(D7-C7)/ABS(C7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="95">
+        <f>IF(D7=0,
+IF(E7=0,0,IF(E7&gt;0,1,-1)),
+(E7-D7)/ABS(D7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="95">
+        <f>IF(E7=0,
+IF(F7=0,0,IF(F7&gt;0,1,-1)),
+(F7-E7)/ABS(E7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="96">
+        <f>IF(F7=0,
+IF(G7=0,0,IF(G7&gt;0,1,-1)),
+(G7-F7)/ABS(F7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="139"/>
+      <c r="K12" s="139"/>
+      <c r="L12" s="139"/>
+      <c r="N12" s="91"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="91"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C14" s="241" t="s">
+        <v>411</v>
+      </c>
+      <c r="D14" s="241"/>
+      <c r="E14" s="241"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
+      <c r="N14" s="91"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C15" s="12">
+        <f>C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" ref="D15:L15" si="1">D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>2026</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="1"/>
+        <v>2027</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="1"/>
+        <v>2028</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
+        <v>2029</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="N15" s="91"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C16" s="95">
+        <f>C7/C6</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="95">
+        <f t="shared" ref="D16:G16" si="2">D7/D6</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="96">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="139"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="139"/>
+      <c r="N16" s="91"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="91"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="91"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N19" s="91"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="232" t="s">
+        <v>413</v>
+      </c>
+      <c r="C20" s="232"/>
+      <c r="N20" s="91"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C21" s="252">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C22" s="253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="C23" s="254">
+        <f>C21*(1+C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C24" s="137">
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="C25" s="253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26" s="143" t="s">
+        <v>210</v>
+      </c>
+      <c r="C26" s="144">
+        <f>C23/(C24-C25)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="B20:C20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
   <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -21711,20 +22318,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -21899,7 +22506,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>77713.647809402697</v>
+        <v>77320.932523549476</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -21953,23 +22560,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9304.7996628130768</v>
+        <v>9301.1798284851084</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7496.7843821504684</v>
+        <v>7490.9525878335553</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6040.0844842546539</v>
+        <v>6033.037927222792</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4866.4358900060406</v>
+        <v>4858.8675745223409</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3920.8389109910381</v>
+        <v>3913.2182478442396</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -21988,7 +22595,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>47248.413160482385</v>
+        <v>46918.280367729436</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22013,7 +22620,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>195.62401128315994</v>
+        <v>194.71491591366197</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22052,7 +22659,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10464317469513994</v>
+        <v>0.10507307986390911</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22113,7 +22720,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31628.943330215276</v>
+        <v>31597.256165908038</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22122,7 +22729,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>47248.413160482385</v>
+        <v>46918.280367729436</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22131,7 +22738,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>78877.356490697653</v>
+        <v>78515.536533637467</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22158,7 +22765,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>77858.356490697653</v>
+        <v>77496.536533637467</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22176,7 +22783,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>195.62401128315994</v>
+        <v>194.71491591366197</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22623,17 +23230,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -32827,15 +33434,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="232" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32972,14 +33579,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="232" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33030,14 +33637,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="232" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33106,14 +33713,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="232" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33189,14 +33796,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="232" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33265,14 +33872,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="232" t="s">
         <v>285</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33309,14 +33916,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="232" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>309</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35298,14 +35905,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="236" t="s">
         <v>319</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="F3" s="240" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>320</v>
       </c>
-      <c r="G3" s="239"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35372,19 +35979,19 @@
       <c r="B7" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C7" s="236">
+      <c r="C7" s="239">
         <f>Statement!AA89</f>
         <v>3.4385745545482967E-2</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="F7" s="236">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1268516941937681</v>
       </c>
-      <c r="G7" s="237"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -35411,19 +36018,19 @@
       <c r="B9" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="239">
         <f>Statement!AA90</f>
         <v>7.6807228915662648E-2</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="F9" s="236">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1206896551724138</v>
       </c>
-      <c r="G9" s="237"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -35450,19 +36057,19 @@
       <c r="B11" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C11" s="236">
+      <c r="C11" s="239">
         <f>Statement!AA91</f>
         <v>2.9473317056156263E-2</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="F11" s="236">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12760267430754538</v>
       </c>
-      <c r="G11" s="237"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -35489,19 +36096,19 @@
       <c r="B13" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="236">
+      <c r="C13" s="239">
         <f>Statement!AA95</f>
         <v>0.10524728588661038</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="F13" s="236">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.172424824056302</v>
       </c>
-      <c r="G13" s="237"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -35528,19 +36135,19 @@
       <c r="B15" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C15" s="236">
+      <c r="C15" s="239">
         <f>Statement!AA96</f>
         <v>-7.4441687344913146E-2</v>
       </c>
-      <c r="D15" s="237"/>
-      <c r="F15" s="236">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.1166429587482217E-2</v>
       </c>
-      <c r="G15" s="237"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -35567,19 +36174,19 @@
       <c r="B17" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C17" s="236">
+      <c r="C17" s="239">
         <f>Statement!AA98</f>
         <v>-9.3700370566437263E-2</v>
       </c>
-      <c r="D17" s="237"/>
-      <c r="F17" s="236">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2418687167356593E-2</v>
       </c>
-      <c r="G17" s="237"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -35606,22 +36213,22 @@
       <c r="B19" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C19" s="236">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.1897810218978103E-2</v>
       </c>
-      <c r="D19" s="237"/>
-      <c r="F19" s="236">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.2937062937062943E-2</v>
       </c>
-      <c r="G19" s="237"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -35648,22 +36255,22 @@
       <c r="B21" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C21" s="236">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-7.6086956521739066E-2</v>
       </c>
-      <c r="D21" s="237"/>
-      <c r="F21" s="236">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>7.8680203045685293E-2</v>
       </c>
-      <c r="G21" s="237"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35711,22 +36318,22 @@
       <c r="B25" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C25" s="236">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5172636334301385E-2</v>
       </c>
-      <c r="D25" s="237"/>
-      <c r="F25" s="236">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13738698812267328</v>
       </c>
-      <c r="G25" s="237"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -35753,22 +36360,22 @@
       <c r="B27" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="236">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-1.1111111111111112E-2</v>
       </c>
-      <c r="D27" s="237"/>
-      <c r="F27" s="236">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="G27" s="237"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35795,49 +36402,49 @@
       <c r="B29" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C29" s="236">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D29" s="237"/>
-      <c r="F29" s="236">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.21527777777777779</v>
       </c>
-      <c r="G29" s="237"/>
+      <c r="G29" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C2EE74-6FB9-BD46-AB88-31C8E85F10FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2710E24-90EC-9547-8B43-25B5ADBFA9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2324,6 +2324,11 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="40" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2378,11 +2383,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12784,13 +12784,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>376.16</v>
+    <v>370.86</v>
     <v>190.12</v>
-    <v>1.4271</v>
-    <v>0.99</v>
-    <v>4.4460000000000003E-3</v>
-    <v>-0.04</v>
-    <v>-1.7889999999999998E-4</v>
+    <v>1.3321000000000001</v>
+    <v>2.5099999999999998</v>
+    <v>1.0125E-2</v>
+    <v>-1.41</v>
+    <v>-5.6310000000000006E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12798,26 +12798,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>228.4</v>
+    <v>250.71</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46213.999230381247</v>
+    <v>46234.91680143516</v>
     <v>4</v>
-    <v>222.82</v>
-    <v>88896900000</v>
+    <v>241.23</v>
+    <v>99537975000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>226.5</v>
-    <v>12.7416</v>
-    <v>222.65</v>
-    <v>223.64</v>
-    <v>223.6</v>
+    <v>244.73</v>
+    <v>14.3302</v>
+    <v>247.9</v>
+    <v>250.41</v>
+    <v>249</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>3206786</v>
-    <v>8249601</v>
+    <v>5586806</v>
+    <v>6067664</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12839,19 +12839,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>0.3</v>
-    <v>6.6090000000000003E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.71</v>
+    <v>46.86</v>
     <v>Index</v>
     <v>7</v>
-    <v>45.39</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.41</v>
-    <v>45.39</v>
-    <v>45.69</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13093,9 +13093,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13682,18 +13682,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="238" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="239"/>
+      <c r="E2" s="238" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="239"/>
+      <c r="H2" s="238" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="239"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>89008.72</v>
+        <v>99663.18</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>318.44270346254751</v>
+        <v>329.21405366448226</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>90027.72</v>
+        <v>100682.18</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>436.79294069561087</v>
+        <v>442.07082695442529</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>223.64</v>
+        <v>250.41</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13773,14 +13773,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>223.6</v>
+        <v>249</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>12.794050343249429</v>
+        <v>14.325514874141879</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>320.09207227162801</v>
+        <v>323.96495462385826</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13797,14 +13797,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.99</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>3.6699396777522022</v>
+        <v>4.1092362489086431</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>349.67984113652943</v>
+        <v>354.66037083977426</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13821,14 +13821,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.04</v>
+        <v>-1.41</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>9.1889873261855687E-2</v>
+        <v>8.2066416102717171E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.56358362160852016</v>
+        <v>0.4163187206572192</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13845,14 +13845,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.4460000000000003E-3</v>
+        <v>1.0125E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>7.816133071006974E-2</v>
+        <v>6.9805518948923756E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13861,14 +13861,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.7889999999999998E-4</v>
+        <v>-5.6310000000000006E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>0.10246187115150066</v>
+        <v>9.1508217979799564E-2</v>
       </c>
       <c r="H10" s="186" t="s">
         <v>408</v>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="C11" s="211" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>376.16</v>
+        <v>370.86</v>
       </c>
       <c r="E11" s="188" t="s">
         <v>295</v>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4271</v>
+        <v>1.3321000000000001</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>8249601</v>
+        <v>6067664</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1448316524493331E-2</v>
+        <v>-1.0224437951909623E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13961,10 +13961,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="240" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="240"/>
       <c r="E17" s="186" t="s">
         <v>302</v>
       </c>
@@ -14037,14 +14037,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="240" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="240"/>
+      <c r="E25" s="238" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="239"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.69</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14093,15 +14093,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="237" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14120,24 +14120,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="237"/>
+      <c r="C39" s="237"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="237" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14152,24 +14152,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="237"/>
+      <c r="C49" s="237"/>
+      <c r="D49" s="237"/>
+      <c r="E49" s="237"/>
+      <c r="F49" s="237"/>
+      <c r="G49" s="237"/>
+      <c r="H49" s="237"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="237" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="237"/>
+      <c r="D52" s="237"/>
+      <c r="E52" s="237"/>
+      <c r="F52" s="237"/>
+      <c r="G52" s="237"/>
+      <c r="H52" s="237"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14195,13 +14195,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="237"/>
+      <c r="C59" s="237"/>
+      <c r="D59" s="237"/>
+      <c r="E59" s="237"/>
+      <c r="F59" s="237"/>
+      <c r="G59" s="237"/>
+      <c r="H59" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14286,36 +14286,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
+      <c r="AA2" s="237" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -14326,32 +14326,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="242" t="s">
+      <c r="S4" s="247" t="s">
         <v>117</v>
       </c>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
-      <c r="AA4" s="243"/>
-      <c r="AB4" s="243"/>
-      <c r="AC4" s="243"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
+      <c r="AA4" s="248"/>
+      <c r="AB4" s="248"/>
+      <c r="AC4" s="248"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14841,33 +14841,33 @@
       <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="246" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="242" t="s">
+      <c r="S11" s="247" t="s">
         <v>123</v>
       </c>
-      <c r="T11" s="243"/>
-      <c r="U11" s="243"/>
-      <c r="V11" s="243"/>
-      <c r="W11" s="243"/>
-      <c r="X11" s="243"/>
-      <c r="Y11" s="243"/>
-      <c r="Z11" s="243"/>
-      <c r="AA11" s="243"/>
-      <c r="AB11" s="243"/>
-      <c r="AC11" s="243"/>
+      <c r="T11" s="248"/>
+      <c r="U11" s="248"/>
+      <c r="V11" s="248"/>
+      <c r="W11" s="248"/>
+      <c r="X11" s="248"/>
+      <c r="Y11" s="248"/>
+      <c r="Z11" s="248"/>
+      <c r="AA11" s="248"/>
+      <c r="AB11" s="248"/>
+      <c r="AC11" s="248"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15335,35 +15335,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
+      <c r="P2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="237"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="237"/>
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15372,31 +15372,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="P4" s="243" t="s">
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="P4" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
+      <c r="Q4" s="248"/>
+      <c r="R4" s="248"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15591,32 +15591,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="246" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="243" t="s">
+      <c r="P9" s="248" t="s">
         <v>127</v>
       </c>
-      <c r="Q9" s="243"/>
-      <c r="R9" s="243"/>
-      <c r="S9" s="243"/>
-      <c r="T9" s="243"/>
-      <c r="U9" s="243"/>
-      <c r="V9" s="243"/>
-      <c r="W9" s="243"/>
-      <c r="X9" s="243"/>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
+      <c r="Q9" s="248"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16465,31 +16465,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="241" t="s">
+      <c r="C21" s="246" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="241"/>
-      <c r="E21" s="241"/>
-      <c r="F21" s="241"/>
-      <c r="G21" s="241"/>
-      <c r="H21" s="241"/>
-      <c r="I21" s="241"/>
-      <c r="J21" s="241"/>
-      <c r="K21" s="241"/>
-      <c r="L21" s="241"/>
-      <c r="P21" s="243" t="s">
+      <c r="D21" s="246"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="246"/>
+      <c r="G21" s="246"/>
+      <c r="H21" s="246"/>
+      <c r="I21" s="246"/>
+      <c r="J21" s="246"/>
+      <c r="K21" s="246"/>
+      <c r="L21" s="246"/>
+      <c r="P21" s="248" t="s">
         <v>129</v>
       </c>
-      <c r="Q21" s="243"/>
-      <c r="R21" s="243"/>
-      <c r="S21" s="243"/>
-      <c r="T21" s="243"/>
-      <c r="U21" s="243"/>
-      <c r="V21" s="243"/>
-      <c r="W21" s="243"/>
-      <c r="X21" s="243"/>
-      <c r="Y21" s="243"/>
-      <c r="Z21" s="243"/>
+      <c r="Q21" s="248"/>
+      <c r="R21" s="248"/>
+      <c r="S21" s="248"/>
+      <c r="T21" s="248"/>
+      <c r="U21" s="248"/>
+      <c r="V21" s="248"/>
+      <c r="W21" s="248"/>
+      <c r="X21" s="248"/>
+      <c r="Y21" s="248"/>
+      <c r="Z21" s="248"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -17304,60 +17304,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17543,30 +17543,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="246" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="246"/>
-      <c r="Q11" s="246"/>
-      <c r="R11" s="246"/>
-      <c r="S11" s="246"/>
-      <c r="T11" s="246"/>
-      <c r="U11" s="246"/>
-      <c r="V11" s="246"/>
-      <c r="W11" s="246"/>
-      <c r="X11" s="246"/>
-      <c r="Y11" s="246"/>
-      <c r="Z11" s="246"/>
+      <c r="P11" s="251"/>
+      <c r="Q11" s="251"/>
+      <c r="R11" s="251"/>
+      <c r="S11" s="251"/>
+      <c r="T11" s="251"/>
+      <c r="U11" s="251"/>
+      <c r="V11" s="251"/>
+      <c r="W11" s="251"/>
+      <c r="X11" s="251"/>
+      <c r="Y11" s="251"/>
+      <c r="Z11" s="251"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17808,18 +17808,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="246" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18032,23 +18032,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="246"/>
-      <c r="C25" s="246"/>
+      <c r="B25" s="251"/>
+      <c r="C25" s="251"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="241" t="s">
+      <c r="C26" s="246" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18240,18 +18240,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="241" t="s">
+      <c r="C33" s="246" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="241"/>
-      <c r="E33" s="241"/>
-      <c r="F33" s="241"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="241"/>
-      <c r="I33" s="241"/>
-      <c r="J33" s="241"/>
-      <c r="K33" s="241"/>
-      <c r="L33" s="241"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18435,18 +18435,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="241" t="s">
+      <c r="C40" s="246" t="s">
         <v>151</v>
       </c>
-      <c r="D40" s="241"/>
-      <c r="E40" s="241"/>
-      <c r="F40" s="241"/>
-      <c r="G40" s="241"/>
-      <c r="H40" s="241"/>
-      <c r="I40" s="241"/>
-      <c r="J40" s="241"/>
-      <c r="K40" s="241"/>
-      <c r="L40" s="241"/>
+      <c r="D40" s="246"/>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="246"/>
+      <c r="H40" s="246"/>
+      <c r="I40" s="246"/>
+      <c r="J40" s="246"/>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18760,60 +18760,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246"/>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
+      <c r="AA2" s="251"/>
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="251"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
+      <c r="AA4" s="251"/>
+      <c r="AB4" s="251"/>
+      <c r="AC4" s="251"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19176,18 +19176,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="246" t="s">
         <v>159</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19280,18 +19280,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="246" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19483,18 +19483,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="241" t="s">
+      <c r="C25" s="246" t="s">
         <v>268</v>
       </c>
-      <c r="D25" s="241"/>
-      <c r="E25" s="241"/>
-      <c r="F25" s="241"/>
-      <c r="G25" s="241"/>
-      <c r="H25" s="241"/>
-      <c r="I25" s="241"/>
-      <c r="J25" s="241"/>
-      <c r="K25" s="241"/>
-      <c r="L25" s="241"/>
+      <c r="D25" s="246"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="246"/>
+      <c r="G25" s="246"/>
+      <c r="H25" s="246"/>
+      <c r="I25" s="246"/>
+      <c r="J25" s="246"/>
+      <c r="K25" s="246"/>
+      <c r="L25" s="246"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19632,18 +19632,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="241" t="s">
+      <c r="C31" s="246" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="241"/>
-      <c r="E31" s="241"/>
-      <c r="F31" s="241"/>
-      <c r="G31" s="241"/>
-      <c r="H31" s="241"/>
-      <c r="I31" s="241"/>
-      <c r="J31" s="241"/>
-      <c r="K31" s="241"/>
-      <c r="L31" s="241"/>
+      <c r="D31" s="246"/>
+      <c r="E31" s="246"/>
+      <c r="F31" s="246"/>
+      <c r="G31" s="246"/>
+      <c r="H31" s="246"/>
+      <c r="I31" s="246"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="246"/>
+      <c r="L31" s="246"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19854,10 +19854,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="237" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="237"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>223.64</v>
+        <v>250.41</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>89008.72</v>
+        <v>99663.18</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4271</v>
+        <v>1.3321000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19942,10 +19942,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="237" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="237"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.9469331668439036E-2</v>
+        <v>6.2506949135993112E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93053066833156095</v>
+        <v>0.93749305086400692</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19980,7 +19980,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.10990949999999999</v>
+        <v>0.1065745</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10507307986390911</v>
+        <v>0.10243125812999526</v>
       </c>
     </row>
   </sheetData>
@@ -20034,60 +20034,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>148808.59778274116</v>
+        <v>153577.73265625874</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20294,23 +20294,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7342.1343450608329</v>
+        <v>7359.728739217433</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7512.0438473618779</v>
+        <v>7548.0901024180375</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7548.1572812040658</v>
+        <v>7602.5517194416525</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7528.7073083702689</v>
+        <v>7601.1330866992666</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7531.2143978887025</v>
+        <v>7621.8854082526814</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20329,14 +20329,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>90296.938798208168</v>
+        <v>94312.804302434859</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="237" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="237"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20352,14 +20352,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10507307986390911</v>
+        <v>0.10243125812999526</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="237" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="237"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37462.257179885746</v>
+        <v>37733.389056029075</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>90296.938798208168</v>
+        <v>94312.804302434859</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20385,7 +20385,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>127759.19597809392</v>
+        <v>132046.19335846393</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>126740.19597809392</v>
+        <v>131027.19335846393</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>318.44270346254751</v>
+        <v>329.21405366448226</v>
       </c>
     </row>
   </sheetData>
@@ -20473,37 +20473,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20692,18 +20692,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="241" t="s">
+      <c r="C10" s="246" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="241"/>
-      <c r="E10" s="241"/>
-      <c r="F10" s="241"/>
-      <c r="G10" s="241"/>
-      <c r="H10" s="241"/>
-      <c r="I10" s="241"/>
-      <c r="J10" s="241"/>
-      <c r="K10" s="241"/>
-      <c r="L10" s="241"/>
+      <c r="D10" s="246"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="246"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20897,18 +20897,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="241" t="s">
+      <c r="C16" s="246" t="s">
         <v>197</v>
       </c>
-      <c r="D16" s="241"/>
-      <c r="E16" s="241"/>
-      <c r="F16" s="241"/>
-      <c r="G16" s="241"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="241"/>
-      <c r="J16" s="241"/>
-      <c r="K16" s="241"/>
-      <c r="L16" s="241"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
+      <c r="I16" s="246"/>
+      <c r="J16" s="246"/>
+      <c r="K16" s="246"/>
+      <c r="L16" s="246"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -21042,18 +21042,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="241" t="s">
+      <c r="C21" s="246" t="s">
         <v>200</v>
       </c>
-      <c r="D21" s="241"/>
-      <c r="E21" s="241"/>
-      <c r="F21" s="241"/>
-      <c r="G21" s="241"/>
-      <c r="H21" s="241"/>
-      <c r="I21" s="241"/>
-      <c r="J21" s="241"/>
-      <c r="K21" s="241"/>
-      <c r="L21" s="241"/>
+      <c r="D21" s="246"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="246"/>
+      <c r="G21" s="246"/>
+      <c r="H21" s="246"/>
+      <c r="I21" s="246"/>
+      <c r="J21" s="246"/>
+      <c r="K21" s="246"/>
+      <c r="L21" s="246"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21137,18 +21137,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="241" t="s">
+      <c r="C26" s="246" t="s">
         <v>201</v>
       </c>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21418,10 +21418,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="237" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="237"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10507307986390911</v>
+        <v>0.10243125812999526</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>174862.59039685313</v>
+        <v>176963.18912786126</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21492,7 +21492,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>173843.59039685313</v>
+        <v>175944.18912786126</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21510,14 +21510,14 @@
       </c>
       <c r="C47" s="144">
         <f ca="1">C45/C46</f>
-        <v>436.79294069561087</v>
+        <v>442.07082695442529</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="232" t="s">
+      <c r="B49" s="237" t="s">
         <v>211</v>
       </c>
-      <c r="C49" s="232"/>
+      <c r="C49" s="237"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21573,10 +21573,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="232" t="s">
+      <c r="B57" s="237" t="s">
         <v>328</v>
       </c>
-      <c r="C57" s="232"/>
+      <c r="C57" s="237"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="C59" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10507307986390911</v>
+        <v>0.10243125812999526</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>128415.64476410794</v>
+        <v>129957.05194029558</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>127396.64476410794</v>
+        <v>128938.05194029558</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="C67" s="144">
         <f ca="1">C65/C66</f>
-        <v>320.09207227162801</v>
+        <v>323.96495462385826</v>
       </c>
     </row>
   </sheetData>
@@ -21716,10 +21716,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="237" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="237"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21728,7 +21728,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>318.44270346254751</v>
+        <v>329.21405366448226</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21737,7 +21737,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C47</f>
-        <v>436.79294069561087</v>
+        <v>442.07082695442529</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C67</f>
-        <v>320.09207227162801</v>
+        <v>323.96495462385826</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>349.67984113652943</v>
+        <v>354.66037083977426</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>223.64</v>
+        <v>250.41</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21782,7 +21782,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.56358362160852016</v>
+        <v>0.4163187206572192</v>
       </c>
     </row>
   </sheetData>
@@ -21838,37 +21838,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="246" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21919,23 +21919,23 @@
       <c r="B6" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="C6" s="250">
+      <c r="C6" s="232">
         <f>Statement!M26</f>
         <v>10.02</v>
       </c>
-      <c r="D6" s="250">
+      <c r="D6" s="232">
         <f>Statement!N26</f>
         <v>10.1</v>
       </c>
-      <c r="E6" s="250">
+      <c r="E6" s="232">
         <f>Statement!O26</f>
         <v>11.82</v>
       </c>
-      <c r="F6" s="250">
+      <c r="F6" s="232">
         <f>Statement!P26</f>
         <v>14.577777777777778</v>
       </c>
-      <c r="G6" s="251">
+      <c r="G6" s="233">
         <f>Statement!Q26</f>
         <v>16.7</v>
       </c>
@@ -21950,23 +21950,23 @@
       <c r="B7" s="16" t="s">
         <v>410</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="232">
         <f>Statement!M82</f>
         <v>0</v>
       </c>
-      <c r="D7" s="250">
+      <c r="D7" s="232">
         <f>Statement!N82</f>
         <v>0</v>
       </c>
-      <c r="E7" s="250">
+      <c r="E7" s="232">
         <f>Statement!O82</f>
         <v>0</v>
       </c>
-      <c r="F7" s="250">
+      <c r="F7" s="232">
         <f>Statement!P82</f>
         <v>0</v>
       </c>
-      <c r="G7" s="251">
+      <c r="G7" s="233">
         <f>Statement!Q82</f>
         <v>0</v>
       </c>
@@ -21981,18 +21981,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="246" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22113,18 +22113,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="246" t="s">
         <v>411</v>
       </c>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="241"/>
-      <c r="H14" s="241"/>
-      <c r="I14" s="241"/>
-      <c r="J14" s="241"/>
-      <c r="K14" s="241"/>
-      <c r="L14" s="241"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22214,17 +22214,17 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="232" t="s">
+      <c r="B20" s="237" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="232"/>
+      <c r="C20" s="237"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C21" s="252">
+      <c r="C21" s="234">
         <f>G7</f>
         <v>0</v>
       </c>
@@ -22233,7 +22233,7 @@
       <c r="B22" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C22" s="253">
+      <c r="C22" s="235">
         <v>0</v>
       </c>
     </row>
@@ -22241,7 +22241,7 @@
       <c r="B23" s="39" t="s">
         <v>416</v>
       </c>
-      <c r="C23" s="254">
+      <c r="C23" s="236">
         <f>C21*(1+C22)</f>
         <v>0</v>
       </c>
@@ -22259,7 +22259,7 @@
       <c r="B25" s="39" t="s">
         <v>417</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="235">
         <v>0</v>
       </c>
     </row>
@@ -22274,12 +22274,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C9:L9"/>
     <mergeCell ref="C14:L14"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22318,60 +22318,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="246" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22506,7 +22506,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>77320.932523549476</v>
+        <v>79798.974526803446</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22560,23 +22560,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9301.1798284851084</v>
+        <v>9323.4688001019076</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7490.9525878335553</v>
+        <v>7526.8976372876359</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6033.037927222792</v>
+        <v>6076.5139302645557</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4858.8675745223409</v>
+        <v>4905.6096314875604</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3913.2182478442396</v>
+        <v>3960.330895760128</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22595,15 +22595,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>46918.280367729436</v>
+        <v>49004.923682044529</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="247" t="s">
+      <c r="B14" s="252" t="s">
         <v>224</v>
       </c>
-      <c r="C14" s="248"/>
+      <c r="C14" s="253"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="157" t="s">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>223.64</v>
+        <v>250.41</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>194.71491591366197</v>
+        <v>200.44910697725206</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22630,20 +22630,20 @@
       <c r="C17" s="160">
         <v>-0.11</v>
       </c>
-      <c r="E17" s="249" t="s">
+      <c r="E17" s="254" t="s">
         <v>227</v>
       </c>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="249"/>
-      <c r="I17" s="249"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="247" t="s">
+      <c r="B19" s="252" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="248"/>
+      <c r="C19" s="253"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="161" t="s">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10507307986390911</v>
+        <v>0.10243125812999526</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22677,7 +22677,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>89008.72</v>
+        <v>99663.18</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22704,15 +22704,15 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>90027.72</v>
+        <v>100682.18</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="247" t="s">
+      <c r="B28" s="252" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="248"/>
+      <c r="C28" s="253"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="161" t="s">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31597.256165908038</v>
+        <v>31792.82089490179</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>46918.280367729436</v>
+        <v>49004.923682044529</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22738,7 +22738,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>78515.536533637467</v>
+        <v>80797.744576946323</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22765,7 +22765,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>77496.536533637467</v>
+        <v>79778.744576946323</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22783,22 +22783,22 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>194.71491591366197</v>
+        <v>200.44910697725206</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="241" t="s">
+      <c r="C39" s="246" t="s">
         <v>230</v>
       </c>
-      <c r="D39" s="241"/>
-      <c r="E39" s="241"/>
-      <c r="F39" s="241"/>
-      <c r="G39" s="241"/>
-      <c r="H39" s="241"/>
-      <c r="I39" s="241"/>
-      <c r="J39" s="241"/>
-      <c r="K39" s="241"/>
-      <c r="L39" s="241"/>
+      <c r="D39" s="246"/>
+      <c r="E39" s="246"/>
+      <c r="F39" s="246"/>
+      <c r="G39" s="246"/>
+      <c r="H39" s="246"/>
+      <c r="I39" s="246"/>
+      <c r="J39" s="246"/>
+      <c r="K39" s="246"/>
+      <c r="L39" s="246"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -29728,17 +29728,33 @@
       <c r="Q116" s="26">
         <v>317.52</v>
       </c>
-      <c r="T116" s="68"/>
-      <c r="U116" s="68"/>
-      <c r="V116" s="68"/>
-      <c r="W116" s="68"/>
-      <c r="X116" s="68"/>
-      <c r="Y116" s="68"/>
-      <c r="Z116" s="68"/>
-      <c r="AA116" s="68"/>
+      <c r="T116" s="26">
+        <v>574.41</v>
+      </c>
+      <c r="U116" s="26">
+        <v>513.88</v>
+      </c>
+      <c r="V116" s="26">
+        <v>438.65</v>
+      </c>
+      <c r="W116" s="26">
+        <v>415.09</v>
+      </c>
+      <c r="X116" s="26">
+        <v>356.7</v>
+      </c>
+      <c r="Y116" s="26">
+        <v>317.52</v>
+      </c>
+      <c r="Z116" s="26">
+        <v>262.41000000000003</v>
+      </c>
+      <c r="AA116" s="26">
+        <v>259.20999999999998</v>
+      </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>223.64</v>
+        <v>250.41</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29775,17 +29791,41 @@
         <f>Q116/Q85</f>
         <v>317.52</v>
       </c>
-      <c r="T117" s="68"/>
-      <c r="U117" s="68"/>
-      <c r="V117" s="68"/>
-      <c r="W117" s="68"/>
-      <c r="X117" s="68"/>
-      <c r="Y117" s="68"/>
-      <c r="Z117" s="68"/>
-      <c r="AA117" s="68"/>
+      <c r="T117" s="65">
+        <f t="shared" ref="T117:AA117" si="66">T116/T85</f>
+        <v>574.41</v>
+      </c>
+      <c r="U117" s="65">
+        <f t="shared" si="66"/>
+        <v>513.88</v>
+      </c>
+      <c r="V117" s="65">
+        <f t="shared" si="66"/>
+        <v>438.65</v>
+      </c>
+      <c r="W117" s="65">
+        <f t="shared" si="66"/>
+        <v>415.09</v>
+      </c>
+      <c r="X117" s="65">
+        <f t="shared" si="66"/>
+        <v>356.7</v>
+      </c>
+      <c r="Y117" s="65">
+        <f t="shared" si="66"/>
+        <v>317.52</v>
+      </c>
+      <c r="Z117" s="65">
+        <f t="shared" si="66"/>
+        <v>262.41000000000003</v>
+      </c>
+      <c r="AA117" s="65">
+        <f t="shared" si="66"/>
+        <v>259.20999999999998</v>
+      </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>223.64</v>
+        <v>250.41</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -29899,19 +29939,19 @@
         <v>103</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="66">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="67">M121*M122</f>
         <v>0.1770125913145626</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.17507822565801581</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.18227610060781085</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.21700297717499173</v>
       </c>
       <c r="Q123" s="76">
@@ -29973,19 +30013,19 @@
         <v>105</v>
       </c>
       <c r="M125" s="76">
-        <f t="shared" ref="M125:P125" si="67">M123*M124</f>
+        <f t="shared" ref="M125:P125" si="68">M123*M124</f>
         <v>0.3258768669324863</v>
       </c>
       <c r="N125" s="76">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.33848124688634257</v>
       </c>
       <c r="O125" s="76">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.32861121201113935</v>
       </c>
       <c r="P125" s="76">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.46508330379298118</v>
       </c>
       <c r="Q125" s="76">
@@ -30147,35 +30187,35 @@
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
       <c r="T131" s="25">
-        <f t="shared" ref="T131:AA131" si="68">U5</f>
+        <f t="shared" ref="T131:AA131" si="69">U5</f>
         <v>5606</v>
       </c>
       <c r="U131" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>5714</v>
       </c>
       <c r="V131" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>5873</v>
       </c>
       <c r="W131" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>5988</v>
       </c>
       <c r="X131" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>6194</v>
       </c>
       <c r="Y131" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>6398</v>
       </c>
       <c r="Z131" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>6618</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
@@ -30200,31 +30240,31 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="227" t="str">
-        <f t="shared" ref="T132:Z132" si="69">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Z132" si="70">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U132" s="227" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>BEAT</v>
       </c>
       <c r="V132" s="227" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>BEAT</v>
       </c>
       <c r="W132" s="227" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>BEAT</v>
       </c>
       <c r="X132" s="227" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>BEAT</v>
       </c>
       <c r="Y132" s="227" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>BEAT</v>
       </c>
       <c r="Z132" s="227" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>BEAT</v>
       </c>
       <c r="AA132" s="227" t="str">
@@ -30347,31 +30387,31 @@
         <v>3.79</v>
       </c>
       <c r="U135" s="231">
-        <f t="shared" ref="U135:AA135" si="70">V25</f>
+        <f t="shared" ref="U135:AA135" si="71">V25</f>
         <v>4.1399999999999997</v>
       </c>
       <c r="V135" s="231">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>3.94</v>
       </c>
       <c r="W135" s="231">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>4.18</v>
       </c>
       <c r="X135" s="231">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>4.45</v>
       </c>
       <c r="Y135" s="231">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="Z135" s="231">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>4.25</v>
       </c>
       <c r="AA135" s="231">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
@@ -30396,31 +30436,31 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="227" t="str">
-        <f t="shared" ref="T136:Z136" si="71">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Z136" si="72">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U136" s="227" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="V136" s="227" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="W136" s="227" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="X136" s="227" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>BEAT</v>
       </c>
       <c r="Y136" s="227" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>MET</v>
       </c>
       <c r="Z136" s="227" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>MISSED</v>
       </c>
       <c r="AA136" s="227" t="str">
@@ -30513,55 +30553,55 @@
         <v>140</v>
       </c>
       <c r="M141" s="120">
-        <f t="shared" ref="M141:Q142" si="72">M30/M5*365</f>
+        <f t="shared" ref="M141:Q142" si="73">M30/M5*365</f>
         <v>43.425403864428255</v>
       </c>
       <c r="N141" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>42.810689537657616</v>
       </c>
       <c r="O141" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>41.823896130661034</v>
       </c>
       <c r="P141" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>35.167635433620084</v>
       </c>
       <c r="Q141" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>35.994783120871723</v>
       </c>
       <c r="T141" s="120">
-        <f t="shared" ref="T141:AA141" si="73">T30/T5*90</f>
+        <f t="shared" ref="T141:AA141" si="74">T30/T5*90</f>
         <v>29.988905325443788</v>
       </c>
       <c r="U141" s="120">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>33.264359614698542</v>
       </c>
       <c r="V141" s="120">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>31.076303815190759</v>
       </c>
       <c r="W141" s="120">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>26.587774561552866</v>
       </c>
       <c r="X141" s="120">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>31.457915831663328</v>
       </c>
       <c r="Y141" s="120">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>34.058766548272523</v>
       </c>
       <c r="Z141" s="120">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>29.427946233197872</v>
       </c>
       <c r="AA141" s="120">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>27.103354487760654</v>
       </c>
       <c r="AC141" s="120">
@@ -30574,55 +30614,55 @@
         <v>141</v>
       </c>
       <c r="M142" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="N142" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="O142" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="P142" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q142" s="120">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="T142" s="120">
-        <f t="shared" ref="T142:AA142" si="74">T31/T6*365</f>
+        <f t="shared" ref="T142:AA142" si="75">T31/T6*365</f>
         <v>0</v>
       </c>
       <c r="U142" s="120">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="V142" s="120">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="W142" s="120">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X142" s="120">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="Y142" s="120">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="Z142" s="120">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AA142" s="120">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AC142" s="120">
@@ -30655,35 +30695,35 @@
         <v>59.664837318698552</v>
       </c>
       <c r="T143" s="120">
-        <f t="shared" ref="T143:AA143" si="75">T38/T6*90</f>
+        <f t="shared" ref="T143:AA143" si="76">T38/T6*90</f>
         <v>51.660649819494587</v>
       </c>
       <c r="U143" s="120">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>52.743506493506494</v>
       </c>
       <c r="V143" s="120">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>47.170418006430864</v>
       </c>
       <c r="W143" s="120">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>50.783699059561123</v>
       </c>
       <c r="X143" s="120">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>47.242990654205606</v>
       </c>
       <c r="Y143" s="120">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>57.827426810477661</v>
       </c>
       <c r="Z143" s="120">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>56.792168674698793</v>
       </c>
       <c r="AA143" s="120">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>62.811188811188813</v>
       </c>
       <c r="AC143" s="120">
@@ -30700,55 +30740,55 @@
         <v>-17.63625833396317</v>
       </c>
       <c r="N144" s="120">
-        <f t="shared" ref="N144:Q144" si="76">N141+N142-N143</f>
+        <f t="shared" ref="N144:Q144" si="77">N141+N142-N143</f>
         <v>-21.085384365344694</v>
       </c>
       <c r="O144" s="120">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-6.863444566025457</v>
       </c>
       <c r="P144" s="120">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-20.712347602851501</v>
       </c>
       <c r="Q144" s="120">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-23.670054197826829</v>
       </c>
       <c r="T144" s="120">
-        <f t="shared" ref="T144" si="77">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="78">T141+T142-T143</f>
         <v>-21.671744494050799</v>
       </c>
       <c r="U144" s="120">
-        <f t="shared" ref="U144" si="78">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="79">U141+U142-U143</f>
         <v>-19.479146878807953</v>
       </c>
       <c r="V144" s="120">
-        <f t="shared" ref="V144" si="79">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="80">V141+V142-V143</f>
         <v>-16.094114191240106</v>
       </c>
       <c r="W144" s="120">
-        <f t="shared" ref="W144" si="80">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="81">W141+W142-W143</f>
         <v>-24.195924498008257</v>
       </c>
       <c r="X144" s="120">
-        <f t="shared" ref="X144" si="81">X141+X142-X143</f>
+        <f t="shared" ref="X144" si="82">X141+X142-X143</f>
         <v>-15.785074822542278</v>
       </c>
       <c r="Y144" s="120">
-        <f t="shared" ref="Y144" si="82">Y141+Y142-Y143</f>
+        <f t="shared" ref="Y144" si="83">Y141+Y142-Y143</f>
         <v>-23.768660262205138</v>
       </c>
       <c r="Z144" s="120">
-        <f t="shared" ref="Z144:AA144" si="83">Z141+Z142-Z143</f>
+        <f t="shared" ref="Z144:AA144" si="84">Z141+Z142-Z143</f>
         <v>-27.364222441500921</v>
       </c>
       <c r="AA144" s="120">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-35.707834323428159</v>
       </c>
       <c r="AC144" s="120">
-        <f t="shared" ref="AC144" si="84">AC141+AC142-AC143</f>
+        <f t="shared" ref="AC144" si="85">AC141+AC142-AC143</f>
         <v>-39.346199522998823</v>
       </c>
     </row>
@@ -30777,35 +30817,35 @@
         <v>0.53428546846769331</v>
       </c>
       <c r="T145" s="120">
-        <f t="shared" ref="T145:AA145" si="85">T108/T49</f>
+        <f t="shared" ref="T145:AA145" si="86">T108/T49</f>
         <v>0.38686833963561362</v>
       </c>
       <c r="U145" s="120">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.39900744416873452</v>
       </c>
       <c r="V145" s="120">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.47002672775868654</v>
       </c>
       <c r="W145" s="120">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.53860936408106219</v>
       </c>
       <c r="X145" s="120">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.52676295666949868</v>
       </c>
       <c r="Y145" s="120">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.53428546846769331</v>
       </c>
       <c r="Z145" s="120">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.54473891367095251</v>
       </c>
       <c r="AA145" s="120">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.57692307692307687</v>
       </c>
       <c r="AC145" s="120">
@@ -30838,35 +30878,35 @@
         <v>-3.3123978318850555E-2</v>
       </c>
       <c r="T146" s="181">
-        <f t="shared" ref="T146:AA146" si="86">(T108-T107)/T49</f>
+        <f t="shared" ref="T146:AA146" si="87">(T108-T107)/T49</f>
         <v>-0.12980405637676176</v>
       </c>
       <c r="U146" s="181">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-0.16008507621410847</v>
       </c>
       <c r="V146" s="181">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-9.7747231767850329E-2</v>
       </c>
       <c r="W146" s="181">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>3.957023060796646E-2</v>
       </c>
       <c r="X146" s="181">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>2.2090059473237042E-2</v>
       </c>
       <c r="Y146" s="181">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-3.3123978318850555E-2</v>
       </c>
       <c r="Z146" s="181">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-5.7902562756931689E-2</v>
       </c>
       <c r="AA146" s="181">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>8.8470220524396598E-2</v>
       </c>
       <c r="AC146" s="181">
@@ -30899,35 +30939,35 @@
         <v>0.87637254901960782</v>
       </c>
       <c r="T147" s="120">
-        <f t="shared" ref="T147:AA147" si="87">(T107+T30)/T40</f>
+        <f t="shared" ref="T147:AA147" si="88">(T107+T30)/T40</f>
         <v>0.9660929075072584</v>
       </c>
       <c r="U147" s="120">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.94648797642809623</v>
       </c>
       <c r="V147" s="120">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1.0267379679144386</v>
       </c>
       <c r="W147" s="120">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.82398495408784156</v>
       </c>
       <c r="X147" s="120">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.8694663924667172</v>
       </c>
       <c r="Y147" s="120">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.87637254901960782</v>
       </c>
       <c r="Z147" s="120">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.78858647936786652</v>
       </c>
       <c r="AA147" s="120">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.63081636032455701</v>
       </c>
       <c r="AC147" s="120">
@@ -30960,35 +31000,35 @@
         <v>0.99637254901960781</v>
       </c>
       <c r="T148" s="120">
-        <f t="shared" ref="T148:AA148" si="88">T32/T40</f>
+        <f t="shared" ref="T148:AA148" si="89">T32/T40</f>
         <v>1.111157196184156</v>
       </c>
       <c r="U148" s="120">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1.0675791274593669</v>
       </c>
       <c r="V148" s="120">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1.1846556804539998</v>
       </c>
       <c r="W148" s="120">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.99325146587011837</v>
       </c>
       <c r="X148" s="120">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1.018724970234874</v>
       </c>
       <c r="Y148" s="120">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.99637254901960781</v>
       </c>
       <c r="Z148" s="120">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.91185250219490777</v>
       </c>
       <c r="AA148" s="120">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.75078655406524264</v>
       </c>
       <c r="AC148" s="120">
@@ -31021,35 +31061,35 @@
         <v>33.102661596958178</v>
       </c>
       <c r="T149" s="183">
-        <f t="shared" ref="T149:AA149" si="89">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T149:AA149" si="90">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>39.058823529411768</v>
       </c>
       <c r="U149" s="183">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>39.14</v>
       </c>
       <c r="V149" s="183">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>34.887096774193552</v>
       </c>
       <c r="W149" s="183">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>31.014705882352942</v>
       </c>
       <c r="X149" s="183">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>32.432835820895519</v>
       </c>
       <c r="Y149" s="183">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>34.257575757575758</v>
       </c>
       <c r="Z149" s="183">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>38.38095238095238</v>
       </c>
       <c r="AA149" s="183">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>34.430769230769229</v>
       </c>
       <c r="AC149" s="183">
@@ -31091,7 +31131,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>12.794050343249429</v>
+        <v>14.325514874141879</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31128,7 +31168,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.6699396777522022</v>
+        <v>4.1092362489086431</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31155,17 +31195,41 @@
         <f>Q117/(Statement!Q49/Statement!Q75)</f>
         <v>11.227800051621784</v>
       </c>
-      <c r="T152" s="49"/>
-      <c r="U152" s="49"/>
-      <c r="V152" s="49"/>
-      <c r="W152" s="49"/>
-      <c r="X152" s="49"/>
-      <c r="Y152" s="49"/>
-      <c r="Z152" s="49"/>
-      <c r="AA152" s="49"/>
+      <c r="T152" s="72">
+        <f>T117/(Statement!T49/Statement!T75)</f>
+        <v>17.37644551392231</v>
+      </c>
+      <c r="U152" s="72">
+        <f>U117/(Statement!U49/Statement!U75)</f>
+        <v>15.848124778447358</v>
+      </c>
+      <c r="V152" s="72">
+        <f>V117/(Statement!V49/Statement!V75)</f>
+        <v>14.269942726231386</v>
+      </c>
+      <c r="W152" s="72">
+        <f>W117/(Statement!W49/Statement!W75)</f>
+        <v>15.373703703703702</v>
+      </c>
+      <c r="X152" s="72">
+        <f>X117/(Statement!X49/Statement!X75)</f>
+        <v>12.698156329651656</v>
+      </c>
+      <c r="Y152" s="72">
+        <f>Y117/(Statement!Y49/Statement!Y75)</f>
+        <v>11.227800051621784</v>
+      </c>
+      <c r="Z152" s="72">
+        <f>Z117/(Statement!Z49/Statement!Z75)</f>
+        <v>9.2726003673576507</v>
+      </c>
+      <c r="AA152" s="72">
+        <f>AA117/(Statement!AA49/Statement!AA75)</f>
+        <v>8.9569005035596447</v>
+      </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.727793019621461</v>
+        <v>8.6528199340163212</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31192,17 +31256,41 @@
         <f>Statement!Q117*Statement!Q78</f>
         <v>130818.23999999999</v>
       </c>
-      <c r="T153" s="49"/>
-      <c r="U153" s="49"/>
-      <c r="V153" s="49"/>
-      <c r="W153" s="49"/>
-      <c r="X153" s="49"/>
-      <c r="Y153" s="49"/>
-      <c r="Z153" s="49"/>
-      <c r="AA153" s="49"/>
+      <c r="T153" s="145">
+        <f>Statement!T117*Statement!T78</f>
+        <v>253889.21999999997</v>
+      </c>
+      <c r="U153" s="145">
+        <f>Statement!U117*Statement!U78</f>
+        <v>225079.44</v>
+      </c>
+      <c r="V153" s="145">
+        <f>Statement!V117*Statement!V78</f>
+        <v>187303.55</v>
+      </c>
+      <c r="W153" s="145">
+        <f>Statement!W117*Statement!W78</f>
+        <v>176413.25</v>
+      </c>
+      <c r="X153" s="145">
+        <f>Statement!X117*Statement!X78</f>
+        <v>149814</v>
+      </c>
+      <c r="Y153" s="145">
+        <f>Statement!Y117*Statement!Y78</f>
+        <v>130818.23999999999</v>
+      </c>
+      <c r="Z153" s="145">
+        <f>Statement!Z117*Statement!Z78</f>
+        <v>106276.05</v>
+      </c>
+      <c r="AA153" s="145">
+        <f>Statement!AA117*Statement!AA78</f>
+        <v>103165.57999999999</v>
+      </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>89008.72</v>
+        <v>99663.18</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31229,17 +31317,41 @@
         <f>Q153+Q108-Q107+Q48+Q45</f>
         <v>130433.23999999999</v>
       </c>
-      <c r="T154" s="49"/>
-      <c r="U154" s="49"/>
-      <c r="V154" s="49"/>
-      <c r="W154" s="49"/>
-      <c r="X154" s="49"/>
-      <c r="Y154" s="49"/>
-      <c r="Z154" s="49"/>
-      <c r="AA154" s="49"/>
+      <c r="T154" s="145">
+        <f t="shared" ref="T154:AA154" si="91">T153+T108-T107+T48+T45</f>
+        <v>252001.21999999997</v>
+      </c>
+      <c r="U154" s="145">
+        <f t="shared" si="91"/>
+        <v>222821.44</v>
+      </c>
+      <c r="V154" s="145">
+        <f t="shared" si="91"/>
+        <v>186023.55</v>
+      </c>
+      <c r="W154" s="145">
+        <f t="shared" si="91"/>
+        <v>176866.25</v>
+      </c>
+      <c r="X154" s="145">
+        <f t="shared" si="91"/>
+        <v>150074</v>
+      </c>
+      <c r="Y154" s="145">
+        <f t="shared" si="91"/>
+        <v>130433.23999999999</v>
+      </c>
+      <c r="Z154" s="145">
+        <f t="shared" si="91"/>
+        <v>105614.05</v>
+      </c>
+      <c r="AA154" s="145">
+        <f t="shared" si="91"/>
+        <v>104184.57999999999</v>
+      </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>90027.72</v>
+        <v>100682.18</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31276,7 +31388,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>3.5728121279466625</v>
+        <v>3.9956417175966346</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31313,7 +31425,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>9.9040396039603955</v>
+        <v>11.076147414741474</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31341,35 +31453,35 @@
         <v>7910</v>
       </c>
       <c r="T157" s="64">
-        <f t="shared" ref="T157:AA157" si="90">T59-T54+T110+T65</f>
+        <f t="shared" ref="T157:AA157" si="92">T59-T54+T110+T65</f>
         <v>0</v>
       </c>
       <c r="U157" s="64">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="V157" s="64">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>1981</v>
       </c>
       <c r="W157" s="64">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>1663</v>
       </c>
       <c r="X157" s="64">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>1629</v>
       </c>
       <c r="Y157" s="64">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>2637</v>
       </c>
       <c r="Z157" s="64">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>2412</v>
       </c>
       <c r="AA157" s="64">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>1501</v>
       </c>
       <c r="AC157" s="64">
@@ -31423,19 +31535,19 @@
         <v>55.017182177877174</v>
       </c>
       <c r="N159" s="72">
-        <f t="shared" ref="N159:Q159" si="91">N153/N157</f>
+        <f t="shared" ref="N159:Q159" si="93">N153/N157</f>
         <v>26.518886836803226</v>
       </c>
       <c r="O159" s="72">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>53.100792496171515</v>
       </c>
       <c r="P159" s="72">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>37.264807947019868</v>
       </c>
       <c r="Q159" s="72">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>16.538336283185838</v>
       </c>
       <c r="T159" s="49"/>
@@ -31447,8 +31559,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
-        <f t="shared" ref="AC159:AC160" ca="1" si="92">AC153/AC157</f>
-        <v>10.882592003912459</v>
+        <f t="shared" ref="AC159:AC160" ca="1" si="94">AC153/AC157</f>
+        <v>12.185252475852792</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31460,19 +31572,19 @@
         <v>56.447947476875164</v>
       </c>
       <c r="N160" s="72">
-        <f t="shared" ref="N160:Q160" si="93">N154/N158</f>
+        <f t="shared" ref="N160:Q160" si="95">N154/N158</f>
         <v>27.967121726551518</v>
       </c>
       <c r="O160" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>49.979558824736309</v>
       </c>
       <c r="P160" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>35.791254971608261</v>
       </c>
       <c r="Q160" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>15.618610823671041</v>
       </c>
       <c r="T160" s="49"/>
@@ -31484,8 +31596,8 @@
       <c r="Z160" s="49"/>
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
-        <f t="shared" ca="1" si="92"/>
-        <v>11.092160263419865</v>
+        <f t="shared" ca="1" si="94"/>
+        <v>12.404877922383085</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31497,19 +31609,19 @@
         <v>1.8176139896930375E-2</v>
       </c>
       <c r="N161" s="74">
-        <f t="shared" ref="N161:Q161" si="94">N157/N153</f>
+        <f t="shared" ref="N161:Q161" si="96">N157/N153</f>
         <v>3.7708973463101328E-2</v>
       </c>
       <c r="O161" s="74">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>1.8832110652060391E-2</v>
       </c>
       <c r="P161" s="74">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>2.6834969911067843E-2</v>
       </c>
       <c r="Q161" s="74">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>6.0465574219619532E-2</v>
       </c>
       <c r="T161" s="49"/>
@@ -31521,8 +31633,8 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
-        <f t="shared" ref="AC161" ca="1" si="95">AC157/AC153</f>
-        <v>9.1889873261855687E-2</v>
+        <f t="shared" ref="AC161" ca="1" si="97">AC157/AC153</f>
+        <v>8.2066416102717171E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31559,7 +31671,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.816133071006974E-2</v>
+        <v>6.9805518948923756E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31633,7 +31745,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>0.10246187115150066</v>
+        <v>9.1508217979799564E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31670,7 +31782,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>0.10246187115150066</v>
+        <v>9.1508217979799564E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31920,35 +32032,35 @@
         <v>16.046228710462287</v>
       </c>
       <c r="T172" s="72">
-        <f t="shared" ref="T172:AA172" si="96">T107/T75</f>
+        <f t="shared" ref="T172:AA172" si="98">T107/T75</f>
         <v>17.079545454545453</v>
       </c>
       <c r="U172" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>18.128735632183908</v>
       </c>
       <c r="V172" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>17.453051643192488</v>
       </c>
       <c r="W172" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>13.474056603773585</v>
       </c>
       <c r="X172" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>14.176610978520287</v>
       </c>
       <c r="Y172" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>16.046228710462287</v>
       </c>
       <c r="Z172" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>17.054455445544555</v>
       </c>
       <c r="AA172" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>14.135678391959798</v>
       </c>
       <c r="AC172" s="72">
@@ -31981,35 +32093,35 @@
         <v>0.19359984049446716</v>
       </c>
       <c r="T173" s="156" t="e">
-        <f t="shared" ref="T173:AA173" si="97">T54/T59</f>
+        <f t="shared" ref="T173:AA173" si="99">T54/T59</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U173" s="156" t="e">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V173" s="156">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0.19137792103142626</v>
       </c>
       <c r="W173" s="156">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0.21953445915107256</v>
       </c>
       <c r="X173" s="156">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0.22611464968152867</v>
       </c>
       <c r="Y173" s="156">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0.15474683544303797</v>
       </c>
       <c r="Z173" s="156">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0.17207572684246111</v>
       </c>
       <c r="AA173" s="156">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0.24665127020785219</v>
       </c>
       <c r="AC173" s="156">
@@ -32042,35 +32154,35 @@
         <v>8.1703058605746975E-2</v>
       </c>
       <c r="T174" s="156">
-        <f t="shared" ref="T174:AA174" si="98">T54/T5</f>
+        <f t="shared" ref="T174:AA174" si="100">T54/T5</f>
         <v>0</v>
       </c>
       <c r="U174" s="156">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="V174" s="156">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>8.3129156457822886E-2</v>
       </c>
       <c r="W174" s="156">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>8.1900221351949604E-2</v>
       </c>
       <c r="X174" s="156">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>8.2999331997327994E-2</v>
       </c>
       <c r="Y174" s="156">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>7.8947368421052627E-2</v>
       </c>
       <c r="Z174" s="156">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>7.9556111284776493E-2</v>
       </c>
       <c r="AA174" s="156">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>8.0689029918404348E-2</v>
       </c>
       <c r="AC174" s="156">
@@ -32103,35 +32215,35 @@
         <v>0.93673965936739656</v>
       </c>
       <c r="T175" s="72">
-        <f t="shared" ref="T175:AA175" si="99">(T107-T108)/T75</f>
+        <f t="shared" ref="T175:AA175" si="101">(T107-T108)/T75</f>
         <v>4.290909090909091</v>
       </c>
       <c r="U175" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>5.190804597701149</v>
       </c>
       <c r="V175" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>3.004694835680751</v>
       </c>
       <c r="W175" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-1.0683962264150944</v>
       </c>
       <c r="X175" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-0.62052505966587113</v>
       </c>
       <c r="Y175" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.93673965936739656</v>
       </c>
       <c r="Z175" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>1.6386138613861385</v>
       </c>
       <c r="AA175" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-2.5603015075376883</v>
       </c>
       <c r="AC175" s="72">
@@ -32173,7 +32285,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.1448316524493331E-2</v>
+        <v>-1.0224437951909623E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32201,35 +32313,35 @@
         <v>7.5308174513021159E-3</v>
       </c>
       <c r="T177" s="156">
-        <f t="shared" ref="T177:AA177" si="100">-T110/T5</f>
+        <f t="shared" ref="T177:AA177" si="102">-T110/T5</f>
         <v>0</v>
       </c>
       <c r="U177" s="156">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="V177" s="156">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>4.5502275113755691E-3</v>
       </c>
       <c r="W177" s="156">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>8.0027243316873834E-3</v>
       </c>
       <c r="X177" s="156">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>1.2024048096192385E-2</v>
       </c>
       <c r="Y177" s="156">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>5.4891830804003876E-3</v>
       </c>
       <c r="Z177" s="156">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>5.7830572053766804E-3</v>
       </c>
       <c r="AA177" s="156">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>1.9643396796615292E-2</v>
       </c>
       <c r="AC177" s="156">
@@ -32262,35 +32374,35 @@
         <v>1.7844681487389095E-2</v>
       </c>
       <c r="T178" s="156" t="e">
-        <f t="shared" ref="T178:AA178" si="101">-(T110/T59)</f>
+        <f t="shared" ref="T178:AA178" si="103">-(T110/T59)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U178" s="156" t="e">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V178" s="156">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.0475423045930701E-2</v>
       </c>
       <c r="W178" s="156">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2.1451392058420813E-2</v>
       </c>
       <c r="X178" s="156">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>3.2757051865332121E-2</v>
       </c>
       <c r="Y178" s="156">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.0759493670886076E-2</v>
       </c>
       <c r="Z178" s="156">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.2508451656524679E-2</v>
       </c>
       <c r="AA178" s="156">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>6.0046189376443418E-2</v>
       </c>
       <c r="AC178" s="156">
@@ -32323,35 +32435,35 @@
         <v>0.21882640586797067</v>
       </c>
       <c r="T179" s="156" t="e">
-        <f t="shared" ref="T179:AA179" si="102">-T110/T53</f>
+        <f t="shared" ref="T179:AA179" si="104">-T110/T53</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U179" s="156" t="e">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V179" s="156">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.11981566820276497</v>
       </c>
       <c r="W179" s="156">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.22488038277511962</v>
       </c>
       <c r="X179" s="156">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.34615384615384615</v>
       </c>
       <c r="Y179" s="156">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.18478260869565216</v>
       </c>
       <c r="Z179" s="156">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.21264367816091953</v>
       </c>
       <c r="AA179" s="156">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>0.67357512953367871</v>
       </c>
       <c r="AC179" s="156">
@@ -32368,19 +32480,19 @@
         <v>0.57945743548327888</v>
       </c>
       <c r="N180" s="226">
-        <f t="shared" ref="N180:Q180" si="103">N5/N37</f>
+        <f t="shared" ref="N180:Q180" si="105">N5/N37</f>
         <v>0.64811338118902995</v>
       </c>
       <c r="O180" s="226">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.65176802444675774</v>
       </c>
       <c r="P180" s="226">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.71137942441283497</v>
       </c>
       <c r="Q180" s="226">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.80583807973962573</v>
       </c>
       <c r="T180" s="49"/>
@@ -32392,7 +32504,7 @@
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
       <c r="AC180" s="226">
-        <f t="shared" ref="AC180" si="104">AC5/AC37</f>
+        <f t="shared" ref="AC180" si="106">AC5/AC37</f>
         <v>0.8418133832225303</v>
       </c>
     </row>
@@ -32405,19 +32517,19 @@
         <v>0.71061702861082388</v>
       </c>
       <c r="N181" s="228">
-        <f t="shared" ref="N181:Q181" si="105">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
+        <f t="shared" ref="N181:Q181" si="107">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
         <v>0.67710724827812396</v>
       </c>
       <c r="O181" s="228">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.54646616541353388</v>
       </c>
       <c r="P181" s="228">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.83489096573208721</v>
       </c>
       <c r="Q181" s="228">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.7133011716057891</v>
       </c>
       <c r="T181" s="49"/>
@@ -32429,7 +32541,7 @@
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
       <c r="AC181" s="228">
-        <f t="shared" ref="AC181" si="106">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
+        <f t="shared" ref="AC181" si="108">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
         <v>0.73102310231023104</v>
       </c>
     </row>
@@ -32442,19 +32554,19 @@
         <v>-0.28869355394691487</v>
       </c>
       <c r="N182" s="228">
-        <f t="shared" ref="N182:Q182" si="107">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
+        <f t="shared" ref="N182:Q182" si="109">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
         <v>-0.32256477533617578</v>
       </c>
       <c r="O182" s="228">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.632781954887218</v>
       </c>
       <c r="P182" s="228">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.33496513870345646</v>
       </c>
       <c r="Q182" s="228">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-4.422237537330577E-2</v>
       </c>
       <c r="T182" s="49"/>
@@ -32466,7 +32578,7 @@
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
       <c r="AC182" s="228">
-        <f t="shared" ref="AC182" si="108">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
+        <f t="shared" ref="AC182" si="110">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
         <v>0.1121012101210121</v>
       </c>
     </row>
@@ -32479,19 +32591,19 @@
         <v>1.2029416247523244</v>
       </c>
       <c r="N183" s="228">
-        <f t="shared" ref="N183:Q183" si="109">N5/(N108+N112-N107)</f>
+        <f t="shared" ref="N183:Q183" si="111">N5/(N108+N112-N107)</f>
         <v>1.4569678914266799</v>
       </c>
       <c r="O183" s="228">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>1.5766856214459788</v>
       </c>
       <c r="P183" s="228">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>1.8152274837511606</v>
       </c>
       <c r="Q183" s="228">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>2.1150560597971171</v>
       </c>
       <c r="T183" s="49"/>
@@ -32503,7 +32615,7 @@
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
       <c r="AC183" s="228">
-        <f t="shared" ref="AC183" si="110">AC5/(AC108+AC112-AC107)</f>
+        <f t="shared" ref="AC183" si="112">AC5/(AC108+AC112-AC107)</f>
         <v>2.0098907234585628</v>
       </c>
     </row>
@@ -32633,7 +32745,7 @@
         <v>89</v>
       </c>
       <c r="AC188" s="62">
-        <f t="shared" ref="AC188:AC193" si="111">SUM(X188:AA188)</f>
+        <f t="shared" ref="AC188:AC193" si="113">SUM(X188:AA188)</f>
         <v>321</v>
       </c>
     </row>
@@ -32691,7 +32803,7 @@
         <v>113</v>
       </c>
       <c r="AC189" s="62">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>483</v>
       </c>
     </row>
@@ -32763,7 +32875,7 @@
         <v>586</v>
       </c>
       <c r="AC191" s="62">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2158</v>
       </c>
     </row>
@@ -32821,7 +32933,7 @@
         <v>5</v>
       </c>
       <c r="AC192" s="62">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>22</v>
       </c>
     </row>
@@ -32879,7 +32991,7 @@
         <v>124</v>
       </c>
       <c r="AC193" s="62">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>490</v>
       </c>
     </row>
@@ -32943,61 +33055,61 @@
       <c r="K197" s="81"/>
       <c r="L197" s="81"/>
       <c r="M197" s="81">
-        <f t="shared" ref="M197:Q199" si="112">IF(L187=0,
+        <f t="shared" ref="M197:Q199" si="114">IF(L187=0,
 IF(M187=0,0,IF(M187&gt;0,1,-1)),
 (M187-L187)/ABS(L187)
 )</f>
         <v>1</v>
       </c>
       <c r="N197" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>0.1245453921635902</v>
       </c>
       <c r="O197" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>0.11569441054430071</v>
       </c>
       <c r="P197" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>0.12234740756945964</v>
       </c>
       <c r="Q197" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>0.11612494517811023</v>
       </c>
       <c r="T197" s="81">
-        <f t="shared" ref="T197:AA199" si="113">IF(S187=0,
+        <f t="shared" ref="T197:AA199" si="115">IF(S187=0,
 IF(T187=0,0,IF(T187&gt;0,1,-1)),
 (T187-S187)/ABS(S187)
 )</f>
         <v>1</v>
       </c>
       <c r="U197" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="V197" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.1994408201304754E-2</v>
       </c>
       <c r="W197" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.8816341418931243E-2</v>
       </c>
       <c r="X197" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.6591029959227089E-2</v>
       </c>
       <c r="Y197" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>3.4190986012778452E-2</v>
       </c>
       <c r="Z197" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>3.4897311738186679E-2</v>
       </c>
       <c r="AA197" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>3.5172636334301385E-2</v>
       </c>
       <c r="AC197" s="49"/>
@@ -33007,55 +33119,55 @@
         <v>389</v>
       </c>
       <c r="M198" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1</v>
       </c>
       <c r="N198" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>-4.1441441441441441E-2</v>
       </c>
       <c r="O198" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>-0.13533834586466165</v>
       </c>
       <c r="P198" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>-0.16086956521739129</v>
       </c>
       <c r="Q198" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>-0.15803108808290156</v>
       </c>
       <c r="T198" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>1</v>
       </c>
       <c r="U198" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>-1.2195121951219513E-2</v>
       </c>
       <c r="V198" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.1728395061728395</v>
       </c>
       <c r="W198" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>-7.3684210526315783E-2</v>
       </c>
       <c r="X198" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>-0.22727272727272727</v>
       </c>
       <c r="Y198" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>8.8235294117647065E-2</v>
       </c>
       <c r="Z198" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.21621621621621623</v>
       </c>
       <c r="AA198" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>-1.1111111111111112E-2</v>
       </c>
       <c r="AC198" s="49"/>
@@ -33065,55 +33177,55 @@
         <v>390</v>
       </c>
       <c r="M199" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1</v>
       </c>
       <c r="N199" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>4.4140030441400302E-2</v>
       </c>
       <c r="O199" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>-3.0612244897959183E-2</v>
       </c>
       <c r="P199" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>-0.10075187969924812</v>
       </c>
       <c r="Q199" s="81">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>-9.6989966555183951E-2</v>
       </c>
       <c r="T199" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>1</v>
       </c>
       <c r="U199" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>9.5890410958904104E-2</v>
       </c>
       <c r="V199" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>-0.15</v>
       </c>
       <c r="W199" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="X199" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>-0.10416666666666667</v>
       </c>
       <c r="Y199" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>1.5503875968992248E-2</v>
       </c>
       <c r="Z199" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>-0.16030534351145037</v>
       </c>
       <c r="AA199" s="81">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.7272727272727271E-2</v>
       </c>
       <c r="AC199" s="49"/>
@@ -33253,15 +33365,15 @@
         <v>51.215990950765026</v>
       </c>
       <c r="O207" s="145">
-        <f t="shared" ref="O207:Q207" si="114">100*(1+((O117-$M117)/ABS($M117)))</f>
+        <f t="shared" ref="O207:Q207" si="116">100*(1+((O117-$M117)/ABS($M117)))</f>
         <v>90.940346490444725</v>
       </c>
       <c r="P207" s="145">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>76.483895933797697</v>
       </c>
       <c r="Q207" s="145">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>47.258439006965524</v>
       </c>
       <c r="T207" s="49"/>
@@ -33286,15 +33398,15 @@
         <v>111.53626860943935</v>
       </c>
       <c r="O208" s="145">
-        <f t="shared" ref="O208:Q208" si="115">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O208:Q208" si="117">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>122.95850490972443</v>
       </c>
       <c r="P208" s="145">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>136.23693379790942</v>
       </c>
       <c r="Q208" s="145">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>150.57966423820082</v>
       </c>
       <c r="T208" s="49"/>
@@ -33319,15 +33431,15 @@
         <v>100.79840319361277</v>
       </c>
       <c r="O209" s="145">
-        <f t="shared" ref="O209:Q209" si="116">100*(1+((O26-$M26)/ABS($M26)))</f>
+        <f t="shared" ref="O209:Q209" si="118">100*(1+((O26-$M26)/ABS($M26)))</f>
         <v>117.96407185628743</v>
       </c>
       <c r="P209" s="145">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>145.4868041694389</v>
       </c>
       <c r="Q209" s="145">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>166.66666666666666</v>
       </c>
       <c r="T209" s="49"/>
@@ -33434,15 +33546,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="237" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="237"/>
+      <c r="E4" s="237" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33450,7 +33562,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>223.64</v>
+        <v>250.41</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33466,7 +33578,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>89008.72</v>
+        <v>99663.18</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33486,7 +33598,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>90027.72</v>
+        <v>100682.18</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33506,7 +33618,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>12.794050343249429</v>
+        <v>14.325514874141879</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -33526,7 +33638,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.6699396777522022</v>
+        <v>4.1092362489086431</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -33546,7 +33658,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>7.727793019621461</v>
+        <v>8.6528199340163212</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33566,7 +33678,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.5728121279466625</v>
+        <v>3.9956417175966346</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33575,18 +33687,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>9.9040396039603955</v>
+        <v>11.076147414741474</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="237" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="237"/>
+      <c r="E15" s="237" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33637,14 +33749,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="237" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="237"/>
+      <c r="E21" s="237" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="237"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33713,14 +33825,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="237" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="237"/>
+      <c r="E29" s="237" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="237"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33796,14 +33908,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="237" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="237"/>
+      <c r="E37" s="237" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="237"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33811,7 +33923,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>7.816133071006974E-2</v>
+        <v>6.9805518948923756E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33827,7 +33939,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>9.1889873261855687E-2</v>
+        <v>8.2066416102717171E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -33859,7 +33971,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.10246187115150066</v>
+        <v>9.1508217979799564E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33868,18 +33980,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.10246187115150066</v>
+        <v>9.1508217979799564E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="237" t="s">
         <v>285</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="237"/>
+      <c r="E45" s="237" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="237"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33912,18 +34024,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1448316524493331E-2</v>
+        <v>-1.0224437951909623E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="237" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="237"/>
+      <c r="E51" s="237" t="s">
         <v>309</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="237"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34091,7 +34203,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>223.64</v>
+        <v>250.41</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34120,7 +34232,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>89008.72</v>
+        <v>99663.18</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34149,7 +34261,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>90027.72</v>
+        <v>100682.18</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34178,7 +34290,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>12.794050343249429</v>
+        <v>14.325514874141879</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34207,7 +34319,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>3.6699396777522022</v>
+        <v>4.1092362489086431</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34236,7 +34348,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>7.727793019621461</v>
+        <v>8.6528199340163212</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34265,7 +34377,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.5728121279466625</v>
+        <v>3.9956417175966346</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34294,7 +34406,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>9.9040396039603955</v>
+        <v>11.076147414741474</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35067,7 +35179,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>7.816133071006974E-2</v>
+        <v>6.9805518948923756E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35096,7 +35208,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>9.1889873261855687E-2</v>
+        <v>8.2066416102717171E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35154,7 +35266,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>0.10246187115150066</v>
+        <v>9.1508217979799564E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35183,7 +35295,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>0.10246187115150066</v>
+        <v>9.1508217979799564E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35419,7 +35531,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-1.1448316524493331E-2</v>
+        <v>-1.0224437951909623E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35905,14 +36017,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="241" t="s">
         <v>319</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>320</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35979,19 +36091,19 @@
       <c r="B7" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="244">
         <f>Statement!AA89</f>
         <v>3.4385745545482967E-2</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1268516941937681</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -36018,19 +36130,19 @@
       <c r="B9" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="244">
         <f>Statement!AA90</f>
         <v>7.6807228915662648E-2</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1206896551724138</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -36057,19 +36169,19 @@
       <c r="B11" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="244">
         <f>Statement!AA91</f>
         <v>2.9473317056156263E-2</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12760267430754538</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -36096,19 +36208,19 @@
       <c r="B13" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="244">
         <f>Statement!AA95</f>
         <v>0.10524728588661038</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.172424824056302</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -36135,19 +36247,19 @@
       <c r="B15" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="244">
         <f>Statement!AA96</f>
         <v>-7.4441687344913146E-2</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.1166429587482217E-2</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -36174,19 +36286,19 @@
       <c r="B17" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="244">
         <f>Statement!AA98</f>
         <v>-9.3700370566437263E-2</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2418687167356593E-2</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -36213,22 +36325,22 @@
       <c r="B19" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.1897810218978103E-2</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.2937062937062943E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -36255,22 +36367,22 @@
       <c r="B21" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-7.6086956521739066E-2</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>7.8680203045685293E-2</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36318,22 +36430,22 @@
       <c r="B25" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5172636334301385E-2</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13738698812267328</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36360,22 +36472,22 @@
       <c r="B27" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-1.1111111111111112E-2</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36402,22 +36514,22 @@
       <c r="B29" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.21527777777777779</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="24">
